--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
         <v>1.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I11" t="n">
         <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>3.25</v>
       </c>
       <c r="J21" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE22" t="n">
         <v>22</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>1.63</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I23" t="n">
         <v>6.4</v>
@@ -4894,7 +4894,7 @@
         <v>55</v>
       </c>
       <c r="AA23" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB23" t="n">
         <v>9.6</v>
@@ -4945,7 +4945,7 @@
         <v>21</v>
       </c>
       <c r="AR23" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS23" t="n">
         <v>44</v>
@@ -4981,7 +4981,7 @@
         <v>14</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE23" t="n">
         <v>85</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.27</v>
       </c>
       <c r="G26" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -5425,7 +5425,7 @@
         <v>5.6</v>
       </c>
       <c r="J26" t="n">
-        <v>2.24</v>
+        <v>1.21</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
         <v>3.65</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>1.37</v>
+        <v>2.54</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5909,52 +5909,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G30" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H30" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I30" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-14 01:56:35</t>
+          <t>2026-03-14 04:27:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
         <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1002,7 +1002,7 @@
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="G11" t="n">
         <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="I11" t="n">
         <v>3.3</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>4.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.12</v>
+        <v>1.28</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>60</v>
       </c>
       <c r="H16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I16" t="n">
         <v>2.1</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="G17" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="I17" t="n">
         <v>60</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K17" t="n">
         <v>85</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
         <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
         <v>1.93</v>
@@ -4781,7 +4781,7 @@
         <v>30</v>
       </c>
       <c r="BB22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC22" t="n">
         <v>42</v>
@@ -4790,7 +4790,7 @@
         <v>48</v>
       </c>
       <c r="BE22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF22" t="n">
         <v>30</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
         <v>9.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>85</v>
@@ -4912,7 +4912,7 @@
         <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
@@ -4942,7 +4942,7 @@
         <v>17</v>
       </c>
       <c r="AQ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR23" t="n">
         <v>46</v>
@@ -4960,10 +4960,10 @@
         <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>9.199999999999999</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.27</v>
       </c>
       <c r="G26" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -5425,7 +5425,7 @@
         <v>5.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.21</v>
+        <v>2.24</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="G28" t="n">
         <v>3.65</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="I28" t="n">
         <v>3</v>
@@ -5816,7 +5816,7 @@
         <v>2.54</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>1.69</v>
       </c>
       <c r="H30" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>7.6</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-14 04:27:53</t>
+          <t>2026-03-14 06:59:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>240</v>
+        <v>2.28</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>240</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
         <v>2.08</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.9</v>
-      </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>85</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>85</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,37 +2295,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.4</v>
       </c>
-      <c r="K10" t="n">
-        <v>5.9</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.28</v>
+        <v>2.68</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.01</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.08</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puskas Akademia</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>60</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>85</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1.97</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>85</v>
+        <v>9.6</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>LR Vicenza Virtus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,37 +4041,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>3.75</v>
       </c>
       <c r="H19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I19" t="n">
         <v>3.25</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.7</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7.6</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.27</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,66 +4235,66 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LR Vicenza Virtus</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P20" t="n">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,66 +4429,66 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.66</v>
+        <v>1.61</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75</v>
+        <v>1.63</v>
       </c>
       <c r="H21" t="n">
-        <v>2.38</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,66 +4817,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="G23" t="n">
-        <v>1.63</v>
+        <v>3.4</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Q24" t="n">
         <v>1.01</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,66 +5205,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="H25" t="n">
         <v>2.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="K25" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="Q25" t="n">
         <v>2.06</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.27</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,36 +5593,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Colo Colo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H27" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.07</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,589 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-14 06:59:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Brazilian Serie A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Gremio</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-03-14 06:59:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Santiago Wanderers</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="K29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-14 06:59:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chilean Primera Division</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Colo Colo</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Huachipato</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="H30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-03-14 06:59:13</t>
+          <t>2026-03-14 09:30:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,16 +975,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1002,7 +1002,7 @@
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Digenis Ypsona</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enosis Neon Paralimni</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G4" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="I4" t="n">
-        <v>240</v>
+        <v>2.24</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="K4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
@@ -1330,28 +1330,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ethnikos Achnas</t>
+          <t>Digenis Ypsona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis Neon Paralimni</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1.77</v>
+        <v>240</v>
       </c>
       <c r="J5" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
         <v>85</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>Ethnikos Achnas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="J6" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>1.87</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>60</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>85</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.4</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.46</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.01</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>60</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>1.65</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>1.97</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>85</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
@@ -3464,22 +3464,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
         <v>4.7</v>
@@ -3488,7 +3488,7 @@
         <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
         <v>1.89</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LR Vicenza Virtus</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>LR Vicenza Virtus</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,61 +4240,61 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="H20" t="n">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="I20" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
         <v>2.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,66 +4429,66 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.61</v>
+        <v>4.3</v>
       </c>
       <c r="G21" t="n">
-        <v>1.63</v>
+        <v>4.5</v>
       </c>
       <c r="H21" t="n">
-        <v>6.2</v>
+        <v>1.99</v>
       </c>
       <c r="I21" t="n">
-        <v>6.4</v>
+        <v>2.02</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>19</v>
       </c>
-      <c r="Y21" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AI21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AW21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>17</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC21" t="n">
         <v>46</v>
       </c>
-      <c r="AS21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA21" t="n">
+      <c r="BD21" t="n">
         <v>50</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BE21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG21" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>36</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,66 +4817,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.46</v>
+        <v>1.76</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Q24" t="n">
         <v>1.01</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,66 +5205,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H25" t="n">
         <v>2.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="J25" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="K25" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="Q25" t="n">
         <v>2.06</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="G26" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="H26" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="n">
-        <v>2.26</v>
+        <v>1.21</v>
       </c>
       <c r="K26" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,201 +5576,783 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-14 09:30:32</t>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K27" t="n">
+        <v>950</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-14 12:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I28" t="n">
+        <v>970</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-14 12:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-14 12:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Chilean Primera Division</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Colo Colo</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Huachipato</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G30" t="n">
         <v>1.69</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H30" t="n">
         <v>6</v>
       </c>
-      <c r="I27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="I30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>4.4</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q30" t="n">
         <v>1.89</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-14 09:30:32</t>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-14 12:01:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -763,19 +763,19 @@
         <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -799,16 +799,16 @@
         <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>16.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
@@ -975,7 +975,7 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
@@ -984,7 +984,7 @@
         <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
         <v>13</v>
@@ -1178,7 +1178,7 @@
         <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
@@ -1196,7 +1196,7 @@
         <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
         <v>25</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1357,37 +1357,37 @@
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R5" t="n">
         <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="T5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
         <v>1.62</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,22 +1644,22 @@
         <v>3.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS6" t="n">
         <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
         <v>4.3</v>
@@ -1668,35 +1668,35 @@
         <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BA6" t="n">
         <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
         <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
         <v>3.25</v>
@@ -1754,13 +1754,13 @@
         <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
@@ -1775,10 +1775,10 @@
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1787,13 +1787,13 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>9.4</v>
@@ -1835,19 +1835,19 @@
         <v>30</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
@@ -1856,41 +1856,41 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>660</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
         <v>770</v>
@@ -1936,31 +1936,31 @@
         <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1972,7 +1972,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
         <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="I9" t="n">
         <v>1.49</v>
@@ -2136,7 +2136,7 @@
         <v>1.24</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>5.1</v>
@@ -2148,16 +2148,16 @@
         <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
         <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2184,7 +2184,7 @@
         <v>38</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2235,7 +2235,7 @@
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AU9" t="n">
         <v>10.5</v>
@@ -2247,38 +2247,38 @@
         <v>10.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
         <v>1.68</v>
@@ -2318,13 +2318,13 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2333,7 +2333,7 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
@@ -2354,7 +2354,7 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V10" t="n">
         <v>1.16</v>
@@ -2366,7 +2366,7 @@
         <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2381,25 +2381,25 @@
         <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK10" t="n">
         <v>18.5</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2423,10 +2423,10 @@
         <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -2438,7 +2438,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>70</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
         <v>11.5</v>
@@ -2462,17 +2462,17 @@
         <v>30</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H11" t="n">
         <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.7</v>
@@ -2527,7 +2527,7 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O11" t="n">
         <v>1.48</v>
@@ -2551,7 +2551,7 @@
         <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
         <v>2.34</v>
@@ -2566,7 +2566,7 @@
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB11" t="n">
         <v>6.8</v>
@@ -2578,7 +2578,7 @@
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
         <v>8.800000000000001</v>
@@ -2620,7 +2620,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT11" t="n">
         <v>5.5</v>
@@ -2632,7 +2632,7 @@
         <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>7.6</v>
@@ -2641,10 +2641,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>15.5</v>
@@ -2656,17 +2656,17 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF11" t="n">
         <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.43</v>
@@ -2727,7 +2727,7 @@
         <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
@@ -2739,16 +2739,16 @@
         <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AR12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB12" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="H13" t="n">
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.29</v>
@@ -2921,7 +2921,7 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
         <v>1.74</v>
@@ -2939,10 +2939,10 @@
         <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2987,7 +2987,7 @@
         <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -2999,62 +2999,62 @@
         <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
         <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY13" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
@@ -3100,10 +3100,10 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3136,7 +3136,7 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -3199,7 +3199,7 @@
         <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS14" t="n">
         <v>5.3</v>
@@ -3214,7 +3214,7 @@
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX14" t="n">
         <v>9.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.18</v>
       </c>
       <c r="G15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H15" t="n">
         <v>21</v>
@@ -3303,25 +3303,25 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
         <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="U15" t="n">
         <v>1.51</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AX15" t="n">
         <v>3.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="BF15" t="n">
         <v>3.45</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3518,10 +3518,10 @@
         <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
@@ -3536,7 +3536,7 @@
         <v>11</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB16" t="n">
         <v>26</v>
@@ -3626,17 +3626,17 @@
         <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG16" t="n">
         <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
         <v>3.35</v>
@@ -3682,7 +3682,7 @@
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.31</v>
@@ -3709,16 +3709,16 @@
         <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="n">
         <v>24</v>
@@ -3736,7 +3736,7 @@
         <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
         <v>17</v>
@@ -3784,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3793,7 +3793,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
         <v>25</v>
@@ -3808,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3820,7 +3820,7 @@
         <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
         <v>3.8</v>
@@ -3894,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
         <v>1.39</v>
@@ -3969,13 +3969,13 @@
         <v>95</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AQ18" t="n">
         <v>16.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS18" t="n">
         <v>4.2</v>
@@ -3987,7 +3987,7 @@
         <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW18" t="n">
         <v>4.1</v>
@@ -3996,7 +3996,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>16.5</v>
@@ -4008,23 +4008,23 @@
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BE18" t="n">
         <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG18" t="n">
         <v>4.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G19" t="n">
         <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I19" t="n">
         <v>3.85</v>
@@ -4070,16 +4070,16 @@
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
@@ -4112,7 +4112,7 @@
         <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
         <v>32</v>
@@ -4121,43 +4121,43 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>19.5</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4172,7 +4172,7 @@
         <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -4196,7 +4196,7 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>19.5</v>
@@ -4205,20 +4205,20 @@
         <v>18.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
         <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
         <v>3.1</v>
@@ -4273,7 +4273,7 @@
         <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O20" t="n">
         <v>1.62</v>
@@ -4282,7 +4282,7 @@
         <v>1.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.16</v>
@@ -4291,10 +4291,10 @@
         <v>6.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
         <v>1.47</v>
@@ -4303,7 +4303,7 @@
         <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y20" t="n">
         <v>8.199999999999999</v>
@@ -4312,7 +4312,7 @@
         <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AB20" t="n">
         <v>8.199999999999999</v>
@@ -4321,28 +4321,28 @@
         <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="AF20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AI20" t="n">
         <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AK20" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="AL20" t="n">
         <v>80</v>
@@ -4354,7 +4354,7 @@
         <v>65</v>
       </c>
       <c r="AO20" t="n">
-        <v>70</v>
+        <v>790</v>
       </c>
       <c r="AP20" t="n">
         <v>6.8</v>
@@ -4366,7 +4366,7 @@
         <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="AT20" t="n">
         <v>7.2</v>
@@ -4375,10 +4375,10 @@
         <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
@@ -4387,32 +4387,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>3.75</v>
       </c>
       <c r="H21" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I21" t="n">
         <v>2.84</v>
       </c>
       <c r="J21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K21" t="n">
         <v>2.88</v>
@@ -4560,7 +4560,7 @@
         <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G22" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
         <v>2.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4703,13 +4703,13 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
         <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4721,7 +4721,7 @@
         <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4745,16 +4745,16 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
         <v>8.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT22" t="n">
         <v>7.8</v>
@@ -4766,41 +4766,41 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX22" t="n">
         <v>14.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
         <v>3.75</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -4858,13 +4858,13 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>1.34</v>
@@ -4876,79 +4876,79 @@
         <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
         <v>17</v>
       </c>
       <c r="Y23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
         <v>17</v>
       </c>
-      <c r="Z23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH23" t="n">
         <v>19</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AI23" t="n">
         <v>60</v>
       </c>
-      <c r="AF23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>65</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP23" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
         <v>8.199999999999999</v>
@@ -4960,7 +4960,7 @@
         <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,7 +4972,7 @@
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4981,20 +4981,20 @@
         <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BF23" t="n">
         <v>12</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G24" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.17</v>
@@ -5049,22 +5049,22 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R24" t="n">
         <v>2.06</v>
       </c>
       <c r="S24" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="T24" t="n">
         <v>1.42</v>
@@ -5073,46 +5073,46 @@
         <v>3.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD24" t="n">
         <v>20</v>
       </c>
       <c r="AE24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
         <v>15.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
@@ -5127,7 +5127,7 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -5136,25 +5136,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT24" t="n">
         <v>18.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV24" t="n">
         <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -5166,10 +5166,10 @@
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC24" t="n">
         <v>14.5</v>
@@ -5178,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF24" t="n">
         <v>5.1</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G25" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H25" t="n">
         <v>4.9</v>
       </c>
       <c r="I25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
         <v>5.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.17</v>
@@ -5249,13 +5249,13 @@
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
         <v>1.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S25" t="n">
         <v>1.8</v>
@@ -5264,13 +5264,13 @@
         <v>1.48</v>
       </c>
       <c r="U25" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5303,7 +5303,7 @@
         <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB25" t="n">
         <v>6</v>
       </c>
-      <c r="BB25" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC25" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>4.1</v>
       </c>
       <c r="G26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I26" t="n">
         <v>1.9</v>
@@ -5449,22 +5449,22 @@
         <v>1.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -5479,7 +5479,7 @@
         <v>25</v>
       </c>
       <c r="AB26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC26" t="n">
         <v>13</v>
@@ -5488,7 +5488,7 @@
         <v>13.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
         <v>46</v>
@@ -5503,16 +5503,16 @@
         <v>32</v>
       </c>
       <c r="AJ26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AK26" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL26" t="n">
         <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN26" t="n">
         <v>38</v>
@@ -5545,7 +5545,7 @@
         <v>14</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY26" t="n">
         <v>15</v>
@@ -5557,26 +5557,26 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF26" t="n">
         <v>4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>3.8</v>
       </c>
       <c r="BG26" t="n">
         <v>5.7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -5610,25 +5610,25 @@
         <v>1.94</v>
       </c>
       <c r="G27" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
         <v>2.46</v>
@@ -5655,7 +5655,7 @@
         <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
         <v>1.87</v>
@@ -5673,7 +5673,7 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5721,10 +5721,10 @@
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT27" t="n">
         <v>5.5</v>
@@ -5736,7 +5736,7 @@
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5745,32 +5745,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="BC27" t="n">
         <v>6</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF27" t="n">
         <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I28" t="n">
         <v>3.95</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K28" t="n">
         <v>4.6</v>
@@ -5825,37 +5825,37 @@
         <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q28" t="n">
         <v>1.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S28" t="n">
         <v>2.36</v>
       </c>
       <c r="T28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U28" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
         <v>1.9</v>
       </c>
       <c r="X28" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y28" t="n">
         <v>21</v>
@@ -5864,7 +5864,7 @@
         <v>32</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
         <v>970</v>
@@ -5876,7 +5876,7 @@
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF28" t="n">
         <v>970</v>
@@ -5903,22 +5903,22 @@
         <v>60</v>
       </c>
       <c r="AN28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP28" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
         <v>12</v>
@@ -5927,10 +5927,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
@@ -5942,29 +5942,29 @@
         <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF28" t="n">
         <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>18.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -5995,58 +5995,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="G29" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="I29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="O29" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>3.15</v>
       </c>
       <c r="H30" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I30" t="n">
         <v>2.72</v>
@@ -6219,22 +6219,22 @@
         <v>1.49</v>
       </c>
       <c r="P30" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R30" t="n">
         <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
         <v>1.58</v>
@@ -6243,7 +6243,7 @@
         <v>1.46</v>
       </c>
       <c r="X30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
         <v>8.800000000000001</v>
@@ -6297,7 +6297,7 @@
         <v>40</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
         <v>7.8</v>
@@ -6342,17 +6342,17 @@
         <v>50</v>
       </c>
       <c r="BE30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG30" t="n">
         <v>30</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -6383,40 +6383,40 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G31" t="n">
         <v>3.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>3.25</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
         <v>1.28</v>
@@ -6431,10 +6431,10 @@
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
         <v>13.5</v>
@@ -6494,7 +6494,7 @@
         <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR31" t="n">
         <v>14.5</v>
@@ -6533,20 +6533,20 @@
         <v>30</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BE31" t="n">
         <v>7.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G32" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H32" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -6604,13 +6604,13 @@
         <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
@@ -6619,7 +6619,7 @@
         <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U32" t="n">
         <v>1.96</v>
@@ -6628,7 +6628,7 @@
         <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X32" t="n">
         <v>12</v>
@@ -6685,7 +6685,7 @@
         <v>70</v>
       </c>
       <c r="AP32" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ32" t="n">
         <v>10.5</v>
@@ -6700,7 +6700,7 @@
         <v>7.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
         <v>13</v>
@@ -6715,16 +6715,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
         <v>6.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD32" t="n">
         <v>6.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -6771,28 +6771,28 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H33" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I33" t="n">
         <v>2.02</v>
       </c>
       <c r="J33" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
         <v>3.1</v>
@@ -6801,7 +6801,7 @@
         <v>1.41</v>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q33" t="n">
         <v>2.2</v>
@@ -6810,7 +6810,7 @@
         <v>1.27</v>
       </c>
       <c r="S33" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
         <v>1.98</v>
@@ -6822,28 +6822,28 @@
         <v>1.98</v>
       </c>
       <c r="W33" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
         <v>13</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>10.5</v>
       </c>
       <c r="AE33" t="n">
         <v>24</v>
@@ -6852,19 +6852,19 @@
         <v>32</v>
       </c>
       <c r="AG33" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
@@ -6873,10 +6873,10 @@
         <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO33" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AP33" t="n">
         <v>10.5</v>
@@ -6900,41 +6900,41 @@
         <v>9.4</v>
       </c>
       <c r="AW33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX33" t="n">
-        <v>26</v>
+        <v>5.1</v>
       </c>
       <c r="AY33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC33" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="BG33" t="n">
         <v>13.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="K34" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
         <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U34" t="n">
         <v>2.02</v>
       </c>
       <c r="V34" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W34" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X34" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA34" t="n">
         <v>65</v>
@@ -7034,7 +7034,7 @@
         <v>10.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD34" t="n">
         <v>970</v>
@@ -7046,7 +7046,7 @@
         <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH34" t="n">
         <v>970</v>
@@ -7064,7 +7064,7 @@
         <v>50</v>
       </c>
       <c r="AM34" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN34" t="n">
         <v>32</v>
@@ -7073,62 +7073,62 @@
         <v>50</v>
       </c>
       <c r="AP34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY34" t="n">
         <v>10</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS34" t="n">
+      <c r="AZ34" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC34" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA34" t="n">
+      <c r="BD34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF34" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB34" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG34" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G35" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H35" t="n">
         <v>5.8</v>
@@ -7171,13 +7171,13 @@
         <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K35" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -7192,25 +7192,25 @@
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
         <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
@@ -7228,7 +7228,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
@@ -7267,28 +7267,28 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT35" t="n">
         <v>7.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV35" t="n">
         <v>6</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX35" t="n">
         <v>8.800000000000001</v>
@@ -7297,32 +7297,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC35" t="n">
         <v>15</v>
       </c>
       <c r="BD35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -7359,16 +7359,16 @@
         <v>4.3</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K36" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.75</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7383,40 +7383,40 @@
         <v>1.33</v>
       </c>
       <c r="P36" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
         <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V36" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W36" t="n">
         <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z36" t="n">
         <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB36" t="n">
         <v>15</v>
@@ -7434,7 +7434,7 @@
         <v>30</v>
       </c>
       <c r="AG36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH36" t="n">
         <v>19</v>
@@ -7449,7 +7449,7 @@
         <v>55</v>
       </c>
       <c r="AL36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM36" t="n">
         <v>100</v>
@@ -7458,49 +7458,49 @@
         <v>60</v>
       </c>
       <c r="AO36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP36" t="n">
         <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU36" t="n">
         <v>7.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW36" t="n">
         <v>19.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY36" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ36" t="n">
         <v>17.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB36" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BC36" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BD36" t="n">
         <v>50</v>
@@ -7509,14 +7509,14 @@
         <v>38</v>
       </c>
       <c r="BF36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG36" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -7553,10 +7553,10 @@
         <v>2.74</v>
       </c>
       <c r="H37" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I37" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
@@ -7571,37 +7571,37 @@
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P37" t="n">
         <v>1.94</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R37" t="n">
         <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="T37" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U37" t="n">
         <v>2.28</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="X37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y37" t="n">
         <v>970</v>
@@ -7625,7 +7625,7 @@
         <v>42</v>
       </c>
       <c r="AF37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG37" t="n">
         <v>970</v>
@@ -7670,10 +7670,10 @@
         <v>3.35</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AW37" t="n">
         <v>3.9</v>
@@ -7682,7 +7682,7 @@
         <v>3.55</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AZ37" t="n">
         <v>3.5</v>
@@ -7697,20 +7697,20 @@
         <v>3.75</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE37" t="n">
         <v>4.1</v>
       </c>
       <c r="BF37" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG37" t="n">
         <v>3.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -7741,16 +7741,16 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G38" t="n">
         <v>1.77</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.78</v>
-      </c>
       <c r="H38" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I38" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>3.9</v>
@@ -7768,13 +7768,13 @@
         <v>3.85</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>1.36</v>
@@ -7795,16 +7795,16 @@
         <v>2.28</v>
       </c>
       <c r="X38" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y38" t="n">
         <v>17.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA38" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB38" t="n">
         <v>8.199999999999999</v>
@@ -7852,7 +7852,7 @@
         <v>13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR38" t="n">
         <v>38</v>
@@ -7864,7 +7864,7 @@
         <v>7.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV38" t="n">
         <v>19</v>
@@ -7873,22 +7873,22 @@
         <v>65</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB38" t="n">
         <v>16.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD38" t="n">
         <v>32</v>
@@ -7897,14 +7897,14 @@
         <v>42</v>
       </c>
       <c r="BF38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG38" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="G39" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H39" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I39" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J39" t="n">
         <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L39" t="n">
         <v>1.48</v>
@@ -7962,28 +7962,28 @@
         <v>2.68</v>
       </c>
       <c r="O39" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P39" t="n">
         <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U39" t="n">
         <v>1.8</v>
       </c>
       <c r="V39" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
         <v>1.72</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G40" t="n">
         <v>1.63</v>
@@ -8141,10 +8141,10 @@
         <v>6.4</v>
       </c>
       <c r="J40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K40" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.36</v>
@@ -8159,10 +8159,10 @@
         <v>1.26</v>
       </c>
       <c r="P40" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R40" t="n">
         <v>1.48</v>
@@ -8171,7 +8171,7 @@
         <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U40" t="n">
         <v>2.08</v>
@@ -8180,13 +8180,13 @@
         <v>1.18</v>
       </c>
       <c r="W40" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z40" t="n">
         <v>50</v>
@@ -8201,13 +8201,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE40" t="n">
         <v>80</v>
       </c>
       <c r="AF40" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG40" t="n">
         <v>9.800000000000001</v>
@@ -8219,7 +8219,7 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK40" t="n">
         <v>16</v>
@@ -8228,7 +8228,7 @@
         <v>32</v>
       </c>
       <c r="AM40" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN40" t="n">
         <v>8</v>
@@ -8237,19 +8237,19 @@
         <v>90</v>
       </c>
       <c r="AP40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ40" t="n">
         <v>21</v>
       </c>
       <c r="AR40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS40" t="n">
         <v>130</v>
       </c>
       <c r="AT40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU40" t="n">
         <v>9.4</v>
@@ -8264,7 +8264,7 @@
         <v>9.4</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ40" t="n">
         <v>19.5</v>
@@ -8288,11 +8288,11 @@
         <v>7.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G41" t="n">
         <v>1.97</v>
@@ -8338,10 +8338,10 @@
         <v>3.75</v>
       </c>
       <c r="K41" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M41" t="n">
         <v>1.06</v>
@@ -8350,34 +8350,34 @@
         <v>4.1</v>
       </c>
       <c r="O41" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P41" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R41" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V41" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W41" t="n">
         <v>2.02</v>
       </c>
       <c r="X41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="n">
         <v>21</v>
@@ -8392,7 +8392,7 @@
         <v>12</v>
       </c>
       <c r="AC41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD41" t="n">
         <v>22</v>
@@ -8437,10 +8437,10 @@
         <v>13</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT41" t="n">
         <v>8.800000000000001</v>
@@ -8452,7 +8452,7 @@
         <v>14</v>
       </c>
       <c r="AW41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX41" t="n">
         <v>11</v>
@@ -8464,29 +8464,29 @@
         <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB41" t="n">
         <v>18.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G42" t="n">
         <v>1.93</v>
@@ -8526,13 +8526,13 @@
         <v>4.5</v>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L42" t="n">
         <v>1.35</v>
@@ -8541,13 +8541,13 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q42" t="n">
         <v>1.92</v>
@@ -8556,7 +8556,7 @@
         <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
         <v>1.73</v>
@@ -8619,68 +8619,68 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR42" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD42" t="n">
         <v>5.4</v>
       </c>
-      <c r="AT42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>5</v>
-      </c>
       <c r="BE42" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF42" t="n">
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -8735,10 +8735,10 @@
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O43" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P43" t="n">
         <v>1.66</v>
@@ -8750,13 +8750,13 @@
         <v>1.24</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T43" t="n">
         <v>1.89</v>
       </c>
       <c r="U43" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V43" t="n">
         <v>1.48</v>
@@ -8765,31 +8765,31 @@
         <v>1.5</v>
       </c>
       <c r="X43" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z43" t="n">
         <v>22</v>
       </c>
       <c r="AA43" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB43" t="n">
         <v>11</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE43" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF43" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG43" t="n">
         <v>15</v>
@@ -8798,13 +8798,13 @@
         <v>23</v>
       </c>
       <c r="AI43" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ43" t="n">
         <v>60</v>
       </c>
       <c r="AK43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL43" t="n">
         <v>65</v>
@@ -8813,13 +8813,13 @@
         <v>160</v>
       </c>
       <c r="AN43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ43" t="n">
         <v>8.4</v>
@@ -8828,7 +8828,7 @@
         <v>15.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT43" t="n">
         <v>8.199999999999999</v>
@@ -8840,7 +8840,7 @@
         <v>11</v>
       </c>
       <c r="AW43" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="AX43" t="n">
         <v>15.5</v>
@@ -8852,29 +8852,29 @@
         <v>16.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC43" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF43" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G44" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H44" t="n">
         <v>5.9</v>
@@ -8917,52 +8917,52 @@
         <v>7.2</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K44" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N44" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P44" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="R44" t="n">
         <v>1.17</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="T44" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U44" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V44" t="n">
         <v>1.16</v>
       </c>
       <c r="W44" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
@@ -8971,7 +8971,7 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC44" t="n">
         <v>9.4</v>
@@ -9013,62 +9013,62 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR44" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX44" t="n">
         <v>7.8</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -9099,43 +9099,43 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G45" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="H45" t="n">
         <v>3.25</v>
       </c>
       <c r="I45" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K45" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="O45" t="n">
         <v>1.43</v>
       </c>
       <c r="P45" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R45" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S45" t="n">
         <v>3.8</v>
@@ -9144,16 +9144,16 @@
         <v>1.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V45" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W45" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X45" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y45" t="n">
         <v>13.5</v>
@@ -9174,10 +9174,10 @@
         <v>18.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF45" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG45" t="n">
         <v>14.5</v>
@@ -9189,10 +9189,10 @@
         <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL45" t="n">
         <v>60</v>
@@ -9201,68 +9201,68 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO45" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>8.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="AQ45" t="n">
-        <v>8.4</v>
+        <v>3.55</v>
       </c>
       <c r="AR45" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT45" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="AU45" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="AV45" t="n">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="AW45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ45" t="n">
         <v>4</v>
       </c>
-      <c r="AX45" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA45" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB45" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BC45" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD45" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF45" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF45" t="n">
-        <v>20</v>
-      </c>
       <c r="BG45" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>2.22</v>
       </c>
       <c r="G46" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H46" t="n">
         <v>4.1</v>
@@ -9308,10 +9308,10 @@
         <v>2.86</v>
       </c>
       <c r="K46" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L46" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M46" t="n">
         <v>1.15</v>
@@ -9320,13 +9320,13 @@
         <v>2.28</v>
       </c>
       <c r="O46" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P46" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R46" t="n">
         <v>1.14</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -9490,10 +9490,10 @@
         <v>2.3</v>
       </c>
       <c r="G47" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="H47" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
         <v>4.3</v>
@@ -9502,7 +9502,7 @@
         <v>2.76</v>
       </c>
       <c r="K47" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L47" t="n">
         <v>1.42</v>
@@ -9514,7 +9514,7 @@
         <v>2.58</v>
       </c>
       <c r="O47" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
@@ -9547,7 +9547,7 @@
         <v>970</v>
       </c>
       <c r="Z47" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA47" t="n">
         <v>85</v>
@@ -9592,7 +9592,7 @@
         <v>38</v>
       </c>
       <c r="AO47" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP47" t="n">
         <v>3.2</v>
@@ -9622,7 +9622,7 @@
         <v>3.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AZ47" t="n">
         <v>3.7</v>
@@ -9646,11 +9646,11 @@
         <v>3.9</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
         <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J48" t="n">
         <v>4.6</v>
@@ -9705,28 +9705,28 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O48" t="n">
         <v>1.45</v>
       </c>
       <c r="P48" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R48" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S48" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T48" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U48" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V48" t="n">
         <v>1.1</v>
@@ -9735,7 +9735,7 @@
         <v>3.2</v>
       </c>
       <c r="X48" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y48" t="n">
         <v>24</v>
@@ -9750,16 +9750,16 @@
         <v>5.8</v>
       </c>
       <c r="AC48" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD48" t="n">
         <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG48" t="n">
         <v>11.5</v>
@@ -9789,62 +9789,62 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ48" t="n">
         <v>19.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="AS48" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AT48" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV48" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AW48" t="n">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AX48" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY48" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ48" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BA48" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB48" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC48" t="n">
         <v>18</v>
       </c>
       <c r="BD48" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="BE48" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF48" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -9875,16 +9875,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G49" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H49" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="I49" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J49" t="n">
         <v>3.25</v>
@@ -9893,7 +9893,7 @@
         <v>3.4</v>
       </c>
       <c r="L49" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -9905,7 +9905,7 @@
         <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
         <v>2.16</v>
@@ -9920,13 +9920,13 @@
         <v>1.83</v>
       </c>
       <c r="U49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W49" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X49" t="n">
         <v>14</v>
@@ -9938,10 +9938,10 @@
         <v>17.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC49" t="n">
         <v>7.8</v>
@@ -9950,7 +9950,7 @@
         <v>13</v>
       </c>
       <c r="AE49" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF49" t="n">
         <v>22</v>
@@ -9959,16 +9959,16 @@
         <v>14.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI49" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL49" t="n">
         <v>55</v>
@@ -9977,10 +9977,10 @@
         <v>130</v>
       </c>
       <c r="AN49" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO49" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP49" t="n">
         <v>10.5</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU49" t="n">
         <v>6.8</v>
@@ -10004,10 +10004,10 @@
         <v>10</v>
       </c>
       <c r="AW49" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AX49" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY49" t="n">
         <v>11.5</v>
@@ -10016,10 +10016,10 @@
         <v>16.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB49" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC49" t="n">
         <v>30</v>
@@ -10028,17 +10028,17 @@
         <v>42</v>
       </c>
       <c r="BE49" t="n">
-        <v>7.8</v>
+        <v>85</v>
       </c>
       <c r="BF49" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BG49" t="n">
         <v>20</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -10069,16 +10069,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G50" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H50" t="n">
         <v>3.05</v>
       </c>
       <c r="I50" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>3.15</v>
@@ -10102,13 +10102,13 @@
         <v>1.73</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R50" t="n">
         <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="T50" t="n">
         <v>1.83</v>
@@ -10117,10 +10117,10 @@
         <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W50" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X50" t="n">
         <v>14.5</v>
@@ -10162,7 +10162,7 @@
         <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL50" t="n">
         <v>1000</v>
@@ -10180,59 +10180,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AR50" t="n">
         <v>16</v>
       </c>
       <c r="AS50" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AV50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX50" t="n">
         <v>3.45</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>3.5</v>
       </c>
       <c r="AY50" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ50" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BA50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE50" t="n">
         <v>4</v>
       </c>
-      <c r="BB50" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF50" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BG50" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.18</v>
       </c>
       <c r="G51" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="H51" t="n">
         <v>3.55</v>
@@ -10278,7 +10278,7 @@
         <v>2.7</v>
       </c>
       <c r="K51" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L51" t="n">
         <v>1.43</v>
@@ -10293,10 +10293,10 @@
         <v>1.45</v>
       </c>
       <c r="P51" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R51" t="n">
         <v>1.22</v>
@@ -10389,7 +10389,7 @@
         <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="AW51" t="n">
         <v>4</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>2.12</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H52" t="n">
         <v>3.5</v>
@@ -10472,10 +10472,10 @@
         <v>3.15</v>
       </c>
       <c r="K52" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L52" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10487,10 +10487,10 @@
         <v>1.39</v>
       </c>
       <c r="P52" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R52" t="n">
         <v>1.26</v>
@@ -10565,37 +10565,37 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR52" t="n">
         <v>4.4</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT52" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV52" t="n">
         <v>4</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX52" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY52" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA52" t="n">
         <v>4.8</v>
@@ -10607,20 +10607,20 @@
         <v>4.4</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>1.62</v>
       </c>
       <c r="G53" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H53" t="n">
         <v>5.8</v>
@@ -10693,7 +10693,7 @@
         <v>3.1</v>
       </c>
       <c r="T53" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U53" t="n">
         <v>2</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
         <v>2.76</v>
       </c>
       <c r="G54" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H54" t="n">
         <v>2.88</v>
@@ -10857,7 +10857,7 @@
         <v>3.1</v>
       </c>
       <c r="J54" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K54" t="n">
         <v>3.25</v>
@@ -10884,7 +10884,7 @@
         <v>1.18</v>
       </c>
       <c r="S54" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T54" t="n">
         <v>2.16</v>
@@ -10896,7 +10896,7 @@
         <v>1.47</v>
       </c>
       <c r="W54" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X54" t="n">
         <v>9.6</v>
@@ -10914,7 +10914,7 @@
         <v>970</v>
       </c>
       <c r="AC54" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD54" t="n">
         <v>970</v>
@@ -10959,10 +10959,10 @@
         <v>7.2</v>
       </c>
       <c r="AR54" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT54" t="n">
         <v>7.2</v>
@@ -10971,44 +10971,44 @@
         <v>5.9</v>
       </c>
       <c r="AV54" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW54" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX54" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY54" t="n">
         <v>6</v>
       </c>
       <c r="AZ54" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB54" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC54" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC54" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE54" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BF54" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BG54" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>1.83</v>
       </c>
       <c r="G55" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H55" t="n">
         <v>5.4</v>
@@ -11051,7 +11051,7 @@
         <v>7.2</v>
       </c>
       <c r="J55" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="K55" t="n">
         <v>3.55</v>
@@ -11060,25 +11060,25 @@
         <v>1.47</v>
       </c>
       <c r="M55" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N55" t="n">
         <v>2.56</v>
       </c>
       <c r="O55" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P55" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="R55" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S55" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T55" t="n">
         <v>2.26</v>
@@ -11087,13 +11087,13 @@
         <v>1.67</v>
       </c>
       <c r="V55" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W55" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X55" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y55" t="n">
         <v>17</v>
@@ -11105,7 +11105,7 @@
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC55" t="n">
         <v>9.4</v>
@@ -11141,7 +11141,7 @@
         <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
@@ -11153,10 +11153,10 @@
         <v>12</v>
       </c>
       <c r="AR55" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT55" t="n">
         <v>5.4</v>
@@ -11168,7 +11168,7 @@
         <v>21</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX55" t="n">
         <v>8.6</v>
@@ -11177,32 +11177,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB55" t="n">
         <v>19</v>
       </c>
       <c r="BC55" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF55" t="n">
         <v>16.5</v>
       </c>
       <c r="BG55" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G2" t="n">
         <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
         <v>2.76</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.4</v>
@@ -781,13 +781,13 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
         <v>1.93</v>
@@ -796,73 +796,73 @@
         <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD2" t="n">
         <v>13</v>
       </c>
-      <c r="Z2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG2" t="n">
         <v>14</v>
       </c>
-      <c r="AC2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -874,7 +874,7 @@
         <v>13.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -898,29 +898,29 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
         <v>18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -969,7 +969,7 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1002,119 +1002,119 @@
         <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.85</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>2.64</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>2.78</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
         <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,104 +1211,104 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AR4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC4" t="n">
         <v>12</v>
       </c>
-      <c r="AH4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="BD4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5</v>
       </c>
-      <c r="AS4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1351,16 +1351,16 @@
         <v>1.13</v>
       </c>
       <c r="J5" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>1.1</v>
@@ -1369,19 +1369,19 @@
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
         <v>1.33</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T5" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="U5" t="n">
         <v>1.52</v>
@@ -1393,7 +1393,7 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1444,65 +1444,65 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
         <v>5.4</v>
       </c>
-      <c r="AU5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>2.04</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="BG5" t="n">
         <v>2.02</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
@@ -1566,13 +1566,13 @@
         <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
         <v>2.08</v>
@@ -1581,13 +1581,13 @@
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,19 +1641,19 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
         <v>9.6</v>
@@ -1662,22 +1662,22 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
         <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
@@ -1686,17 +1686,17 @@
         <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
         <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
         <v>2.68</v>
@@ -1736,7 +1736,7 @@
         <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
@@ -1781,7 +1781,7 @@
         <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -1790,7 +1790,7 @@
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -1802,7 +1802,7 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -1814,16 +1814,16 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM7" t="n">
         <v>90</v>
@@ -1835,19 +1835,19 @@
         <v>30</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
@@ -1859,38 +1859,38 @@
         <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
         <v>26</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
         <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
         <v>20</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
         <v>770</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
@@ -1945,22 +1945,22 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1972,7 +1972,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G9" t="n">
         <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.24</v>
@@ -2139,25 +2139,25 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2166,10 +2166,10 @@
         <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y9" t="n">
         <v>12.5</v>
@@ -2181,19 +2181,19 @@
         <v>15.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>17.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AG9" t="n">
         <v>36</v>
@@ -2220,25 +2220,25 @@
         <v>130</v>
       </c>
       <c r="AO9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>9</v>
@@ -2247,10 +2247,10 @@
         <v>10.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>19.5</v>
@@ -2259,26 +2259,26 @@
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
         <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2312,64 +2312,64 @@
         <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V10" t="n">
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X10" t="n">
         <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2405,13 +2405,13 @@
         <v>18.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2423,10 +2423,10 @@
         <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -2438,7 +2438,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
         <v>11.5</v>
@@ -2462,17 +2462,17 @@
         <v>30</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2503,49 +2503,49 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
         <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
         <v>1.68</v>
@@ -2560,113 +2560,113 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA11" t="n">
         <v>290</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
         <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
         <v>170</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2697,64 +2697,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="I12" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="W12" t="n">
         <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2766,10 +2766,10 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2781,7 +2781,7 @@
         <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2802,65 +2802,65 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AX12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA12" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BF12" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.7</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.29</v>
@@ -2939,28 +2939,28 @@
         <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y13" t="n">
         <v>22</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>23</v>
       </c>
       <c r="Z13" t="n">
         <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>23</v>
@@ -2975,16 +2975,16 @@
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
         <v>34</v>
@@ -2993,22 +2993,22 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT13" t="n">
         <v>8.6</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3041,20 +3041,20 @@
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3127,16 +3127,16 @@
         <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
         <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -3184,13 +3184,13 @@
         <v>46</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>15.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP14" t="n">
         <v>11.5</v>
@@ -3199,7 +3199,7 @@
         <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
         <v>5.3</v>
@@ -3235,20 +3235,20 @@
         <v>16.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF14" t="n">
         <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>1.32</v>
@@ -3309,7 +3309,7 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
         <v>1.64</v>
@@ -3321,7 +3321,7 @@
         <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="U15" t="n">
         <v>1.51</v>
@@ -3381,68 +3381,68 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.64</v>
+        <v>4.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AW15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC15" t="n">
         <v>5.9</v>
       </c>
-      <c r="AV15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BB15" t="n">
+      <c r="BD15" t="n">
         <v>4</v>
       </c>
-      <c r="BC15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="BF15" t="n">
         <v>3.45</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.64</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>6.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="I16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3497,13 +3497,13 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
         <v>1.96</v>
@@ -3515,16 +3515,16 @@
         <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>1.84</v>
       </c>
       <c r="V16" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
         <v>17.5</v>
@@ -3542,43 +3542,43 @@
         <v>26</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>22</v>
       </c>
       <c r="AF16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AH16" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
         <v>260</v>
       </c>
       <c r="AK16" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="AL16" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AM16" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>180</v>
+        <v>540</v>
       </c>
       <c r="AO16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3614,29 +3614,29 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG16" t="n">
         <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
         <v>3.35</v>
@@ -3682,7 +3682,7 @@
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.31</v>
@@ -3694,16 +3694,16 @@
         <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
         <v>2.62</v>
@@ -3715,16 +3715,16 @@
         <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
@@ -3739,10 +3739,10 @@
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
@@ -3751,10 +3751,10 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
         <v>32</v>
@@ -3763,10 +3763,10 @@
         <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
         <v>14.5</v>
@@ -3784,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3808,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3820,7 +3820,7 @@
         <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G18" t="n">
         <v>1.82</v>
@@ -3870,13 +3870,13 @@
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.3</v>
@@ -3909,7 +3909,7 @@
         <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
         <v>2.22</v>
@@ -3918,7 +3918,7 @@
         <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
         <v>55</v>
@@ -3945,10 +3945,10 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ18" t="n">
         <v>22</v>
@@ -3966,19 +3966,19 @@
         <v>12</v>
       </c>
       <c r="AO18" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
         <v>16.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
         <v>7.8</v>
@@ -3990,7 +3990,7 @@
         <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX18" t="n">
         <v>9.199999999999999</v>
@@ -4002,7 +4002,7 @@
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
@@ -4011,20 +4011,20 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE18" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
         <v>8.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
         <v>2.22</v>
@@ -4070,10 +4070,10 @@
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4109,7 +4109,7 @@
         <v>1.81</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y19" t="n">
         <v>16</v>
@@ -4130,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF19" t="n">
         <v>15.5</v>
@@ -4145,16 +4145,16 @@
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>15</v>
@@ -4172,7 +4172,7 @@
         <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -4196,7 +4196,7 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
         <v>19.5</v>
@@ -4205,20 +4205,20 @@
         <v>18.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BF19" t="n">
         <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4249,145 +4249,145 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
         <v>1.64</v>
       </c>
       <c r="M20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O20" t="n">
         <v>1.62</v>
       </c>
       <c r="P20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T20" t="n">
         <v>2.24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
         <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AJ20" t="n">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="AK20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL20" t="n">
         <v>170</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>80</v>
       </c>
       <c r="AM20" t="n">
         <v>270</v>
       </c>
       <c r="AN20" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AO20" t="n">
-        <v>790</v>
+        <v>210</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY20" t="n">
         <v>13</v>
       </c>
-      <c r="AW20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
         <v>36</v>
@@ -4396,23 +4396,23 @@
         <v>27</v>
       </c>
       <c r="BC20" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF20" t="n">
         <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>3.75</v>
       </c>
       <c r="H21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I21" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="L21" t="n">
         <v>1.76</v>
@@ -4470,22 +4470,22 @@
         <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="P21" t="n">
         <v>1.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S21" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="U21" t="n">
         <v>1.57</v>
@@ -4497,7 +4497,7 @@
         <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y21" t="n">
         <v>6.8</v>
@@ -4509,7 +4509,7 @@
         <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>7.4</v>
@@ -4530,7 +4530,7 @@
         <v>36</v>
       </c>
       <c r="AI21" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ21" t="n">
         <v>110</v>
@@ -4539,13 +4539,13 @@
         <v>85</v>
       </c>
       <c r="AL21" t="n">
-        <v>160</v>
+        <v>540</v>
       </c>
       <c r="AM21" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
         <v>85</v>
@@ -4560,7 +4560,7 @@
         <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
         <v>19.5</v>
@@ -4581,32 +4581,32 @@
         <v>16</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG21" t="n">
         <v>55</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4661,7 +4661,7 @@
         <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
         <v>1.46</v>
@@ -4676,49 +4676,49 @@
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z22" t="n">
         <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
         <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
         <v>22</v>
@@ -4727,16 +4727,16 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="AN22" t="n">
         <v>1000</v>
@@ -4751,56 +4751,56 @@
         <v>8.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
         <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>2.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
         <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>1.39</v>
@@ -4861,16 +4861,16 @@
         <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="T23" t="n">
         <v>1.83</v>
@@ -4882,25 +4882,25 @@
         <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
         <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
         <v>17</v>
@@ -4930,7 +4930,7 @@
         <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
         <v>17</v>
@@ -4945,10 +4945,10 @@
         <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
         <v>8.199999999999999</v>
@@ -4972,7 +4972,7 @@
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4984,17 +4984,17 @@
         <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
         <v>12</v>
       </c>
       <c r="BG23" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.82</v>
       </c>
       <c r="G24" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H24" t="n">
         <v>3.65</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
         <v>5.2</v>
@@ -5055,16 +5055,16 @@
         <v>1.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T24" t="n">
         <v>1.42</v>
@@ -5076,7 +5076,7 @@
         <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5085,19 +5085,19 @@
         <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA24" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
@@ -5106,19 +5106,19 @@
         <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
         <v>1000</v>
@@ -5127,25 +5127,25 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>11.5</v>
@@ -5154,31 +5154,31 @@
         <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BF24" t="n">
         <v>5.1</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H25" t="n">
         <v>4.9</v>
@@ -5231,10 +5231,10 @@
         <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.17</v>
@@ -5243,22 +5243,22 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="T25" t="n">
         <v>1.48</v>
@@ -5270,7 +5270,7 @@
         <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5285,7 +5285,7 @@
         <v>110</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC25" t="n">
         <v>1000</v>
@@ -5300,7 +5300,7 @@
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5309,7 +5309,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA25" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BB25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG25" t="n">
         <v>6</v>
       </c>
-      <c r="BC25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>1.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
@@ -5452,7 +5452,7 @@
         <v>1.67</v>
       </c>
       <c r="S26" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
         <v>1.54</v>
@@ -5461,46 +5461,46 @@
         <v>2.6</v>
       </c>
       <c r="V26" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y26" t="n">
         <v>17</v>
       </c>
       <c r="Z26" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AB26" t="n">
         <v>28</v>
       </c>
       <c r="AC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD26" t="n">
         <v>13</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13.5</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ26" t="n">
         <v>85</v>
@@ -5512,13 +5512,13 @@
         <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AP26" t="n">
         <v>24</v>
@@ -5545,7 +5545,7 @@
         <v>14</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>15</v>
@@ -5557,26 +5557,26 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="BF26" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
         <v>1.87</v>
       </c>
       <c r="X27" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y27" t="n">
         <v>13</v>
@@ -5670,7 +5670,7 @@
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
         <v>7.6</v>
@@ -5682,7 +5682,7 @@
         <v>23</v>
       </c>
       <c r="AE27" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF27" t="n">
         <v>11.5</v>
@@ -5703,7 +5703,7 @@
         <v>32</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -5721,10 +5721,10 @@
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT27" t="n">
         <v>5.5</v>
@@ -5736,7 +5736,7 @@
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5748,29 +5748,29 @@
         <v>22</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
         <v>22</v>
       </c>
       <c r="BC27" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF27" t="n">
         <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q28" t="n">
         <v>1.54</v>
@@ -5849,76 +5849,76 @@
         <v>2.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X28" t="n">
         <v>34</v>
       </c>
       <c r="Y28" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="Z28" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AA28" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="n">
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH28" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="AK28" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AM28" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO28" t="n">
         <v>32</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AT28" t="n">
         <v>12</v>
@@ -5930,7 +5930,7 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
@@ -5942,29 +5942,29 @@
         <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>19.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>19</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF28" t="n">
         <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G29" t="n">
         <v>1.69</v>
@@ -6007,43 +6007,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
         <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W29" t="n">
         <v>2.44</v>
@@ -6061,10 +6061,10 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6073,10 +6073,10 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH29" t="n">
         <v>1000</v>
@@ -6097,68 +6097,68 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.3</v>
+        <v>2.22</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.3</v>
+        <v>2.26</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.3</v>
+        <v>2.52</v>
       </c>
       <c r="AX29" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>2.26</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H30" t="n">
         <v>2.64</v>
       </c>
       <c r="I30" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J30" t="n">
         <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
         <v>1.54</v>
@@ -6213,40 +6213,40 @@
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="V30" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W30" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z30" t="n">
         <v>16.5</v>
@@ -6255,64 +6255,64 @@
         <v>44</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC30" t="n">
         <v>7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE30" t="n">
         <v>38</v>
       </c>
       <c r="AF30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH30" t="n">
         <v>20</v>
       </c>
-      <c r="AG30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>22</v>
-      </c>
       <c r="AI30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL30" t="n">
         <v>60</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>65</v>
-      </c>
       <c r="AM30" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO30" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
         <v>34</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
         <v>11</v>
@@ -6324,35 +6324,35 @@
         <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BB30" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BD30" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="BE30" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BF30" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BG30" t="n">
         <v>30</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.96</v>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H31" t="n">
         <v>2.6</v>
@@ -6401,34 +6401,34 @@
         <v>3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
         <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V31" t="n">
         <v>1.55</v>
@@ -6437,31 +6437,31 @@
         <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
@@ -6470,7 +6470,7 @@
         <v>19.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
         <v>55</v>
@@ -6482,7 +6482,7 @@
         <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AN31" t="n">
         <v>44</v>
@@ -6494,7 +6494,7 @@
         <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR31" t="n">
         <v>14.5</v>
@@ -6503,50 +6503,50 @@
         <v>34</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AX31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BC31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF31" t="n">
         <v>30</v>
       </c>
-      <c r="BD31" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>29</v>
-      </c>
       <c r="BG31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -6577,127 +6577,127 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
         <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="U32" t="n">
         <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
         <v>16</v>
       </c>
       <c r="AE32" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI32" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>75</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>34</v>
-      </c>
       <c r="AK32" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AL32" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO32" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AP32" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR32" t="n">
         <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
@@ -6706,7 +6706,7 @@
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6715,32 +6715,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BB32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BE32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BF32" t="n">
         <v>19</v>
       </c>
       <c r="BG32" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
@@ -6813,10 +6813,10 @@
         <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V33" t="n">
         <v>1.98</v>
@@ -6825,7 +6825,7 @@
         <v>1.27</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y33" t="n">
         <v>7.6</v>
@@ -6861,16 +6861,16 @@
         <v>55</v>
       </c>
       <c r="AJ33" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK33" t="n">
         <v>80</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM33" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="AN33" t="n">
         <v>110</v>
@@ -6903,7 +6903,7 @@
         <v>21</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="AY33" t="n">
         <v>15.5</v>
@@ -6912,29 +6912,29 @@
         <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG33" t="n">
         <v>13.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -6968,37 +6968,37 @@
         <v>2.6</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K34" t="n">
         <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O34" t="n">
         <v>1.4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
@@ -7007,28 +7007,28 @@
         <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U34" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V34" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W34" t="n">
         <v>1.56</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AA34" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
         <v>10.5</v>
@@ -7037,10 +7037,10 @@
         <v>6.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE34" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
@@ -7049,40 +7049,40 @@
         <v>13.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AI34" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AJ34" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK34" t="n">
         <v>40</v>
       </c>
-      <c r="AK34" t="n">
-        <v>32</v>
-      </c>
       <c r="AL34" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AN34" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO34" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
         <v>11</v>
       </c>
       <c r="AR34" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AT34" t="n">
         <v>8.800000000000001</v>
@@ -7091,44 +7091,44 @@
         <v>5.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AX34" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ34" t="n">
         <v>14</v>
       </c>
       <c r="BA34" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD34" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB34" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG34" t="n">
         <v>34</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G35" t="n">
         <v>1.71</v>
@@ -7171,25 +7171,25 @@
         <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>1.29</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
         <v>1.9</v>
@@ -7198,40 +7198,40 @@
         <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
         <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V35" t="n">
         <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB35" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
@@ -7240,13 +7240,13 @@
         <v>10.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH35" t="n">
         <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ35" t="n">
         <v>18.5</v>
@@ -7258,10 +7258,10 @@
         <v>42</v>
       </c>
       <c r="AM35" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
@@ -7270,13 +7270,13 @@
         <v>14</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AR35" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AS35" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT35" t="n">
         <v>7.6</v>
@@ -7285,10 +7285,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV35" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX35" t="n">
         <v>8.800000000000001</v>
@@ -7297,13 +7297,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB35" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC35" t="n">
         <v>15</v>
@@ -7312,17 +7312,17 @@
         <v>26</v>
       </c>
       <c r="BE35" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF35" t="n">
         <v>8.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -7356,19 +7356,19 @@
         <v>4.2</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
         <v>2.02</v>
       </c>
-      <c r="I36" t="n">
-        <v>2.06</v>
-      </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K36" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7386,7 +7386,7 @@
         <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R36" t="n">
         <v>1.36</v>
@@ -7401,22 +7401,22 @@
         <v>2.12</v>
       </c>
       <c r="V36" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X36" t="n">
         <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
         <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB36" t="n">
         <v>15</v>
@@ -7434,7 +7434,7 @@
         <v>30</v>
       </c>
       <c r="AG36" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH36" t="n">
         <v>19</v>
@@ -7458,37 +7458,37 @@
         <v>60</v>
       </c>
       <c r="AO36" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR36" t="n">
         <v>11</v>
       </c>
       <c r="AS36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU36" t="n">
         <v>7.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX36" t="n">
         <v>27</v>
       </c>
       <c r="AY36" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ36" t="n">
         <v>17.5</v>
@@ -7500,23 +7500,23 @@
         <v>70</v>
       </c>
       <c r="BC36" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD36" t="n">
         <v>50</v>
       </c>
       <c r="BE36" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF36" t="n">
         <v>50</v>
       </c>
       <c r="BG36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G37" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="H37" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.34</v>
@@ -7577,7 +7577,7 @@
         <v>1.25</v>
       </c>
       <c r="P37" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q37" t="n">
         <v>1.73</v>
@@ -7601,16 +7601,16 @@
         <v>1.63</v>
       </c>
       <c r="X37" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y37" t="n">
         <v>970</v>
       </c>
       <c r="Z37" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AA37" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB37" t="n">
         <v>970</v>
@@ -7622,52 +7622,52 @@
         <v>970</v>
       </c>
       <c r="AE37" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="n">
         <v>21</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH37" t="n">
         <v>970</v>
       </c>
       <c r="AI37" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK37" t="n">
         <v>48</v>
       </c>
-      <c r="AJ37" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>29</v>
-      </c>
       <c r="AL37" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM37" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO37" t="n">
         <v>32</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AU37" t="n">
         <v>6.4</v>
@@ -7676,41 +7676,41 @@
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BF37" t="n">
         <v>11.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -7768,10 +7768,10 @@
         <v>3.85</v>
       </c>
       <c r="O38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
@@ -7780,13 +7780,13 @@
         <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V38" t="n">
         <v>1.21</v>
@@ -7798,7 +7798,7 @@
         <v>13.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z38" t="n">
         <v>42</v>
@@ -7867,44 +7867,44 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV38" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW38" t="n">
         <v>65</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
         <v>20</v>
       </c>
       <c r="BA38" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB38" t="n">
         <v>16.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD38" t="n">
         <v>32</v>
       </c>
       <c r="BE38" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF38" t="n">
         <v>11</v>
       </c>
       <c r="BG38" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
         <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N39" t="n">
         <v>2.68</v>
@@ -7989,13 +7989,13 @@
         <v>1.72</v>
       </c>
       <c r="X39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
@@ -8010,7 +8010,7 @@
         <v>18.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF39" t="n">
         <v>13.5</v>
@@ -8022,22 +8022,22 @@
         <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
@@ -8049,10 +8049,10 @@
         <v>9.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT39" t="n">
         <v>6.2</v>
@@ -8064,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX39" t="n">
         <v>10.5</v>
@@ -8076,29 +8076,29 @@
         <v>19</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BC39" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.62</v>
       </c>
-      <c r="G40" t="n">
-        <v>1.63</v>
-      </c>
       <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" t="n">
         <v>6.2</v>
       </c>
-      <c r="I40" t="n">
-        <v>6.4</v>
-      </c>
       <c r="J40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.36</v>
@@ -8153,37 +8153,37 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P40" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T40" t="n">
         <v>1.86</v>
       </c>
       <c r="U40" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W40" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X40" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y40" t="n">
         <v>22</v>
@@ -8192,13 +8192,13 @@
         <v>50</v>
       </c>
       <c r="AA40" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD40" t="n">
         <v>22</v>
@@ -8219,25 +8219,25 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK40" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>16</v>
       </c>
       <c r="AL40" t="n">
         <v>32</v>
       </c>
       <c r="AM40" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN40" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO40" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP40" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ40" t="n">
         <v>21</v>
@@ -8246,13 +8246,13 @@
         <v>42</v>
       </c>
       <c r="AS40" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AT40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU40" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV40" t="n">
         <v>21</v>
@@ -8267,16 +8267,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA40" t="n">
         <v>65</v>
       </c>
       <c r="BB40" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC40" t="n">
         <v>14.5</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>15.5</v>
       </c>
       <c r="BD40" t="n">
         <v>29</v>
@@ -8285,14 +8285,14 @@
         <v>90</v>
       </c>
       <c r="BF40" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG40" t="n">
         <v>75</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G41" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I41" t="n">
         <v>4.8</v>
@@ -8341,67 +8341,67 @@
         <v>3.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M41" t="n">
         <v>1.06</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P41" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="U41" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V41" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W41" t="n">
         <v>2.02</v>
       </c>
       <c r="X41" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD41" t="n">
         <v>21</v>
       </c>
-      <c r="Z41" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>22</v>
-      </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF41" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG41" t="n">
         <v>12.5</v>
@@ -8410,7 +8410,7 @@
         <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ41" t="n">
         <v>26</v>
@@ -8422,71 +8422,71 @@
         <v>40</v>
       </c>
       <c r="AM41" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR41" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>4</v>
-      </c>
       <c r="AS41" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT41" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU41" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV41" t="n">
         <v>14</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="AX41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
         <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G42" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H42" t="n">
         <v>4.5</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
         <v>3.6</v>
@@ -8538,22 +8538,22 @@
         <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P42" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="R42" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S42" t="n">
         <v>3.4</v>
@@ -8565,10 +8565,10 @@
         <v>1.89</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8601,7 +8601,7 @@
         <v>10</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
@@ -8619,68 +8619,68 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX42" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY42" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BF42" t="n">
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -8753,10 +8753,10 @@
         <v>4.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U43" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V43" t="n">
         <v>1.48</v>
@@ -8765,40 +8765,40 @@
         <v>1.5</v>
       </c>
       <c r="X43" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AA43" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AB43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF43" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AG43" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AI43" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ43" t="n">
         <v>60</v>
@@ -8810,13 +8810,13 @@
         <v>65</v>
       </c>
       <c r="AM43" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN43" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AO43" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AP43" t="n">
         <v>9.4</v>
@@ -8828,7 +8828,7 @@
         <v>15.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT43" t="n">
         <v>8.199999999999999</v>
@@ -8840,7 +8840,7 @@
         <v>11</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AX43" t="n">
         <v>15.5</v>
@@ -8852,29 +8852,29 @@
         <v>16.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.9</v>
+        <v>44</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -8911,13 +8911,13 @@
         <v>1.91</v>
       </c>
       <c r="H44" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
         <v>3.6</v>
@@ -8974,34 +8974,34 @@
         <v>6.4</v>
       </c>
       <c r="AC44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD44" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AG44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH44" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK44" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM44" t="n">
         <v>1000</v>
@@ -9016,25 +9016,25 @@
         <v>7</v>
       </c>
       <c r="AQ44" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR44" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AV44" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX44" t="n">
         <v>7.8</v>
@@ -9043,32 +9043,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB44" t="n">
         <v>17.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -9102,28 +9102,28 @@
         <v>2.28</v>
       </c>
       <c r="G45" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H45" t="n">
         <v>3.25</v>
       </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J45" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="K45" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="O45" t="n">
         <v>1.43</v>
@@ -9135,7 +9135,7 @@
         <v>2.22</v>
       </c>
       <c r="R45" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S45" t="n">
         <v>3.8</v>
@@ -9144,13 +9144,13 @@
         <v>1.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V45" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W45" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X45" t="n">
         <v>11.5</v>
@@ -9162,7 +9162,7 @@
         <v>29</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB45" t="n">
         <v>10.5</v>
@@ -9174,10 +9174,10 @@
         <v>18.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF45" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG45" t="n">
         <v>14.5</v>
@@ -9186,83 +9186,83 @@
         <v>24</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK45" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL45" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
         <v>60</v>
       </c>
-      <c r="AM45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>32</v>
-      </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY45" t="n">
         <v>10</v>
       </c>
-      <c r="AY45" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AZ45" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="BG45" t="n">
-        <v>4.5</v>
+        <v>40</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G46" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H46" t="n">
         <v>4.1</v>
@@ -9332,7 +9332,7 @@
         <v>1.14</v>
       </c>
       <c r="S46" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T46" t="n">
         <v>2.38</v>
@@ -9347,13 +9347,13 @@
         <v>1.72</v>
       </c>
       <c r="X46" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="AA46" t="n">
         <v>150</v>
@@ -9362,40 +9362,40 @@
         <v>6.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AD46" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="AE46" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF46" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AG46" t="n">
         <v>970</v>
       </c>
       <c r="AH46" t="n">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="AI46" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AJ46" t="n">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="AK46" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="AL46" t="n">
-        <v>95</v>
+        <v>460</v>
       </c>
       <c r="AM46" t="n">
         <v>320</v>
       </c>
       <c r="AN46" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AO46" t="n">
         <v>190</v>
@@ -9404,13 +9404,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ46" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR46" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AT46" t="n">
         <v>5.6</v>
@@ -9419,44 +9419,44 @@
         <v>6</v>
       </c>
       <c r="AV46" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AZ46" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BB46" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF46" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC46" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>8</v>
-      </c>
       <c r="BG46" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -9487,82 +9487,82 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="H47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J47" t="n">
         <v>3</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.76</v>
       </c>
       <c r="K47" t="n">
         <v>3.55</v>
       </c>
       <c r="L47" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M47" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
         <v>1.42</v>
       </c>
       <c r="P47" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R47" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S47" t="n">
         <v>3.85</v>
       </c>
       <c r="T47" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="U47" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W47" t="n">
         <v>1.6</v>
       </c>
       <c r="X47" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y47" t="n">
         <v>970</v>
       </c>
       <c r="Z47" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AA47" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD47" t="n">
         <v>970</v>
       </c>
       <c r="AE47" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AF47" t="n">
         <v>970</v>
@@ -9571,86 +9571,86 @@
         <v>970</v>
       </c>
       <c r="AH47" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI47" t="n">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AJ47" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AM47" t="n">
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AO47" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AT47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA47" t="n">
         <v>3.05</v>
       </c>
-      <c r="AU47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BB47" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BC47" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD47" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="BF47" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G48" t="n">
         <v>1.45</v>
@@ -9690,10 +9690,10 @@
         <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K48" t="n">
         <v>4.7</v>
@@ -9705,10 +9705,10 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O48" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P48" t="n">
         <v>1.65</v>
@@ -9723,13 +9723,13 @@
         <v>4.8</v>
       </c>
       <c r="T48" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="U48" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V48" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W48" t="n">
         <v>3.2</v>
@@ -9753,13 +9753,13 @@
         <v>11</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG48" t="n">
         <v>11.5</v>
@@ -9777,19 +9777,19 @@
         <v>22</v>
       </c>
       <c r="AL48" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM48" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="AN48" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ48" t="n">
         <v>19.5</v>
@@ -9798,16 +9798,16 @@
         <v>50</v>
       </c>
       <c r="AS48" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU48" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV48" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AW48" t="n">
         <v>50</v>
@@ -9822,7 +9822,7 @@
         <v>30</v>
       </c>
       <c r="BA48" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB48" t="n">
         <v>10.5</v>
@@ -9834,7 +9834,7 @@
         <v>48</v>
       </c>
       <c r="BE48" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BF48" t="n">
         <v>9.4</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -9875,100 +9875,100 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G49" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H49" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I49" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L49" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O49" t="n">
         <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R49" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T49" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U49" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V49" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W49" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X49" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z49" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC49" t="n">
         <v>7.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF49" t="n">
         <v>22</v>
       </c>
       <c r="AG49" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH49" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ49" t="n">
         <v>55</v>
       </c>
       <c r="AK49" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL49" t="n">
         <v>55</v>
@@ -9977,49 +9977,49 @@
         <v>130</v>
       </c>
       <c r="AN49" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO49" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP49" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR49" t="n">
         <v>14</v>
       </c>
       <c r="AS49" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AT49" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV49" t="n">
         <v>10</v>
       </c>
       <c r="AW49" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX49" t="n">
         <v>17</v>
       </c>
       <c r="AY49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ49" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BB49" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BC49" t="n">
         <v>30</v>
@@ -10028,7 +10028,7 @@
         <v>42</v>
       </c>
       <c r="BE49" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="BF49" t="n">
         <v>26</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -10072,16 +10072,16 @@
         <v>2.42</v>
       </c>
       <c r="G50" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H50" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I50" t="n">
         <v>3.4</v>
       </c>
       <c r="J50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K50" t="n">
         <v>3.6</v>
@@ -10099,7 +10099,7 @@
         <v>1.38</v>
       </c>
       <c r="P50" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
         <v>2.18</v>
@@ -10108,7 +10108,7 @@
         <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T50" t="n">
         <v>1.83</v>
@@ -10117,10 +10117,10 @@
         <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W50" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X50" t="n">
         <v>14.5</v>
@@ -10141,37 +10141,37 @@
         <v>9</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF50" t="n">
         <v>19.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI50" t="n">
         <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK50" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
@@ -10180,59 +10180,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR50" t="n">
         <v>16</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="AW50" t="n">
-        <v>3.9</v>
+        <v>18</v>
       </c>
       <c r="AX50" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AY50" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ50" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB50" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BC50" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE50" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF50" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BG50" t="n">
         <v>30</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -10263,19 +10263,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G51" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H51" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I51" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="K51" t="n">
         <v>3.55</v>
@@ -10293,10 +10293,10 @@
         <v>1.45</v>
       </c>
       <c r="P51" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R51" t="n">
         <v>1.22</v>
@@ -10311,122 +10311,122 @@
         <v>1.71</v>
       </c>
       <c r="V51" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W51" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="X51" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Y51" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z51" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AA51" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB51" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AC51" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD51" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AE51" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AF51" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AG51" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AH51" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AJ51" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AL51" t="n">
-        <v>65</v>
+        <v>450</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN51" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AO51" t="n">
         <v>95</v>
       </c>
       <c r="AP51" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AQ51" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="AU51" t="n">
         <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AX51" t="n">
         <v>10</v>
       </c>
       <c r="AY51" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="AZ51" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB51" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC51" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD51" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF51" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -10460,10 +10460,10 @@
         <v>2.12</v>
       </c>
       <c r="G52" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H52" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I52" t="n">
         <v>4.3</v>
@@ -10475,7 +10475,7 @@
         <v>3.65</v>
       </c>
       <c r="L52" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10490,31 +10490,31 @@
         <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R52" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
         <v>1.86</v>
       </c>
       <c r="U52" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V52" t="n">
         <v>1.3</v>
       </c>
       <c r="W52" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z52" t="n">
         <v>1000</v>
@@ -10523,10 +10523,10 @@
         <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD52" t="n">
         <v>1000</v>
@@ -10547,7 +10547,7 @@
         <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK52" t="n">
         <v>1000</v>
@@ -10565,62 +10565,62 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS52" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT52" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT52" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AU52" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AV52" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX52" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY52" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ52" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB52" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC52" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF52" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G53" t="n">
         <v>1.69</v>
@@ -10675,7 +10675,7 @@
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.28</v>
@@ -10693,16 +10693,16 @@
         <v>3.1</v>
       </c>
       <c r="T53" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U53" t="n">
         <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W53" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X53" t="n">
         <v>19.5</v>
@@ -10729,7 +10729,7 @@
         <v>100</v>
       </c>
       <c r="AF53" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG53" t="n">
         <v>11.5</v>
@@ -10738,25 +10738,25 @@
         <v>25</v>
       </c>
       <c r="AI53" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AJ53" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AK53" t="n">
         <v>17.5</v>
       </c>
       <c r="AL53" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN53" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO53" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AP53" t="n">
         <v>14.5</v>
@@ -10768,7 +10768,7 @@
         <v>34</v>
       </c>
       <c r="AS53" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT53" t="n">
         <v>7.8</v>
@@ -10780,7 +10780,7 @@
         <v>20</v>
       </c>
       <c r="AW53" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX53" t="n">
         <v>9</v>
@@ -10789,10 +10789,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ53" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BA53" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB53" t="n">
         <v>14</v>
@@ -10801,20 +10801,20 @@
         <v>15</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BE53" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF53" t="n">
         <v>8</v>
       </c>
       <c r="BG53" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
         <v>2.76</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H54" t="n">
         <v>2.88</v>
@@ -10893,10 +10893,10 @@
         <v>1.76</v>
       </c>
       <c r="V54" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W54" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X54" t="n">
         <v>9.6</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
         <v>27</v>
       </c>
       <c r="AK55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL55" t="n">
         <v>75</v>
@@ -11153,7 +11153,7 @@
         <v>12</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS55" t="n">
         <v>5.2</v>
@@ -11180,7 +11180,7 @@
         <v>4.6</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB55" t="n">
         <v>19</v>
@@ -11189,7 +11189,7 @@
         <v>4.6</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE55" t="n">
         <v>5.2</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -766,7 +766,7 @@
         <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -787,13 +787,13 @@
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
         <v>1.93</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
         <v>3.35</v>
@@ -817,10 +817,10 @@
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
         <v>12.5</v>
@@ -847,22 +847,22 @@
         <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -871,10 +871,10 @@
         <v>9.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -883,44 +883,44 @@
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF2" t="n">
         <v>7.4</v>
       </c>
-      <c r="BD2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7</v>
-      </c>
       <c r="BG2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G3" t="n">
         <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I3" t="n">
         <v>3.05</v>
@@ -966,37 +966,37 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.48</v>
@@ -1026,10 +1026,10 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1038,16 +1038,16 @@
         <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1065,56 +1065,56 @@
         <v>5.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1172,13 +1172,13 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
@@ -1187,16 +1187,16 @@
         <v>2.64</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
         <v>85</v>
@@ -1223,7 +1223,7 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1235,7 +1235,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
@@ -1247,7 +1247,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1259,10 +1259,10 @@
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
         <v>7.4</v>
@@ -1274,10 +1274,10 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
         <v>8.6</v>
@@ -1289,7 +1289,7 @@
         <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
@@ -1298,17 +1298,17 @@
         <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
         <v>7.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1351,10 +1351,10 @@
         <v>1.13</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
         <v>1.18</v>
@@ -1369,7 +1369,7 @@
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1.33</v>
@@ -1378,10 +1378,10 @@
         <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="T5" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
         <v>1.52</v>
@@ -1399,10 +1399,10 @@
         <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
@@ -1444,34 +1444,34 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS5" t="n">
         <v>3.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
         <v>5.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
         <v>6.2</v>
@@ -1480,29 +1480,29 @@
         <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1566,28 +1566,28 @@
         <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AU6" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY6" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
         <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
         <v>3.2</v>
@@ -1742,7 +1742,7 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.34</v>
@@ -1751,7 +1751,7 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
@@ -1763,31 +1763,31 @@
         <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -1796,101 +1796,101 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>150</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>26</v>
+        <v>6.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>770</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
@@ -1945,16 +1945,16 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1963,10 +1963,10 @@
         <v>1.16</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2118,34 +2118,34 @@
         <v>7.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="H9" t="n">
         <v>1.43</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="n">
         <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
         <v>1.61</v>
@@ -2154,70 +2154,70 @@
         <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
         <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC9" t="n">
         <v>12</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE9" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AF9" t="n">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="AG9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AH9" t="n">
         <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
         <v>280</v>
       </c>
       <c r="AK9" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="AL9" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AN9" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AO9" t="n">
         <v>6</v>
@@ -2226,7 +2226,7 @@
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
         <v>8.4</v>
@@ -2244,10 +2244,10 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9" t="n">
         <v>15.5</v>
@@ -2256,29 +2256,29 @@
         <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2309,28 +2309,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
         <v>3.7</v>
@@ -2345,13 +2345,13 @@
         <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
         <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
         <v>1.93</v>
@@ -2360,25 +2360,25 @@
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
         <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD10" t="n">
         <v>26</v>
@@ -2390,7 +2390,7 @@
         <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2399,10 +2399,10 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>85</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
         <v>1.75</v>
@@ -2521,34 +2521,34 @@
         <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
         <v>1.16</v>
@@ -2557,116 +2557,116 @@
         <v>2.34</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
+        <v>130</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>21</v>
-      </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="BF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG11" t="n">
         <v>13</v>
       </c>
-      <c r="BG11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="G12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.41</v>
@@ -2721,16 +2721,16 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
         <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -2739,34 +2739,34 @@
         <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X12" t="n">
         <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>36</v>
@@ -2814,7 +2814,7 @@
         <v>5.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
         <v>7.6</v>
@@ -2826,41 +2826,41 @@
         <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="BC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.2</v>
       </c>
-      <c r="BD12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -2915,31 +2915,31 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.74</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.72</v>
-      </c>
       <c r="U13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
         <v>2.2</v>
@@ -2951,110 +2951,110 @@
         <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK13" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>19</v>
       </c>
       <c r="AL13" t="n">
         <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN13" t="n">
         <v>10.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
         <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
         <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
       </c>
       <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK14" t="n">
         <v>23</v>
       </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>24</v>
-      </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>1.18</v>
       </c>
       <c r="G15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.32</v>
@@ -3303,7 +3303,7 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.23</v>
@@ -3312,31 +3312,31 @@
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
         <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="T15" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,13 +3345,13 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
@@ -3387,7 +3387,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.2</v>
@@ -3402,7 +3402,7 @@
         <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV15" t="n">
         <v>4.2</v>
@@ -3411,38 +3411,38 @@
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.52</v>
+        <v>1.82</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3503,43 +3503,43 @@
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
         <v>1.96</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AC16" t="n">
         <v>9.800000000000001</v>
@@ -3548,13 +3548,13 @@
         <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH16" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
         <v>400</v>
       </c>
       <c r="AL16" t="n">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
@@ -3581,62 +3581,62 @@
         <v>10.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I17" t="n">
         <v>3.35</v>
@@ -3691,25 +3691,25 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
         <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
         <v>2.6</v>
@@ -3718,25 +3718,25 @@
         <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="AB17" t="n">
         <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
         <v>15</v>
@@ -3745,7 +3745,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3754,28 +3754,28 @@
         <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AL17" t="n">
         <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3784,13 +3784,13 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AT17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
@@ -3802,7 +3802,7 @@
         <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3823,14 +3823,14 @@
         <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.3</v>
@@ -3891,13 +3891,13 @@
         <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -3906,10 +3906,10 @@
         <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
         <v>2.22</v>
@@ -3921,28 +3921,28 @@
         <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
         <v>21</v>
@@ -3951,46 +3951,46 @@
         <v>190</v>
       </c>
       <c r="AJ18" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO18" t="n">
         <v>150</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>16.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>7.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
         <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX18" t="n">
         <v>9.199999999999999</v>
@@ -4002,7 +4002,7 @@
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
@@ -4014,17 +4014,17 @@
         <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
         <v>3.55</v>
@@ -4073,7 +4073,7 @@
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4091,31 +4091,31 @@
         <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
         <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
         <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="n">
         <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -4130,10 +4130,10 @@
         <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
@@ -4142,7 +4142,7 @@
         <v>17.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="n">
         <v>90</v>
@@ -4163,7 +4163,7 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
@@ -4172,7 +4172,7 @@
         <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -4211,14 +4211,14 @@
         <v>22</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J20" t="n">
         <v>2.96</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.64</v>
@@ -4282,7 +4282,7 @@
         <v>1.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.17</v>
@@ -4297,13 +4297,13 @@
         <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y20" t="n">
         <v>8</v>
@@ -4315,7 +4315,7 @@
         <v>420</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>7</v>
@@ -4330,34 +4330,34 @@
         <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI20" t="n">
         <v>460</v>
       </c>
       <c r="AJ20" t="n">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="AK20" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AL20" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AP20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.4</v>
@@ -4366,7 +4366,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -4375,16 +4375,16 @@
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>17.5</v>
@@ -4393,7 +4393,7 @@
         <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BC20" t="n">
         <v>36</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I21" t="n">
         <v>2.82</v>
@@ -4458,25 +4458,25 @@
         <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="L21" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="O21" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>1.15</v>
       </c>
       <c r="R21" t="n">
         <v>1.11</v>
@@ -4485,7 +4485,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
         <v>1.57</v>
@@ -4494,49 +4494,49 @@
         <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG21" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AI21" t="n">
         <v>540</v>
       </c>
       <c r="AJ21" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL21" t="n">
         <v>540</v>
@@ -4548,65 +4548,65 @@
         <v>500</v>
       </c>
       <c r="AO21" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.7</v>
+        <v>1.32</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>1.33</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.8</v>
+        <v>1.33</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>1.31</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="AX21" t="n">
-        <v>19.5</v>
+        <v>1.33</v>
       </c>
       <c r="AY21" t="n">
-        <v>16</v>
+        <v>1.31</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>1.33</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>1.35</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="BG21" t="n">
-        <v>55</v>
+        <v>1.55</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G22" t="n">
         <v>2.68</v>
       </c>
       <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4679,58 +4679,58 @@
         <v>4.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.59</v>
       </c>
       <c r="X22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
         <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF22" t="n">
         <v>38</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR22" t="n">
         <v>9</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
         <v>7.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC22" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BD22" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -4855,7 +4855,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
         <v>1.35</v>
@@ -4870,7 +4870,7 @@
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
         <v>1.83</v>
@@ -4882,7 +4882,7 @@
         <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -4894,7 +4894,7 @@
         <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
         <v>9.800000000000001</v>
@@ -4903,22 +4903,22 @@
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -4936,10 +4936,10 @@
         <v>17</v>
       </c>
       <c r="AO23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4954,13 +4954,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,29 +4972,29 @@
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BE23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG23" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G24" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
@@ -5040,7 +5040,7 @@
         <v>4.5</v>
       </c>
       <c r="K24" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
         <v>1.17</v>
@@ -5049,22 +5049,22 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>1.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
         <v>1.32</v>
       </c>
       <c r="R24" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S24" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="T24" t="n">
         <v>1.42</v>
@@ -5073,19 +5073,19 @@
         <v>3.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
         <v>2.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Y24" t="n">
         <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
         <v>160</v>
@@ -5103,7 +5103,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
@@ -5112,83 +5112,83 @@
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK24" t="n">
         <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX24" t="n">
         <v>17</v>
       </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW24" t="n">
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA24" t="n">
         <v>8</v>
       </c>
-      <c r="AX24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BB24" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BC24" t="n">
         <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
         <v>19</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.17</v>
@@ -5243,7 +5243,7 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
@@ -5252,16 +5252,16 @@
         <v>3.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="T25" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U25" t="n">
         <v>2.8</v>
@@ -5282,10 +5282,10 @@
         <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AB25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
         <v>1000</v>
@@ -5297,10 +5297,10 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5321,55 +5321,55 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY25" t="n">
         <v>5.8</v>
       </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AZ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA25" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="BB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC25" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
         <v>14</v>
@@ -5378,11 +5378,11 @@
         <v>4.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>4.1</v>
       </c>
       <c r="G26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I26" t="n">
         <v>1.89</v>
@@ -5449,10 +5449,10 @@
         <v>1.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
         <v>1.54</v>
@@ -5470,7 +5470,7 @@
         <v>29</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Z26" t="n">
         <v>15.5</v>
@@ -5479,22 +5479,22 @@
         <v>22</v>
       </c>
       <c r="AB26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC26" t="n">
         <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
         <v>40</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH26" t="n">
         <v>16.5</v>
@@ -5503,13 +5503,13 @@
         <v>27</v>
       </c>
       <c r="AJ26" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK26" t="n">
         <v>46</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM26" t="n">
         <v>200</v>
@@ -5533,7 +5533,7 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
         <v>9.4</v>
@@ -5548,7 +5548,7 @@
         <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
@@ -5557,7 +5557,7 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5569,14 +5569,14 @@
         <v>23</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG26" t="n">
         <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G27" t="n">
         <v>2.16</v>
@@ -5619,7 +5619,7 @@
         <v>5.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
         <v>3.45</v>
@@ -5628,7 +5628,7 @@
         <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
         <v>2.46</v>
@@ -5640,7 +5640,7 @@
         <v>1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R27" t="n">
         <v>1.17</v>
@@ -5670,10 +5670,10 @@
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5718,13 +5718,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27" t="n">
         <v>5.5</v>
@@ -5736,7 +5736,7 @@
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5748,29 +5748,29 @@
         <v>22</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB27" t="n">
         <v>22</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G28" t="n">
         <v>2.1</v>
@@ -5810,7 +5810,7 @@
         <v>3.45</v>
       </c>
       <c r="I28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>4.1</v>
@@ -5834,13 +5834,13 @@
         <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
         <v>1.58</v>
@@ -5849,46 +5849,46 @@
         <v>2.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
         <v>1.91</v>
       </c>
       <c r="X28" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Y28" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
         <v>100</v>
       </c>
       <c r="AA28" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AB28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AE28" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG28" t="n">
         <v>16</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
         <v>85</v>
@@ -5897,7 +5897,7 @@
         <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -5906,10 +5906,10 @@
         <v>9.4</v>
       </c>
       <c r="AO28" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
         <v>11.5</v>
@@ -5918,53 +5918,53 @@
         <v>16</v>
       </c>
       <c r="AS28" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA28" t="n">
         <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC28" t="n">
         <v>9</v>
       </c>
       <c r="BD28" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BE28" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BF28" t="n">
         <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.85</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6022,7 +6022,7 @@
         <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
         <v>1.71</v>
@@ -6034,10 +6034,10 @@
         <v>1.26</v>
       </c>
       <c r="S29" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
         <v>1.76</v>
@@ -6073,7 +6073,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="AG29" t="n">
         <v>36</v>
@@ -6085,7 +6085,7 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="AX29" t="n">
         <v>4.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.4</v>
+        <v>1.83</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H30" t="n">
         <v>2.64</v>
       </c>
       <c r="I30" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J30" t="n">
         <v>3.25</v>
@@ -6207,25 +6207,25 @@
         <v>3.35</v>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
         <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
         <v>4.7</v>
@@ -6237,10 +6237,10 @@
         <v>1.93</v>
       </c>
       <c r="V30" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X30" t="n">
         <v>10.5</v>
@@ -6249,28 +6249,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z30" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC30" t="n">
         <v>7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>20</v>
@@ -6282,7 +6282,7 @@
         <v>55</v>
       </c>
       <c r="AK30" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL30" t="n">
         <v>60</v>
@@ -6291,22 +6291,22 @@
         <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
         <v>8.800000000000001</v>
@@ -6315,44 +6315,44 @@
         <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="BB30" t="n">
         <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BD30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BE30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BF30" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="BG30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H31" t="n">
         <v>2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J31" t="n">
         <v>3.25</v>
@@ -6401,7 +6401,7 @@
         <v>3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
@@ -6413,31 +6413,31 @@
         <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q31" t="n">
         <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U31" t="n">
         <v>1.99</v>
       </c>
       <c r="V31" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W31" t="n">
         <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y31" t="n">
         <v>10</v>
@@ -6467,7 +6467,7 @@
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
         <v>55</v>
@@ -6476,34 +6476,34 @@
         <v>55</v>
       </c>
       <c r="AK31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP31" t="n">
         <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR31" t="n">
         <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
         <v>6.8</v>
@@ -6521,7 +6521,7 @@
         <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
         <v>36</v>
@@ -6536,17 +6536,17 @@
         <v>23</v>
       </c>
       <c r="BE31" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6592,19 +6592,19 @@
         <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
         <v>1.71</v>
@@ -6613,22 +6613,22 @@
         <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.95</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
         <v>11.5</v>
@@ -6637,13 +6637,13 @@
         <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC32" t="n">
         <v>7.6</v>
@@ -6652,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="AE32" t="n">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
@@ -6661,16 +6661,16 @@
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI32" t="n">
         <v>370</v>
       </c>
       <c r="AJ32" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AK32" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AL32" t="n">
         <v>290</v>
@@ -6685,7 +6685,7 @@
         <v>160</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>11</v>
@@ -6694,19 +6694,19 @@
         <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT32" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6715,32 +6715,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BB32" t="n">
         <v>24</v>
       </c>
       <c r="BC32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE32" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG32" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6783,13 +6783,13 @@
         <v>2.02</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
@@ -6804,16 +6804,16 @@
         <v>1.73</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
         <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
         <v>1.9</v>
@@ -6825,28 +6825,28 @@
         <v>1.27</v>
       </c>
       <c r="X33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y33" t="n">
         <v>7.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AB33" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF33" t="n">
         <v>32</v>
@@ -6855,28 +6855,28 @@
         <v>18</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI33" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ33" t="n">
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="AL33" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AP33" t="n">
         <v>10.5</v>
@@ -6903,38 +6903,38 @@
         <v>21</v>
       </c>
       <c r="AX33" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AY33" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BC33" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BD33" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>2.78</v>
       </c>
       <c r="H34" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I34" t="n">
         <v>3.5</v>
@@ -6983,28 +6983,28 @@
         <v>3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q34" t="n">
         <v>2.32</v>
       </c>
       <c r="R34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
         <v>1.84</v>
@@ -7022,10 +7022,10 @@
         <v>10</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA34" t="n">
         <v>900</v>
@@ -7043,10 +7043,10 @@
         <v>190</v>
       </c>
       <c r="AF34" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AG34" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AH34" t="n">
         <v>46</v>
@@ -7058,7 +7058,7 @@
         <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AL34" t="n">
         <v>290</v>
@@ -7067,34 +7067,34 @@
         <v>450</v>
       </c>
       <c r="AN34" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AO34" t="n">
         <v>90</v>
       </c>
       <c r="AP34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS34" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>23</v>
-      </c>
       <c r="AT34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV34" t="n">
         <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
@@ -7103,32 +7103,32 @@
         <v>11</v>
       </c>
       <c r="AZ34" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB34" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BC34" t="n">
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE34" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE34" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF34" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G35" t="n">
         <v>1.71</v>
       </c>
       <c r="H35" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I35" t="n">
         <v>6.6</v>
@@ -7183,25 +7183,25 @@
         <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O35" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R35" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
         <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U35" t="n">
         <v>1.99</v>
@@ -7213,7 +7213,7 @@
         <v>2.4</v>
       </c>
       <c r="X35" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Y35" t="n">
         <v>40</v>
@@ -7222,16 +7222,16 @@
         <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
@@ -7243,86 +7243,86 @@
         <v>10</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI35" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ35" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AK35" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AL35" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM35" t="n">
         <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV35" t="n">
         <v>18.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX35" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ35" t="n">
         <v>18</v>
       </c>
       <c r="BA35" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BB35" t="n">
         <v>14</v>
       </c>
       <c r="BC35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>26</v>
+        <v>9.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BF35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7371,34 +7371,34 @@
         <v>3.75</v>
       </c>
       <c r="L36" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T36" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U36" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V36" t="n">
         <v>1.98</v>
@@ -7407,22 +7407,22 @@
         <v>1.29</v>
       </c>
       <c r="X36" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA36" t="n">
         <v>23</v>
       </c>
       <c r="AB36" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
         <v>10.5</v>
@@ -7443,22 +7443,22 @@
         <v>38</v>
       </c>
       <c r="AJ36" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK36" t="n">
         <v>55</v>
       </c>
       <c r="AL36" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM36" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>60</v>
       </c>
       <c r="AO36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP36" t="n">
         <v>12.5</v>
@@ -7470,19 +7470,19 @@
         <v>11</v>
       </c>
       <c r="AS36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU36" t="n">
         <v>7.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX36" t="n">
         <v>27</v>
@@ -7491,32 +7491,32 @@
         <v>15.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA36" t="n">
         <v>34</v>
       </c>
       <c r="BB36" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BC36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE36" t="n">
         <v>65</v>
       </c>
       <c r="BF36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BG36" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7547,170 +7547,170 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G37" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H37" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K37" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L37" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M37" t="n">
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P37" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S37" t="n">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="T37" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U37" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X37" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y37" t="n">
         <v>970</v>
       </c>
       <c r="Z37" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AA37" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB37" t="n">
         <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AD37" t="n">
         <v>970</v>
       </c>
       <c r="AE37" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AH37" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AI37" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ37" t="n">
         <v>900</v>
       </c>
       <c r="AK37" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AL37" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM37" t="n">
         <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AO37" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AQ37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW37" t="n">
         <v>4</v>
       </c>
-      <c r="AR37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU37" t="n">
+      <c r="AX37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC37" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD37" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7747,16 +7747,16 @@
         <v>1.77</v>
       </c>
       <c r="H38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I38" t="n">
         <v>5.6</v>
       </c>
-      <c r="I38" t="n">
-        <v>5.7</v>
-      </c>
       <c r="J38" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
         <v>1.42</v>
@@ -7786,7 +7786,7 @@
         <v>1.94</v>
       </c>
       <c r="U38" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>1.21</v>
@@ -7795,7 +7795,7 @@
         <v>2.28</v>
       </c>
       <c r="X38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y38" t="n">
         <v>18</v>
@@ -7840,13 +7840,13 @@
         <v>38</v>
       </c>
       <c r="AM38" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN38" t="n">
         <v>11.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP38" t="n">
         <v>13</v>
@@ -7855,7 +7855,7 @@
         <v>17</v>
       </c>
       <c r="AR38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS38" t="n">
         <v>42</v>
@@ -7864,25 +7864,25 @@
         <v>7.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV38" t="n">
         <v>19.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY38" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BB38" t="n">
         <v>16.5</v>
@@ -7900,11 +7900,11 @@
         <v>11</v>
       </c>
       <c r="BG38" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G39" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H39" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I39" t="n">
         <v>4.3</v>
@@ -7950,13 +7950,13 @@
         <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L39" t="n">
         <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
         <v>2.68</v>
@@ -7980,13 +7980,13 @@
         <v>2.06</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W39" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X39" t="n">
         <v>9.4</v>
@@ -7998,10 +7998,10 @@
         <v>48</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC39" t="n">
         <v>7.6</v>
@@ -8010,19 +8010,19 @@
         <v>18.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AF39" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG39" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH39" t="n">
         <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
         <v>75</v>
@@ -8037,7 +8037,7 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
@@ -8046,37 +8046,37 @@
         <v>8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR39" t="n">
         <v>11.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU39" t="n">
         <v>6.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ39" t="n">
         <v>19</v>
       </c>
       <c r="BA39" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BB39" t="n">
         <v>13</v>
@@ -8085,20 +8085,20 @@
         <v>14.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -8135,10 +8135,10 @@
         <v>1.62</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
         <v>4.5</v>
@@ -8153,7 +8153,7 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.25</v>
@@ -8171,13 +8171,13 @@
         <v>2.94</v>
       </c>
       <c r="T40" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U40" t="n">
         <v>2.12</v>
       </c>
       <c r="V40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W40" t="n">
         <v>2.6</v>
@@ -8201,7 +8201,7 @@
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE40" t="n">
         <v>80</v>
@@ -8219,13 +8219,13 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK40" t="n">
         <v>15.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM40" t="n">
         <v>95</v>
@@ -8285,14 +8285,14 @@
         <v>90</v>
       </c>
       <c r="BF40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG40" t="n">
         <v>75</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -8323,46 +8323,46 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G41" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H41" t="n">
         <v>4.3</v>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K41" t="n">
         <v>3.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M41" t="n">
         <v>1.06</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O41" t="n">
         <v>1.31</v>
       </c>
       <c r="P41" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
         <v>1.91</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
         <v>1.83</v>
@@ -8374,52 +8374,52 @@
         <v>1.27</v>
       </c>
       <c r="W41" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X41" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z41" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC41" t="n">
         <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
+        <v>320</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>65</v>
       </c>
-      <c r="AF41" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>26</v>
-      </c>
       <c r="AK41" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AL41" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM41" t="n">
         <v>580</v>
@@ -8428,10 +8428,10 @@
         <v>14</v>
       </c>
       <c r="AO41" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ41" t="n">
         <v>13.5</v>
@@ -8440,7 +8440,7 @@
         <v>14.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AT41" t="n">
         <v>8</v>
@@ -8449,10 +8449,10 @@
         <v>7.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW41" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AX41" t="n">
         <v>10</v>
@@ -8461,32 +8461,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BB41" t="n">
         <v>10.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BD41" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BF41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -8520,16 +8520,16 @@
         <v>1.82</v>
       </c>
       <c r="G42" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H42" t="n">
         <v>4.5</v>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K42" t="n">
         <v>4.1</v>
@@ -8544,34 +8544,34 @@
         <v>3.7</v>
       </c>
       <c r="O42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P42" t="n">
         <v>1.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="R42" t="n">
         <v>1.35</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T42" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="V42" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W42" t="n">
         <v>2.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y42" t="n">
         <v>1000</v>
@@ -8583,10 +8583,10 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
@@ -8601,7 +8601,7 @@
         <v>10</v>
       </c>
       <c r="AH42" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT42" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AU42" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AV42" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="BB42" t="n">
         <v>6.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.1</v>
+        <v>2.54</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="BF42" t="n">
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.3</v>
+        <v>2.64</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G43" t="n">
         <v>3</v>
@@ -8723,10 +8723,10 @@
         <v>3.05</v>
       </c>
       <c r="J43" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K43" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
@@ -8741,10 +8741,10 @@
         <v>1.46</v>
       </c>
       <c r="P43" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -8756,7 +8756,7 @@
         <v>1.87</v>
       </c>
       <c r="U43" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V43" t="n">
         <v>1.48</v>
@@ -8771,10 +8771,10 @@
         <v>10.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>44</v>
+        <v>19.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>120</v>
+        <v>340</v>
       </c>
       <c r="AB43" t="n">
         <v>10</v>
@@ -8786,7 +8786,7 @@
         <v>13.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AF43" t="n">
         <v>32</v>
@@ -8798,16 +8798,16 @@
         <v>46</v>
       </c>
       <c r="AI43" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AJ43" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AK43" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AL43" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AM43" t="n">
         <v>580</v>
@@ -8822,13 +8822,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR43" t="n">
         <v>15.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT43" t="n">
         <v>8.199999999999999</v>
@@ -8840,7 +8840,7 @@
         <v>11</v>
       </c>
       <c r="AW43" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AX43" t="n">
         <v>15.5</v>
@@ -8849,22 +8849,22 @@
         <v>11</v>
       </c>
       <c r="AZ43" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="BB43" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC43" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BD43" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE43" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF43" t="n">
         <v>7.2</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.75</v>
       </c>
       <c r="G44" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H44" t="n">
         <v>5.8</v>
@@ -8935,43 +8935,43 @@
         <v>1.57</v>
       </c>
       <c r="P44" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q44" t="n">
         <v>2.72</v>
       </c>
       <c r="R44" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S44" t="n">
         <v>5.4</v>
       </c>
       <c r="T44" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V44" t="n">
         <v>1.16</v>
       </c>
       <c r="W44" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X44" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA44" t="n">
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AC44" t="n">
         <v>8.4</v>
@@ -8983,7 +8983,7 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG44" t="n">
         <v>12</v>
@@ -9001,13 +9001,13 @@
         <v>65</v>
       </c>
       <c r="AL44" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
@@ -9016,25 +9016,25 @@
         <v>7</v>
       </c>
       <c r="AQ44" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AR44" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AS44" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT44" t="n">
         <v>5</v>
       </c>
       <c r="AU44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX44" t="n">
         <v>7.8</v>
@@ -9043,32 +9043,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB44" t="n">
         <v>17.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD44" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>2.28</v>
       </c>
       <c r="G45" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H45" t="n">
         <v>3.25</v>
       </c>
       <c r="I45" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>3.05</v>
@@ -9117,7 +9117,7 @@
         <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -9126,7 +9126,7 @@
         <v>2.92</v>
       </c>
       <c r="O45" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P45" t="n">
         <v>1.65</v>
@@ -9138,7 +9138,7 @@
         <v>1.24</v>
       </c>
       <c r="S45" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T45" t="n">
         <v>1.9</v>
@@ -9150,28 +9150,28 @@
         <v>1.35</v>
       </c>
       <c r="W45" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X45" t="n">
         <v>11.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z45" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA45" t="n">
         <v>160</v>
       </c>
       <c r="AB45" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE45" t="n">
         <v>130</v>
@@ -9180,16 +9180,16 @@
         <v>15.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI45" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AJ45" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK45" t="n">
         <v>75</v>
@@ -9201,7 +9201,7 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT45" t="n">
         <v>7.2</v>
@@ -9228,7 +9228,7 @@
         <v>12.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX45" t="n">
         <v>12.5</v>
@@ -9240,7 +9240,7 @@
         <v>16.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BB45" t="n">
         <v>13</v>
@@ -9249,20 +9249,20 @@
         <v>14.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BF45" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BG45" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -9296,16 +9296,16 @@
         <v>2.24</v>
       </c>
       <c r="G46" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H46" t="n">
         <v>4.1</v>
       </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K46" t="n">
         <v>3.05</v>
@@ -9314,49 +9314,49 @@
         <v>1.68</v>
       </c>
       <c r="M46" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N46" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O46" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P46" t="n">
         <v>1.41</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
         <v>1.14</v>
       </c>
       <c r="S46" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T46" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U46" t="n">
         <v>1.63</v>
       </c>
       <c r="V46" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W46" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X46" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y46" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z46" t="n">
         <v>120</v>
       </c>
       <c r="AA46" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="AB46" t="n">
         <v>6.4</v>
@@ -9365,7 +9365,7 @@
         <v>12</v>
       </c>
       <c r="AD46" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AE46" t="n">
         <v>240</v>
@@ -9392,71 +9392,71 @@
         <v>460</v>
       </c>
       <c r="AM46" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AN46" t="n">
         <v>110</v>
       </c>
       <c r="AO46" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP46" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AR46" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS46" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AT46" t="n">
         <v>5.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV46" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AW46" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX46" t="n">
         <v>10.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ46" t="n">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB46" t="n">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="BC46" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BD46" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF46" t="n">
         <v>7.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G47" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H47" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -9520,7 +9520,7 @@
         <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R47" t="n">
         <v>1.24</v>
@@ -9532,7 +9532,7 @@
         <v>1.9</v>
       </c>
       <c r="U47" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V47" t="n">
         <v>1.36</v>
@@ -9544,55 +9544,55 @@
         <v>90</v>
       </c>
       <c r="Y47" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z47" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA47" t="n">
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="AC47" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD47" t="n">
         <v>970</v>
       </c>
       <c r="AE47" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AF47" t="n">
         <v>970</v>
       </c>
       <c r="AG47" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH47" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI47" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK47" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL47" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM47" t="n">
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO47" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP47" t="n">
         <v>5.6</v>
@@ -9601,10 +9601,10 @@
         <v>6.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS47" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="AT47" t="n">
         <v>4.9</v>
@@ -9613,10 +9613,10 @@
         <v>4.9</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX47" t="n">
         <v>6.2</v>
@@ -9625,32 +9625,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ47" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA47" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BB47" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
       <c r="BF47" t="n">
         <v>5.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -9708,13 +9708,13 @@
         <v>2.92</v>
       </c>
       <c r="O48" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P48" t="n">
         <v>1.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R48" t="n">
         <v>1.24</v>
@@ -9723,7 +9723,7 @@
         <v>4.8</v>
       </c>
       <c r="T48" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="U48" t="n">
         <v>1.53</v>
@@ -9747,16 +9747,16 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AC48" t="n">
         <v>11</v>
       </c>
       <c r="AD48" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AE48" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF48" t="n">
         <v>6.6</v>
@@ -9765,34 +9765,34 @@
         <v>11.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="n">
         <v>330</v>
       </c>
       <c r="AJ48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK48" t="n">
         <v>22</v>
       </c>
       <c r="AL48" t="n">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="AM48" t="n">
         <v>500</v>
       </c>
       <c r="AN48" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ48" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR48" t="n">
         <v>50</v>
@@ -9813,7 +9813,7 @@
         <v>50</v>
       </c>
       <c r="AX48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY48" t="n">
         <v>10</v>
@@ -9825,7 +9825,7 @@
         <v>50</v>
       </c>
       <c r="BB48" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC48" t="n">
         <v>18</v>
@@ -9834,17 +9834,17 @@
         <v>48</v>
       </c>
       <c r="BE48" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF48" t="n">
         <v>9.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -9881,19 +9881,19 @@
         <v>3.2</v>
       </c>
       <c r="H49" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J49" t="n">
         <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L49" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -9902,7 +9902,7 @@
         <v>3.35</v>
       </c>
       <c r="O49" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P49" t="n">
         <v>1.83</v>
@@ -9917,34 +9917,34 @@
         <v>3.95</v>
       </c>
       <c r="T49" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U49" t="n">
         <v>2.08</v>
       </c>
       <c r="V49" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W49" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X49" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB49" t="n">
         <v>12</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD49" t="n">
         <v>12.5</v>
@@ -9953,7 +9953,7 @@
         <v>32</v>
       </c>
       <c r="AF49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG49" t="n">
         <v>14</v>
@@ -9974,71 +9974,71 @@
         <v>55</v>
       </c>
       <c r="AM49" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO49" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP49" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR49" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS49" t="n">
         <v>32</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW49" t="n">
         <v>14.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ49" t="n">
         <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BB49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC49" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BD49" t="n">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE49" t="n">
         <v>30</v>
       </c>
       <c r="BF49" t="n">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -10069,170 +10069,170 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H50" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N50" t="n">
         <v>3.1</v>
       </c>
-      <c r="I50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O50" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R50" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S50" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U50" t="n">
         <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W50" t="n">
         <v>1.58</v>
       </c>
       <c r="X50" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Y50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC50" t="n">
         <v>14</v>
       </c>
-      <c r="Z50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9</v>
-      </c>
       <c r="AD50" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AI50" t="n">
         <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AK50" t="n">
         <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AQ50" t="n">
         <v>6.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="AT50" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AU50" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AV50" t="n">
         <v>8.4</v>
       </c>
       <c r="AW50" t="n">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="AX50" t="n">
         <v>7.6</v>
       </c>
       <c r="AY50" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AZ50" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="BA50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB50" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB50" t="n">
-        <v>4</v>
-      </c>
       <c r="BC50" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF50" t="n">
         <v>5</v>
       </c>
       <c r="BG50" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.22</v>
       </c>
       <c r="G51" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="H51" t="n">
         <v>3.6</v>
@@ -10275,28 +10275,28 @@
         <v>4.2</v>
       </c>
       <c r="J51" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="K51" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L51" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M51" t="n">
         <v>1.1</v>
       </c>
       <c r="N51" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O51" t="n">
         <v>1.45</v>
       </c>
       <c r="P51" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R51" t="n">
         <v>1.22</v>
@@ -10305,25 +10305,25 @@
         <v>4.1</v>
       </c>
       <c r="T51" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="U51" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V51" t="n">
         <v>1.31</v>
       </c>
       <c r="W51" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="X51" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z51" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA51" t="n">
         <v>900</v>
@@ -10332,13 +10332,13 @@
         <v>18</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD51" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AE51" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AF51" t="n">
         <v>30</v>
@@ -10347,28 +10347,28 @@
         <v>30</v>
       </c>
       <c r="AH51" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AI51" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AJ51" t="n">
         <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AL51" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AM51" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO51" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
         <v>4.9</v>
@@ -10377,10 +10377,10 @@
         <v>6.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AT51" t="n">
         <v>4.4</v>
@@ -10389,44 +10389,44 @@
         <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX51" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AY51" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
         <v>3.65</v>
       </c>
       <c r="L52" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10484,25 +10484,25 @@
         <v>3.1</v>
       </c>
       <c r="O52" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P52" t="n">
         <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R52" t="n">
         <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T52" t="n">
         <v>1.86</v>
       </c>
       <c r="U52" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V52" t="n">
         <v>1.3</v>
@@ -10511,7 +10511,7 @@
         <v>1.72</v>
       </c>
       <c r="X52" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="n">
         <v>24</v>
@@ -10538,10 +10538,10 @@
         <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI52" t="n">
         <v>1000</v>
@@ -10550,7 +10550,7 @@
         <v>900</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL52" t="n">
         <v>1000</v>
@@ -10559,7 +10559,7 @@
         <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO52" t="n">
         <v>1000</v>
@@ -10574,7 +10574,7 @@
         <v>6.8</v>
       </c>
       <c r="AS52" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT52" t="n">
         <v>4.9</v>
@@ -10586,19 +10586,19 @@
         <v>9</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX52" t="n">
         <v>6.4</v>
       </c>
       <c r="AY52" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AZ52" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA52" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB52" t="n">
         <v>6.8</v>
@@ -10607,20 +10607,20 @@
         <v>6.6</v>
       </c>
       <c r="BD52" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF52" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG52" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H53" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I53" t="n">
         <v>6.6</v>
@@ -10675,16 +10675,16 @@
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
         <v>1.28</v>
       </c>
       <c r="P53" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R53" t="n">
         <v>1.41</v>
@@ -10699,49 +10699,49 @@
         <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W53" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X53" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="Z53" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AA53" t="n">
         <v>190</v>
       </c>
       <c r="AB53" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC53" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD53" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AE53" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AF53" t="n">
         <v>10.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH53" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI53" t="n">
         <v>320</v>
       </c>
       <c r="AJ53" t="n">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="AK53" t="n">
         <v>17.5</v>
@@ -10753,7 +10753,7 @@
         <v>580</v>
       </c>
       <c r="AN53" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO53" t="n">
         <v>540</v>
@@ -10762,28 +10762,28 @@
         <v>14.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AT53" t="n">
         <v>7.8</v>
       </c>
       <c r="AU53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV53" t="n">
         <v>20</v>
       </c>
       <c r="AW53" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AX53" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY53" t="n">
         <v>8.800000000000001</v>
@@ -10792,7 +10792,7 @@
         <v>18</v>
       </c>
       <c r="BA53" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BB53" t="n">
         <v>14</v>
@@ -10801,20 +10801,20 @@
         <v>15</v>
       </c>
       <c r="BD53" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BE53" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BF53" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG53" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -10845,43 +10845,43 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G54" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H54" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I54" t="n">
         <v>3.1</v>
       </c>
       <c r="J54" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K54" t="n">
         <v>3.15</v>
       </c>
-      <c r="K54" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L54" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M54" t="n">
         <v>1.14</v>
       </c>
       <c r="N54" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O54" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P54" t="n">
         <v>1.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R54" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S54" t="n">
         <v>5.8</v>
@@ -10890,125 +10890,125 @@
         <v>2.16</v>
       </c>
       <c r="U54" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V54" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W54" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X54" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y54" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y54" t="n">
-        <v>970</v>
-      </c>
       <c r="Z54" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA54" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE54" t="n">
         <v>60</v>
       </c>
-      <c r="AB54" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>48</v>
-      </c>
       <c r="AF54" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG54" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI54" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ54" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK54" t="n">
         <v>55</v>
       </c>
-      <c r="AK54" t="n">
-        <v>46</v>
-      </c>
       <c r="AL54" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM54" t="n">
         <v>230</v>
       </c>
       <c r="AN54" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO54" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP54" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ54" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AR54" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS54" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AT54" t="n">
         <v>7.2</v>
       </c>
       <c r="AU54" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV54" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AW54" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AX54" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="AY54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ54" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BB54" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="BC54" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BD54" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BE54" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="BF54" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="BG54" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -11039,19 +11039,19 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G55" t="n">
         <v>1.95</v>
       </c>
       <c r="H55" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I55" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J55" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K55" t="n">
         <v>3.55</v>
@@ -11063,13 +11063,13 @@
         <v>1.12</v>
       </c>
       <c r="N55" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O55" t="n">
         <v>1.53</v>
       </c>
       <c r="P55" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q55" t="n">
         <v>2.58</v>
@@ -11078,10 +11078,10 @@
         <v>1.19</v>
       </c>
       <c r="S55" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="T55" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U55" t="n">
         <v>1.67</v>
@@ -11090,10 +11090,10 @@
         <v>1.18</v>
       </c>
       <c r="W55" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X55" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y55" t="n">
         <v>17</v>
@@ -11105,25 +11105,25 @@
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD55" t="n">
         <v>30</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF55" t="n">
         <v>12</v>
       </c>
       <c r="AG55" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI55" t="n">
         <v>1000</v>
@@ -11147,28 +11147,28 @@
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ55" t="n">
         <v>12</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT55" t="n">
         <v>5.4</v>
       </c>
       <c r="AU55" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV55" t="n">
         <v>21</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX55" t="n">
         <v>8.6</v>
@@ -11177,32 +11177,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB55" t="n">
         <v>19</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD55" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF55" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -760,70 +760,70 @@
         <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
@@ -832,7 +832,7 @@
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>21</v>
@@ -841,52 +841,52 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM2" t="n">
         <v>200</v>
       </c>
-      <c r="AK2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
         <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
@@ -895,32 +895,32 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="BE2" t="n">
         <v>80</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
         <v>90</v>
@@ -1029,7 +1029,7 @@
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1068,19 +1068,19 @@
         <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AV3" t="n">
         <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1089,32 +1089,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD3" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
         <v>90</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
         <v>1.44</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.9</v>
@@ -1169,37 +1169,37 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
         <v>80</v>
@@ -1211,85 +1211,85 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
         <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY4" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
@@ -1298,17 +1298,17 @@
         <v>21</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1351,43 +1351,43 @@
         <v>1.13</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
         <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1399,10 +1399,10 @@
         <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
@@ -1444,43 +1444,43 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
         <v>4.2</v>
@@ -1492,17 +1492,17 @@
         <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1533,49 +1533,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="I6" t="n">
         <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.73</v>
@@ -1584,7 +1584,7 @@
         <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
         <v>42</v>
@@ -1611,7 +1611,7 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
         <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.24</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
         <v>2.96</v>
@@ -1742,49 +1742,49 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
         <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
         <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
         <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -1829,68 +1829,68 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,13 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
         <v>1.48</v>
@@ -1960,7 +1960,7 @@
         <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
         <v>2.4</v>
@@ -1972,7 +1972,7 @@
         <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X8" t="n">
         <v>32</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK8" t="n">
         <v>18.5</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU8" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AV8" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AW8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX8" t="n">
         <v>3.55</v>
       </c>
-      <c r="AU8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AY8" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
         <v>3.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J9" t="n">
         <v>4.8</v>
@@ -2133,46 +2133,46 @@
         <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
         <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
         <v>9.800000000000001</v>
@@ -2181,7 +2181,7 @@
         <v>13.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
         <v>12</v>
@@ -2190,22 +2190,22 @@
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
         <v>280</v>
       </c>
       <c r="AG9" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AK9" t="n">
         <v>400</v>
@@ -2217,68 +2217,68 @@
         <v>380</v>
       </c>
       <c r="AN9" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>14</v>
+        <v>5.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>28</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>2.56</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
@@ -2321,46 +2321,46 @@
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="U10" t="n">
         <v>1.92</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.93</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X10" t="n">
         <v>15.5</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -2387,7 +2387,7 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
@@ -2399,13 +2399,13 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK10" t="n">
         <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2423,10 +2423,10 @@
         <v>17.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -2438,7 +2438,7 @@
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>8.199999999999999</v>
@@ -2447,10 +2447,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
@@ -2462,17 +2462,17 @@
         <v>18.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
         <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
         <v>1.75</v>
@@ -2512,52 +2512,52 @@
         <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
         <v>2.34</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>130</v>
@@ -2569,10 +2569,10 @@
         <v>700</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,7 +2581,7 @@
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
@@ -2593,19 +2593,19 @@
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18.5</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="n">
         <v>700</v>
       </c>
       <c r="AN11" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,25 +2614,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW11" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -2644,29 +2644,29 @@
         <v>24</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB11" t="n">
         <v>15.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2697,46 +2697,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>600</v>
+        <v>2.32</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>870</v>
+        <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="I13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.34</v>
@@ -2924,43 +2924,43 @@
         <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
         <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
         <v>36</v>
@@ -2972,7 +2972,7 @@
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
         <v>60</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
         <v>55</v>
       </c>
       <c r="AP13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="AW13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3085,31 +3085,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
@@ -3118,25 +3118,25 @@
         <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
         <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
         <v>18.5</v>
@@ -3154,10 +3154,10 @@
         <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>160</v>
@@ -3178,13 +3178,13 @@
         <v>19.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>10.5</v>
@@ -3193,28 +3193,28 @@
         <v>290</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>17.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
@@ -3226,7 +3226,7 @@
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3235,20 +3235,20 @@
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3279,55 +3279,55 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
         <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
         <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
         <v>2.08</v>
@@ -3336,10 +3336,10 @@
         <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -3351,7 +3351,7 @@
         <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AE15" t="n">
         <v>400</v>
@@ -3369,10 +3369,10 @@
         <v>320</v>
       </c>
       <c r="AJ15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK15" t="n">
         <v>22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>100</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" t="n">
         <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
         <v>18.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>13</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
         <v>7.2</v>
@@ -3491,43 +3491,43 @@
         <v>9.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
         <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
         <v>65</v>
@@ -3539,13 +3539,13 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3569,7 +3569,7 @@
         <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,7 +3581,7 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.2</v>
@@ -3596,7 +3596,7 @@
         <v>4.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
         <v>4.2</v>
@@ -3605,38 +3605,38 @@
         <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="BA16" t="n">
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
         <v>3.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3667,61 +3667,61 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
         <v>8.199999999999999</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
         <v>9.6</v>
@@ -3745,19 +3745,19 @@
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK17" t="n">
         <v>400</v>
@@ -3766,10 +3766,10 @@
         <v>390</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN17" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AO17" t="n">
         <v>10.5</v>
@@ -3778,19 +3778,19 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
         <v>8.800000000000001</v>
@@ -3799,38 +3799,38 @@
         <v>15.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="AZ17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA17" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>8</v>
-      </c>
       <c r="BB17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3861,127 +3861,127 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
         <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>440</v>
+        <v>48</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>15</v>
       </c>
-      <c r="AE18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>16</v>
-      </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AJ18" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>65</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3990,41 +3990,41 @@
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4055,79 +4055,79 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.79</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>9.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>200</v>
@@ -4139,13 +4139,13 @@
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
         <v>18.5</v>
@@ -4157,10 +4157,10 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="AP19" t="n">
         <v>14.5</v>
@@ -4169,13 +4169,13 @@
         <v>16.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
@@ -4184,7 +4184,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4208,17 +4208,17 @@
         <v>16</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF19" t="n">
         <v>8.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4249,61 +4249,61 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H20" t="n">
         <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T20" t="n">
         <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
         <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
         <v>16</v>
@@ -4339,67 +4339,67 @@
         <v>150</v>
       </c>
       <c r="AJ20" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP20" t="n">
         <v>15</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC20" t="n">
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE20" t="n">
         <v>22</v>
@@ -4408,11 +4408,11 @@
         <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4443,100 +4443,100 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I21" t="n">
         <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
         <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V21" t="n">
         <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA21" t="n">
         <v>420</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>290</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
         <v>42</v>
       </c>
       <c r="AI21" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AL21" t="n">
         <v>500</v>
@@ -4545,31 +4545,31 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO21" t="n">
         <v>500</v>
       </c>
-      <c r="AO21" t="n">
-        <v>210</v>
-      </c>
       <c r="AP21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
         <v>15.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
         <v>40</v>
@@ -4578,35 +4578,35 @@
         <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BB21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC21" t="n">
         <v>42</v>
       </c>
       <c r="BD21" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE21" t="n">
         <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG21" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4637,100 +4637,100 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H22" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="N22" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.15</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
         <v>1.11</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="n">
         <v>500</v>
       </c>
-      <c r="AB22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>540</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AL22" t="n">
         <v>540</v>
@@ -4745,62 +4745,62 @@
         <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.32</v>
+        <v>5.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.33</v>
+        <v>11.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.34</v>
+        <v>30</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.33</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.31</v>
+        <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.34</v>
+        <v>38</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.33</v>
+        <v>16</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.31</v>
+        <v>14.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.33</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.35</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.35</v>
+        <v>48</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.35</v>
+        <v>46</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.35</v>
+        <v>44</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.55</v>
+        <v>42</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.55</v>
+        <v>32</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4831,88 +4831,88 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H23" t="n">
         <v>3.25</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K23" t="n">
         <v>3.15</v>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="M23" t="n">
         <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P23" t="n">
         <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD23" t="n">
         <v>24</v>
       </c>
       <c r="AE23" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AH23" t="n">
         <v>46</v>
@@ -4924,13 +4924,13 @@
         <v>170</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM23" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>11</v>
       </c>
-      <c r="AX23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF23" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>10</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.08</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
@@ -5043,25 +5043,25 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
         <v>3.6</v>
@@ -5070,34 +5070,34 @@
         <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
         <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA24" t="n">
         <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC24" t="n">
         <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
         <v>55</v>
@@ -5109,7 +5109,7 @@
         <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>130</v>
@@ -5124,7 +5124,7 @@
         <v>40</v>
       </c>
       <c r="AM24" t="n">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="AN24" t="n">
         <v>17</v>
@@ -5139,10 +5139,10 @@
         <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT24" t="n">
         <v>8.199999999999999</v>
@@ -5154,41 +5154,41 @@
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G25" t="n">
         <v>1.93</v>
@@ -5228,16 +5228,16 @@
         <v>3.75</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
@@ -5246,19 +5246,19 @@
         <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P25" t="n">
         <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="R25" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="S25" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="T25" t="n">
         <v>1.42</v>
@@ -5267,13 +5267,13 @@
         <v>3.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
         <v>2.06</v>
       </c>
       <c r="X25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5282,13 +5282,13 @@
         <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB25" t="n">
         <v>38</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
         <v>34</v>
@@ -5327,28 +5327,28 @@
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
         <v>17</v>
@@ -5363,26 +5363,26 @@
         <v>26</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
         <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE25" t="n">
         <v>19</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG25" t="n">
         <v>14</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5416,55 +5416,55 @@
         <v>1.61</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I26" t="n">
         <v>5.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K26" t="n">
         <v>5.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R26" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="S26" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T26" t="n">
         <v>1.54</v>
       </c>
       <c r="U26" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V26" t="n">
         <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5491,7 +5491,7 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="AG26" t="n">
         <v>20</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
         <v>8.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
         <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC26" t="n">
         <v>7</v>
       </c>
-      <c r="BC26" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD26" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
         <v>14</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5607,85 +5607,85 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G27" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I27" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S27" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U27" t="n">
         <v>2.6</v>
       </c>
       <c r="V27" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="n">
         <v>14.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
         <v>22</v>
       </c>
       <c r="AB27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD27" t="n">
         <v>11.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG27" t="n">
         <v>19</v>
@@ -5700,7 +5700,7 @@
         <v>85</v>
       </c>
       <c r="AK27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL27" t="n">
         <v>44</v>
@@ -5751,26 +5751,26 @@
         <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BG27" t="n">
         <v>6.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5801,82 +5801,82 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G28" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
         <v>5.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="R28" t="n">
         <v>1.17</v>
       </c>
       <c r="S28" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U28" t="n">
         <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y28" t="n">
         <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>6.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
         <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
         <v>11.5</v>
@@ -5894,7 +5894,7 @@
         <v>27</v>
       </c>
       <c r="AK28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL28" t="n">
         <v>160</v>
@@ -5903,22 +5903,22 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>5.5</v>
@@ -5927,10 +5927,10 @@
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>9.199999999999999</v>
@@ -5939,32 +5939,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
         <v>8</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5995,91 +5995,91 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="G29" t="n">
         <v>2.08</v>
       </c>
       <c r="H29" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I29" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J29" t="n">
         <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P29" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="T29" t="n">
         <v>1.58</v>
       </c>
       <c r="U29" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
         <v>1.92</v>
       </c>
       <c r="X29" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
         <v>500</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>100</v>
       </c>
       <c r="AA29" t="n">
         <v>500</v>
       </c>
       <c r="AB29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC29" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AD29" t="n">
         <v>500</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF29" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
         <v>16</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AI29" t="n">
         <v>500</v>
@@ -6088,7 +6088,7 @@
         <v>85</v>
       </c>
       <c r="AK29" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
         <v>500</v>
@@ -6097,34 +6097,34 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO29" t="n">
         <v>500</v>
       </c>
       <c r="AP29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT29" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV29" t="n">
         <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AX29" t="n">
         <v>13.5</v>
@@ -6133,32 +6133,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BB29" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BE29" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G30" t="n">
         <v>1.68</v>
@@ -6198,46 +6198,46 @@
         <v>7.4</v>
       </c>
       <c r="I30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
         <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
         <v>2.46</v>
@@ -6258,7 +6258,7 @@
         <v>46</v>
       </c>
       <c r="AC30" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AX30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BA30" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.89</v>
+        <v>9.4</v>
       </c>
       <c r="BF30" t="n">
         <v>5.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>2.62</v>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J31" t="n">
         <v>3.25</v>
@@ -6401,16 +6401,16 @@
         <v>3.35</v>
       </c>
       <c r="L31" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="O31" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P31" t="n">
         <v>1.64</v>
@@ -6419,31 +6419,31 @@
         <v>2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W31" t="n">
         <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA31" t="n">
         <v>44</v>
@@ -6461,7 +6461,7 @@
         <v>36</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
@@ -6479,7 +6479,7 @@
         <v>44</v>
       </c>
       <c r="AL31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM31" t="n">
         <v>150</v>
@@ -6491,19 +6491,19 @@
         <v>40</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS31" t="n">
         <v>36</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
         <v>6.8</v>
@@ -6512,10 +6512,10 @@
         <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
@@ -6530,23 +6530,23 @@
         <v>50</v>
       </c>
       <c r="BC31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD31" t="n">
         <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BF31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BG31" t="n">
         <v>34</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I32" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
@@ -6595,28 +6595,28 @@
         <v>3.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
         <v>1.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
         <v>1.87</v>
@@ -6625,7 +6625,7 @@
         <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
         <v>1.48</v>
@@ -6634,7 +6634,7 @@
         <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z32" t="n">
         <v>17</v>
@@ -6643,10 +6643,10 @@
         <v>42</v>
       </c>
       <c r="AB32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD32" t="n">
         <v>12.5</v>
@@ -6664,7 +6664,7 @@
         <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ32" t="n">
         <v>55</v>
@@ -6676,10 +6676,10 @@
         <v>60</v>
       </c>
       <c r="AM32" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO32" t="n">
         <v>34</v>
@@ -6691,25 +6691,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS32" t="n">
         <v>36</v>
       </c>
       <c r="AT32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY32" t="n">
         <v>12</v>
@@ -6730,17 +6730,17 @@
         <v>23</v>
       </c>
       <c r="BE32" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6774,43 +6774,43 @@
         <v>2.24</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H33" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I33" t="n">
         <v>3.95</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K33" t="n">
         <v>3.45</v>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
         <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
         <v>1.95</v>
@@ -6822,7 +6822,7 @@
         <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6831,13 +6831,13 @@
         <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AA33" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC33" t="n">
         <v>7.6</v>
@@ -6861,7 +6861,7 @@
         <v>370</v>
       </c>
       <c r="AJ33" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK33" t="n">
         <v>30</v>
@@ -6888,7 +6888,7 @@
         <v>20</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT33" t="n">
         <v>7.6</v>
@@ -6912,7 +6912,7 @@
         <v>11.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB33" t="n">
         <v>24</v>
@@ -6924,7 +6924,7 @@
         <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF33" t="n">
         <v>20</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6968,46 +6968,46 @@
         <v>4.2</v>
       </c>
       <c r="G34" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>2.04</v>
       </c>
       <c r="J34" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K34" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
         <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P34" t="n">
         <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
         <v>1.9</v>
@@ -7016,7 +7016,7 @@
         <v>1.97</v>
       </c>
       <c r="W34" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
         <v>12</v>
@@ -7031,10 +7031,10 @@
         <v>25</v>
       </c>
       <c r="AB34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34" t="n">
         <v>10.5</v>
@@ -7046,7 +7046,7 @@
         <v>32</v>
       </c>
       <c r="AG34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH34" t="n">
         <v>23</v>
@@ -7055,13 +7055,13 @@
         <v>46</v>
       </c>
       <c r="AJ34" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK34" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM34" t="n">
         <v>580</v>
@@ -7088,7 +7088,7 @@
         <v>11.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV34" t="n">
         <v>9.4</v>
@@ -7100,35 +7100,35 @@
         <v>13</v>
       </c>
       <c r="AY34" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="BB34" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC34" t="n">
         <v>12</v>
       </c>
-      <c r="BC34" t="n">
-        <v>11</v>
-      </c>
       <c r="BD34" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG34" t="n">
         <v>16.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7162,55 +7162,55 @@
         <v>2.72</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H35" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I35" t="n">
         <v>3.35</v>
       </c>
       <c r="J35" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L35" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
         <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>1.42</v>
       </c>
       <c r="W35" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X35" t="n">
         <v>10</v>
@@ -7282,13 +7282,13 @@
         <v>9</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV35" t="n">
         <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX35" t="n">
         <v>12.5</v>
@@ -7309,7 +7309,7 @@
         <v>14.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE35" t="n">
         <v>10</v>
@@ -7318,11 +7318,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7353,46 +7353,46 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H36" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I36" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K36" t="n">
         <v>4.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
         <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
         <v>1.86</v>
@@ -7401,16 +7401,16 @@
         <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="X36" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Y36" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,7 +7419,7 @@
         <v>900</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC36" t="n">
         <v>9.199999999999999</v>
@@ -7428,7 +7428,7 @@
         <v>44</v>
       </c>
       <c r="AE36" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF36" t="n">
         <v>10.5</v>
@@ -7461,25 +7461,25 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT36" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>7.8</v>
       </c>
       <c r="AU36" t="n">
         <v>8</v>
       </c>
       <c r="AV36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW36" t="n">
         <v>12</v>
@@ -7494,7 +7494,7 @@
         <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB36" t="n">
         <v>14</v>
@@ -7503,7 +7503,7 @@
         <v>15.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BE36" t="n">
         <v>12.5</v>
@@ -7512,11 +7512,11 @@
         <v>8.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>4.2</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
@@ -7565,31 +7565,31 @@
         <v>3.7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R37" t="n">
         <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
         <v>2.08</v>
@@ -7598,13 +7598,13 @@
         <v>1.98</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X37" t="n">
         <v>13.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z37" t="n">
         <v>11.5</v>
@@ -7625,10 +7625,10 @@
         <v>21</v>
       </c>
       <c r="AF37" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH37" t="n">
         <v>19</v>
@@ -7649,16 +7649,16 @@
         <v>110</v>
       </c>
       <c r="AN37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO37" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP37" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AR37" t="n">
         <v>11</v>
@@ -7667,7 +7667,7 @@
         <v>22</v>
       </c>
       <c r="AT37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU37" t="n">
         <v>7.6</v>
@@ -7688,10 +7688,10 @@
         <v>18</v>
       </c>
       <c r="BA37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB37" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BC37" t="n">
         <v>50</v>
@@ -7700,7 +7700,7 @@
         <v>55</v>
       </c>
       <c r="BE37" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF37" t="n">
         <v>55</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7741,25 +7741,25 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G38" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H38" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -7768,25 +7768,25 @@
         <v>4.4</v>
       </c>
       <c r="O38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U38" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V38" t="n">
         <v>1.44</v>
@@ -7807,10 +7807,10 @@
         <v>900</v>
       </c>
       <c r="AB38" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC38" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AD38" t="n">
         <v>970</v>
@@ -7849,62 +7849,62 @@
         <v>500</v>
       </c>
       <c r="AP38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY38" t="n">
         <v>6</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX38" t="n">
+      <c r="AZ38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG38" t="n">
         <v>6</v>
       </c>
-      <c r="AY38" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G39" t="n">
         <v>1.76</v>
       </c>
-      <c r="G39" t="n">
-        <v>1.77</v>
-      </c>
       <c r="H39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J39" t="n">
         <v>3.95</v>
@@ -7953,31 +7953,31 @@
         <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
         <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O39" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T39" t="n">
         <v>1.97</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.94</v>
       </c>
       <c r="U39" t="n">
         <v>2</v>
@@ -7986,22 +7986,22 @@
         <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X39" t="n">
         <v>14</v>
       </c>
       <c r="Y39" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA39" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC39" t="n">
         <v>8.6</v>
@@ -8010,10 +8010,10 @@
         <v>21</v>
       </c>
       <c r="AE39" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG39" t="n">
         <v>9.6</v>
@@ -8034,19 +8034,19 @@
         <v>38</v>
       </c>
       <c r="AM39" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN39" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO39" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP39" t="n">
         <v>13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR39" t="n">
         <v>38</v>
@@ -8055,10 +8055,10 @@
         <v>42</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV39" t="n">
         <v>19.5</v>
@@ -8067,7 +8067,7 @@
         <v>65</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY39" t="n">
         <v>9.199999999999999</v>
@@ -8076,13 +8076,13 @@
         <v>19.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB39" t="n">
         <v>16.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD39" t="n">
         <v>34</v>
@@ -8091,14 +8091,14 @@
         <v>100</v>
       </c>
       <c r="BF39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG39" t="n">
         <v>80</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -8132,16 +8132,16 @@
         <v>2.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H40" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
         <v>3.3</v>
@@ -8150,22 +8150,22 @@
         <v>1.56</v>
       </c>
       <c r="M40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.51</v>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R40" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S40" t="n">
         <v>5.2</v>
@@ -8177,7 +8177,7 @@
         <v>1.83</v>
       </c>
       <c r="V40" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
         <v>1.72</v>
@@ -8189,7 +8189,7 @@
         <v>11.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AA40" t="n">
         <v>900</v>
@@ -8201,7 +8201,7 @@
         <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE40" t="n">
         <v>370</v>
@@ -8210,22 +8210,22 @@
         <v>14</v>
       </c>
       <c r="AG40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AK40" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL40" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
@@ -8243,10 +8243,10 @@
         <v>9.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT40" t="n">
         <v>6.4</v>
@@ -8270,29 +8270,29 @@
         <v>19</v>
       </c>
       <c r="BA40" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="BC40" t="n">
         <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF40" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G41" t="n">
         <v>1.62</v>
       </c>
       <c r="H41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I41" t="n">
         <v>6.4</v>
-      </c>
-      <c r="I41" t="n">
-        <v>6.6</v>
       </c>
       <c r="J41" t="n">
         <v>4.4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
         <v>1.36</v>
@@ -8347,25 +8347,25 @@
         <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
         <v>1.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R41" t="n">
         <v>1.49</v>
       </c>
       <c r="S41" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T41" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U41" t="n">
         <v>2.12</v>
@@ -8374,10 +8374,10 @@
         <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X41" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y41" t="n">
         <v>23</v>
@@ -8413,13 +8413,13 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK41" t="n">
         <v>15.5</v>
       </c>
       <c r="AL41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM41" t="n">
         <v>95</v>
@@ -8431,22 +8431,22 @@
         <v>95</v>
       </c>
       <c r="AP41" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ41" t="n">
         <v>21</v>
       </c>
       <c r="AR41" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS41" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AT41" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV41" t="n">
         <v>21</v>
@@ -8455,25 +8455,25 @@
         <v>70</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY41" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB41" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE41" t="n">
         <v>90</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -8520,61 +8520,61 @@
         <v>1.91</v>
       </c>
       <c r="G42" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K42" t="n">
         <v>3.9</v>
       </c>
       <c r="L42" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O42" t="n">
         <v>1.31</v>
       </c>
       <c r="P42" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U42" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V42" t="n">
         <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X42" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z42" t="n">
         <v>90</v>
@@ -8583,16 +8583,16 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
         <v>11.5</v>
@@ -8601,16 +8601,16 @@
         <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AK42" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL42" t="n">
         <v>85</v>
@@ -8619,68 +8619,68 @@
         <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP42" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>13.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AS42" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AT42" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV42" t="n">
         <v>16</v>
       </c>
       <c r="AW42" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AX42" t="n">
         <v>10</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BB42" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC42" t="n">
         <v>15.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BE42" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF42" t="n">
         <v>11</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BG42" t="n">
         <v>12</v>
       </c>
-      <c r="BG42" t="n">
-        <v>10</v>
-      </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -8711,58 +8711,58 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G43" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H43" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O43" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P43" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T43" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U43" t="n">
         <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X43" t="n">
         <v>32</v>
@@ -8780,7 +8780,7 @@
         <v>27</v>
       </c>
       <c r="AC43" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD43" t="n">
         <v>1000</v>
@@ -8819,62 +8819,62 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ43" t="n">
         <v>4</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT43" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AV43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.68</v>
+        <v>3.95</v>
       </c>
       <c r="AX43" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY43" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ43" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="BB43" t="n">
         <v>6.8</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="BF43" t="n">
         <v>10</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -8905,61 +8905,61 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="H44" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="I44" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K44" t="n">
         <v>3.45</v>
       </c>
       <c r="L44" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.46</v>
       </c>
       <c r="P44" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R44" t="n">
         <v>1.24</v>
       </c>
       <c r="S44" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T44" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U44" t="n">
         <v>1.96</v>
       </c>
       <c r="V44" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y44" t="n">
         <v>10.5</v>
@@ -8974,7 +8974,7 @@
         <v>10</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD44" t="n">
         <v>13.5</v>
@@ -9001,16 +9001,16 @@
         <v>110</v>
       </c>
       <c r="AL44" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AM44" t="n">
         <v>580</v>
       </c>
       <c r="AN44" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AO44" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP44" t="n">
         <v>9.4</v>
@@ -9022,7 +9022,7 @@
         <v>15.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT44" t="n">
         <v>8.199999999999999</v>
@@ -9046,29 +9046,29 @@
         <v>17</v>
       </c>
       <c r="BA44" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF44" t="n">
         <v>8</v>
       </c>
-      <c r="BB44" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD44" t="n">
+      <c r="BG44" t="n">
         <v>8</v>
       </c>
-      <c r="BE44" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -9099,73 +9099,73 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G45" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="H45" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M45" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N45" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P45" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="R45" t="n">
         <v>1.16</v>
       </c>
       <c r="S45" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U45" t="n">
         <v>1.59</v>
       </c>
       <c r="V45" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W45" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X45" t="n">
         <v>8.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z45" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC45" t="n">
         <v>8.4</v>
@@ -9210,13 +9210,13 @@
         <v>7</v>
       </c>
       <c r="AQ45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR45" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AS45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT45" t="n">
         <v>5</v>
@@ -9225,44 +9225,44 @@
         <v>7</v>
       </c>
       <c r="AV45" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX45" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ45" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BA45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB45" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC45" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD45" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE45" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF45" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG45" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -9293,64 +9293,64 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G46" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J46" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K46" t="n">
         <v>3.5</v>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O46" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T46" t="n">
         <v>1.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V46" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X46" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y46" t="n">
         <v>11.5</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>12</v>
       </c>
       <c r="Z46" t="n">
         <v>25</v>
@@ -9359,7 +9359,7 @@
         <v>160</v>
       </c>
       <c r="AB46" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC46" t="n">
         <v>7.8</v>
@@ -9368,7 +9368,7 @@
         <v>16</v>
       </c>
       <c r="AE46" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
         <v>15.5</v>
@@ -9383,7 +9383,7 @@
         <v>370</v>
       </c>
       <c r="AJ46" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AK46" t="n">
         <v>75</v>
@@ -9410,7 +9410,7 @@
         <v>20</v>
       </c>
       <c r="AS46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -9422,7 +9422,7 @@
         <v>12.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX46" t="n">
         <v>12.5</v>
@@ -9431,10 +9431,10 @@
         <v>10</v>
       </c>
       <c r="AZ46" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB46" t="n">
         <v>13</v>
@@ -9446,17 +9446,17 @@
         <v>40</v>
       </c>
       <c r="BE46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF46" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -9487,55 +9487,55 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G47" t="n">
         <v>2.34</v>
       </c>
       <c r="H47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K47" t="n">
         <v>3.05</v>
       </c>
       <c r="L47" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O47" t="n">
         <v>1.69</v>
       </c>
       <c r="P47" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
         <v>1.14</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T47" t="n">
         <v>2.44</v>
       </c>
       <c r="U47" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V47" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W47" t="n">
         <v>1.74</v>
@@ -9544,10 +9544,10 @@
         <v>7</v>
       </c>
       <c r="Y47" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AA47" t="n">
         <v>500</v>
@@ -9559,7 +9559,7 @@
         <v>7.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE47" t="n">
         <v>500</v>
@@ -9568,28 +9568,28 @@
         <v>12.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AI47" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ47" t="n">
         <v>34</v>
       </c>
       <c r="AK47" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AM47" t="n">
         <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO47" t="n">
         <v>500</v>
@@ -9598,10 +9598,10 @@
         <v>6.2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR47" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AS47" t="n">
         <v>65</v>
@@ -9613,31 +9613,31 @@
         <v>6.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA47" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BB47" t="n">
         <v>19.5</v>
       </c>
       <c r="BC47" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BD47" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE47" t="n">
         <v>100</v>
@@ -9646,11 +9646,11 @@
         <v>23</v>
       </c>
       <c r="BG47" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -9681,58 +9681,58 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H48" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I48" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K48" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P48" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R48" t="n">
         <v>1.24</v>
       </c>
       <c r="S48" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.9</v>
       </c>
-      <c r="U48" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V48" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W48" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X48" t="n">
         <v>90</v>
@@ -9750,7 +9750,7 @@
         <v>500</v>
       </c>
       <c r="AC48" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD48" t="n">
         <v>970</v>
@@ -9771,7 +9771,7 @@
         <v>500</v>
       </c>
       <c r="AJ48" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AK48" t="n">
         <v>500</v>
@@ -9795,10 +9795,10 @@
         <v>6.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AT48" t="n">
         <v>4.9</v>
@@ -9807,10 +9807,10 @@
         <v>4.9</v>
       </c>
       <c r="AV48" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW48" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AX48" t="n">
         <v>6.2</v>
@@ -9819,32 +9819,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ48" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.98</v>
+        <v>2.52</v>
       </c>
       <c r="BB48" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="BF48" t="n">
         <v>5.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G49" t="n">
         <v>1.47</v>
@@ -9884,7 +9884,7 @@
         <v>10</v>
       </c>
       <c r="I49" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J49" t="n">
         <v>4.4</v>
@@ -9893,13 +9893,13 @@
         <v>4.6</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
         <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>1.46</v>
@@ -9908,19 +9908,19 @@
         <v>1.67</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R49" t="n">
         <v>1.24</v>
       </c>
       <c r="S49" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U49" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V49" t="n">
         <v>1.09</v>
@@ -9941,7 +9941,7 @@
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AC49" t="n">
         <v>11</v>
@@ -9950,34 +9950,34 @@
         <v>100</v>
       </c>
       <c r="AE49" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
         <v>6.8</v>
       </c>
       <c r="AG49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH49" t="n">
         <v>95</v>
       </c>
       <c r="AI49" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AJ49" t="n">
         <v>12</v>
       </c>
       <c r="AK49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AM49" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="AN49" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO49" t="n">
         <v>1000</v>
@@ -9989,10 +9989,10 @@
         <v>20</v>
       </c>
       <c r="AR49" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AS49" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AT49" t="n">
         <v>5.2</v>
@@ -10013,32 +10013,32 @@
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BA49" t="n">
         <v>50</v>
       </c>
       <c r="BB49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC49" t="n">
         <v>18</v>
       </c>
       <c r="BD49" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG49" t="n">
         <v>55</v>
       </c>
-      <c r="BE49" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>60</v>
-      </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>2.94</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H50" t="n">
         <v>2.7</v>
@@ -10087,25 +10087,25 @@
         <v>3.4</v>
       </c>
       <c r="L50" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M50" t="n">
         <v>1.08</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
         <v>1.37</v>
       </c>
       <c r="P50" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q50" t="n">
         <v>2.14</v>
       </c>
       <c r="R50" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S50" t="n">
         <v>3.95</v>
@@ -10114,7 +10114,7 @@
         <v>1.83</v>
       </c>
       <c r="U50" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V50" t="n">
         <v>1.57</v>
@@ -10123,7 +10123,7 @@
         <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y50" t="n">
         <v>10.5</v>
@@ -10135,7 +10135,7 @@
         <v>40</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC50" t="n">
         <v>7.4</v>
@@ -10165,13 +10165,13 @@
         <v>36</v>
       </c>
       <c r="AL50" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO50" t="n">
         <v>30</v>
@@ -10189,7 +10189,7 @@
         <v>36</v>
       </c>
       <c r="AT50" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU50" t="n">
         <v>7</v>
@@ -10207,7 +10207,7 @@
         <v>11</v>
       </c>
       <c r="AZ50" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BA50" t="n">
         <v>36</v>
@@ -10225,14 +10225,14 @@
         <v>30</v>
       </c>
       <c r="BF50" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BG50" t="n">
         <v>25</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G51" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H51" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I51" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K51" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L51" t="n">
         <v>1.48</v>
@@ -10290,43 +10290,43 @@
         <v>3.25</v>
       </c>
       <c r="O51" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P51" t="n">
         <v>1.73</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R51" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T51" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V51" t="n">
         <v>1.41</v>
       </c>
       <c r="W51" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X51" t="n">
         <v>22</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z51" t="n">
         <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
         <v>1000</v>
@@ -10341,7 +10341,7 @@
         <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG51" t="n">
         <v>1000</v>
@@ -10374,25 +10374,25 @@
         <v>6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AS51" t="n">
-        <v>40</v>
+        <v>3.9</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU51" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV51" t="n">
         <v>8.4</v>
       </c>
       <c r="AW51" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="AX51" t="n">
         <v>7.6</v>
@@ -10401,22 +10401,22 @@
         <v>10</v>
       </c>
       <c r="AZ51" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC51" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD51" t="n">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BE51" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="BF51" t="n">
         <v>5</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -10457,64 +10457,64 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G52" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H52" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L52" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O52" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P52" t="n">
         <v>1.62</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R52" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
         <v>1.83</v>
       </c>
       <c r="V52" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X52" t="n">
         <v>17.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z52" t="n">
         <v>500</v>
@@ -10523,13 +10523,13 @@
         <v>900</v>
       </c>
       <c r="AB52" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC52" t="n">
         <v>14</v>
       </c>
       <c r="AD52" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE52" t="n">
         <v>500</v>
@@ -10556,7 +10556,7 @@
         <v>500</v>
       </c>
       <c r="AM52" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN52" t="n">
         <v>500</v>
@@ -10571,7 +10571,7 @@
         <v>6.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS52" t="n">
         <v>7.6</v>
@@ -10583,7 +10583,7 @@
         <v>6.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW52" t="n">
         <v>7.4</v>
@@ -10595,32 +10595,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ52" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BA52" t="n">
         <v>7.6</v>
       </c>
       <c r="BB52" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC52" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD52" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF52" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE52" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG52" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -10651,58 +10651,58 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G53" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H53" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K53" t="n">
         <v>3.6</v>
       </c>
-      <c r="I53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L53" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M53" t="n">
         <v>1.09</v>
       </c>
       <c r="N53" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O53" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P53" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R53" t="n">
         <v>1.27</v>
       </c>
       <c r="S53" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T53" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U53" t="n">
         <v>1.96</v>
       </c>
       <c r="V53" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W53" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="X53" t="n">
         <v>20</v>
@@ -10729,13 +10729,13 @@
         <v>1000</v>
       </c>
       <c r="AF53" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG53" t="n">
         <v>21</v>
       </c>
       <c r="AH53" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AI53" t="n">
         <v>1000</v>
@@ -10765,10 +10765,10 @@
         <v>6.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT53" t="n">
         <v>4.9</v>
@@ -10792,7 +10792,7 @@
         <v>6</v>
       </c>
       <c r="BA53" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB53" t="n">
         <v>6.8</v>
@@ -10804,7 +10804,7 @@
         <v>7.2</v>
       </c>
       <c r="BE53" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BF53" t="n">
         <v>6.2</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G54" t="n">
         <v>1.65</v>
@@ -10854,16 +10854,16 @@
         <v>5.9</v>
       </c>
       <c r="I54" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J54" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K54" t="n">
         <v>4.5</v>
       </c>
       <c r="L54" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M54" t="n">
         <v>1.06</v>
@@ -10872,28 +10872,28 @@
         <v>4.1</v>
       </c>
       <c r="O54" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P54" t="n">
         <v>2.06</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R54" t="n">
         <v>1.41</v>
       </c>
       <c r="S54" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T54" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U54" t="n">
         <v>2.02</v>
       </c>
       <c r="V54" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W54" t="n">
         <v>2.52</v>
@@ -10908,7 +10908,7 @@
         <v>230</v>
       </c>
       <c r="AA54" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB54" t="n">
         <v>8.800000000000001</v>
@@ -10920,10 +10920,10 @@
         <v>100</v>
       </c>
       <c r="AE54" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF54" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG54" t="n">
         <v>10</v>
@@ -10932,10 +10932,10 @@
         <v>44</v>
       </c>
       <c r="AI54" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ54" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="AK54" t="n">
         <v>17.5</v>
@@ -10950,7 +10950,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO54" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AP54" t="n">
         <v>14.5</v>
@@ -10959,10 +10959,10 @@
         <v>10.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT54" t="n">
         <v>7.8</v>
@@ -10974,7 +10974,7 @@
         <v>20</v>
       </c>
       <c r="AW54" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX54" t="n">
         <v>8.800000000000001</v>
@@ -10986,7 +10986,7 @@
         <v>18</v>
       </c>
       <c r="BA54" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB54" t="n">
         <v>14</v>
@@ -10998,17 +10998,17 @@
         <v>18</v>
       </c>
       <c r="BE54" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF54" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG54" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -11042,16 +11042,16 @@
         <v>2.8</v>
       </c>
       <c r="G55" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H55" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I55" t="n">
         <v>3.1</v>
       </c>
       <c r="J55" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K55" t="n">
         <v>3.15</v>
@@ -11060,25 +11060,25 @@
         <v>1.65</v>
       </c>
       <c r="M55" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N55" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O55" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P55" t="n">
         <v>1.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="R55" t="n">
         <v>1.17</v>
       </c>
       <c r="S55" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T55" t="n">
         <v>2.16</v>
@@ -11090,10 +11090,10 @@
         <v>1.47</v>
       </c>
       <c r="W55" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X55" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y55" t="n">
         <v>9.6</v>
@@ -11108,7 +11108,7 @@
         <v>9.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD55" t="n">
         <v>16.5</v>
@@ -11117,10 +11117,10 @@
         <v>60</v>
       </c>
       <c r="AF55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG55" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH55" t="n">
         <v>28</v>
@@ -11129,13 +11129,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="n">
         <v>55</v>
       </c>
       <c r="AL55" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM55" t="n">
         <v>230</v>
@@ -11147,16 +11147,16 @@
         <v>75</v>
       </c>
       <c r="AP55" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="AQ55" t="n">
         <v>7.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT55" t="n">
         <v>7.2</v>
@@ -11165,44 +11165,44 @@
         <v>6.2</v>
       </c>
       <c r="AV55" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY55" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY55" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ55" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA55" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD55" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF55" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG55" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -11233,67 +11233,67 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="G56" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="H56" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I56" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K56" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L56" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="M56" t="n">
         <v>1.12</v>
       </c>
       <c r="N56" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="O56" t="n">
         <v>1.53</v>
       </c>
       <c r="P56" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R56" t="n">
         <v>1.19</v>
       </c>
       <c r="S56" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T56" t="n">
         <v>2.28</v>
       </c>
       <c r="U56" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V56" t="n">
         <v>1.18</v>
       </c>
       <c r="W56" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="X56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y56" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z56" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA56" t="n">
         <v>1000</v>
@@ -11302,13 +11302,13 @@
         <v>6.2</v>
       </c>
       <c r="AC56" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE56" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF56" t="n">
         <v>11</v>
@@ -11323,13 +11323,13 @@
         <v>1000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK56" t="n">
         <v>32</v>
       </c>
       <c r="AL56" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
@@ -11341,16 +11341,16 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ56" t="n">
         <v>12</v>
       </c>
       <c r="AR56" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AS56" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT56" t="n">
         <v>5.4</v>
@@ -11362,41 +11362,41 @@
         <v>21</v>
       </c>
       <c r="AW56" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX56" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY56" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ56" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB56" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BC56" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BD56" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE56" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF56" t="n">
         <v>16</v>
       </c>
       <c r="BG56" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -784,46 +784,46 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.58</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
@@ -832,82 +832,82 @@
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
         <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
         <v>80</v>
@@ -916,11 +916,11 @@
         <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
@@ -966,7 +966,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -981,10 +981,10 @@
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -993,7 +993,7 @@
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
         <v>2.02</v>
@@ -1002,7 +1002,7 @@
         <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
         <v>90</v>
@@ -1011,7 +1011,7 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1068,53 +1068,53 @@
         <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC3" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
         <v>90</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1175,31 +1175,31 @@
         <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
         <v>80</v>
@@ -1211,31 +1211,31 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
@@ -1247,68 +1247,68 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>90</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1339,70 +1339,70 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="S5" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>60</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
@@ -1414,7 +1414,7 @@
         <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF5" t="n">
         <v>1000</v>
@@ -1444,65 +1444,65 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1563,7 +1563,7 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.71</v>
@@ -1575,16 +1575,16 @@
         <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW6" t="n">
         <v>5.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BA6" t="n">
         <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
         <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
         <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.39</v>
@@ -1751,40 +1751,40 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
         <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
         <v>1.61</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -1793,7 +1793,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1802,16 +1802,16 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG7" t="n">
         <v>500</v>
       </c>
-      <c r="AF7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>970</v>
-      </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -1835,19 +1835,19 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
@@ -1856,41 +1856,41 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>7.6</v>
       </c>
       <c r="BA7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G8" t="n">
         <v>1.23</v>
@@ -1930,10 +1930,10 @@
         <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="K8" t="n">
         <v>9</v>
@@ -1954,28 +1954,28 @@
         <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
         <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1999,7 +1999,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AG8" t="n">
         <v>15.5</v>
@@ -2023,46 +2023,46 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>4.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AY8" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -2071,20 +2071,20 @@
         <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
         <v>3.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2115,28 +2115,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
@@ -2145,67 +2145,67 @@
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AB9" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
         <v>280</v>
       </c>
       <c r="AG9" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="AK9" t="n">
         <v>400</v>
@@ -2217,68 +2217,68 @@
         <v>380</v>
       </c>
       <c r="AN9" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AO9" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AP9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS9" t="n">
         <v>10</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AT9" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.56</v>
+        <v>4.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
@@ -2321,10 +2321,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.41</v>
@@ -2333,40 +2333,40 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X10" t="n">
         <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2384,10 +2384,10 @@
         <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
@@ -2396,28 +2396,28 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ10" t="n">
         <v>16.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
         <v>17.5</v>
@@ -2426,7 +2426,7 @@
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -2438,19 +2438,19 @@
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
@@ -2462,17 +2462,17 @@
         <v>18.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.71</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.75</v>
       </c>
       <c r="H11" t="n">
         <v>6.4</v>
@@ -2518,10 +2518,10 @@
         <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
@@ -2530,25 +2530,25 @@
         <v>2.88</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
         <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
         <v>1.17</v>
@@ -2557,7 +2557,7 @@
         <v>2.34</v>
       </c>
       <c r="X11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
         <v>130</v>
@@ -2569,7 +2569,7 @@
         <v>700</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC11" t="n">
         <v>8.4</v>
@@ -2587,7 +2587,7 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
@@ -2596,7 +2596,7 @@
         <v>120</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="n">
         <v>160</v>
@@ -2605,34 +2605,34 @@
         <v>700</v>
       </c>
       <c r="AN11" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -2644,7 +2644,7 @@
         <v>24</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB11" t="n">
         <v>15.5</v>
@@ -2653,20 +2653,20 @@
         <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BE11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.33</v>
       </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>4.2</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I13" t="n">
         <v>2.02</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
@@ -2915,16 +2915,16 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R13" t="n">
         <v>1.34</v>
@@ -2933,52 +2933,52 @@
         <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
         <v>1.98</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AH13" t="n">
         <v>60</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2993,25 +2993,25 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
         <v>10.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3020,31 +3020,31 @@
         <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
         <v>11.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
@@ -3112,7 +3112,7 @@
         <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
         <v>2.18</v>
@@ -3127,7 +3127,7 @@
         <v>2.96</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
         <v>2.16</v>
@@ -3136,7 +3136,7 @@
         <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
         <v>18.5</v>
@@ -3175,7 +3175,7 @@
         <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK14" t="n">
         <v>18</v>
@@ -3193,28 +3193,28 @@
         <v>290</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
@@ -3226,7 +3226,7 @@
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3238,17 +3238,17 @@
         <v>14.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.84</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
         <v>5.2</v>
@@ -3294,7 +3294,7 @@
         <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>1.45</v>
@@ -3303,40 +3303,40 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
         <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
         <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z15" t="n">
         <v>100</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
         <v>8.4</v>
@@ -3354,19 +3354,19 @@
         <v>38</v>
       </c>
       <c r="AE15" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
         <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
         <v>48</v>
@@ -3381,34 +3381,34 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
         <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -3420,29 +3420,29 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
         <v>18</v>
       </c>
       <c r="BC15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD15" t="n">
         <v>18.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>18</v>
       </c>
       <c r="BE15" t="n">
         <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3479,52 +3479,52 @@
         <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K16" t="n">
         <v>9.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X16" t="n">
         <v>32</v>
@@ -3539,13 +3539,13 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3569,19 +3569,19 @@
         <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.2</v>
@@ -3593,7 +3593,7 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU16" t="n">
         <v>6.4</v>
@@ -3605,38 +3605,38 @@
         <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.52</v>
+        <v>3.35</v>
       </c>
       <c r="BA16" t="n">
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>3.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
@@ -3691,7 +3691,7 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>1.32</v>
@@ -3700,7 +3700,7 @@
         <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R17" t="n">
         <v>1.35</v>
@@ -3709,13 +3709,13 @@
         <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W17" t="n">
         <v>1.16</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9.6</v>
@@ -3745,10 +3745,10 @@
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
@@ -3772,16 +3772,16 @@
         <v>700</v>
       </c>
       <c r="AO17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>13.5</v>
@@ -3799,38 +3799,38 @@
         <v>15.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
         <v>2.54</v>
       </c>
       <c r="H18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I18" t="n">
         <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
@@ -3891,10 +3891,10 @@
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.55</v>
@@ -3909,7 +3909,7 @@
         <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
         <v>1.64</v>
@@ -3918,7 +3918,7 @@
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
         <v>23</v>
@@ -3936,13 +3936,13 @@
         <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
         <v>18.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
@@ -3954,7 +3954,7 @@
         <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>32</v>
@@ -3966,7 +3966,7 @@
         <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
@@ -3975,7 +3975,7 @@
         <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
         <v>38</v>
@@ -4017,14 +4017,14 @@
         <v>44</v>
       </c>
       <c r="BF18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG18" t="n">
         <v>17.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>4.3</v>
@@ -4100,13 +4100,13 @@
         <v>1.79</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
         <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
@@ -4169,10 +4169,10 @@
         <v>16.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>8.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4273,22 +4273,22 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
         <v>1.69</v>
@@ -4303,7 +4303,7 @@
         <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
         <v>16</v>
@@ -4339,7 +4339,7 @@
         <v>150</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
         <v>22</v>
@@ -4348,13 +4348,13 @@
         <v>80</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN20" t="n">
         <v>14.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
         <v>15</v>
@@ -4363,10 +4363,10 @@
         <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
         <v>9.800000000000001</v>
@@ -4378,19 +4378,19 @@
         <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BB20" t="n">
         <v>20</v>
@@ -4399,7 +4399,7 @@
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="BE20" t="n">
         <v>22</v>
@@ -4408,11 +4408,11 @@
         <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4443,31 +4443,31 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H21" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.67</v>
@@ -4482,7 +4482,7 @@
         <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T21" t="n">
         <v>2.28</v>
@@ -4491,10 +4491,10 @@
         <v>1.71</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
         <v>7.4</v>
@@ -4509,31 +4509,31 @@
         <v>420</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
         <v>18.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI21" t="n">
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK21" t="n">
         <v>55</v>
@@ -4545,10 +4545,10 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
         <v>6.8</v>
@@ -4563,50 +4563,50 @@
         <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV21" t="n">
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ21" t="n">
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BB21" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC21" t="n">
         <v>42</v>
       </c>
       <c r="BD21" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
         <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BG21" t="n">
         <v>55</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
         <v>3.65</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I22" t="n">
         <v>2.8</v>
@@ -4652,10 +4652,10 @@
         <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="L22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
         <v>1.21</v>
@@ -4664,7 +4664,7 @@
         <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="P22" t="n">
         <v>1.32</v>
@@ -4676,19 +4676,19 @@
         <v>1.11</v>
       </c>
       <c r="S22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
         <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X22" t="n">
         <v>6</v>
@@ -4697,110 +4697,110 @@
         <v>6.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL22" t="n">
         <v>500</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL22" t="n">
+      <c r="AM22" t="n">
         <v>540</v>
       </c>
-      <c r="AM22" t="n">
-        <v>500</v>
-      </c>
       <c r="AN22" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR22" t="n">
         <v>11.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AX22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB22" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BC22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BD22" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BF22" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BG22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G23" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J23" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.52</v>
@@ -4855,28 +4855,28 @@
         <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="U23" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.42</v>
@@ -4885,10 +4885,10 @@
         <v>1.58</v>
       </c>
       <c r="X23" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
         <v>38</v>
@@ -4897,10 +4897,10 @@
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
         <v>24</v>
@@ -4909,31 +4909,31 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AK23" t="n">
         <v>90</v>
       </c>
       <c r="AL23" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4942,22 +4942,22 @@
         <v>8.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR23" t="n">
         <v>15</v>
       </c>
       <c r="AS23" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU23" t="n">
         <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>18</v>
@@ -4966,35 +4966,35 @@
         <v>14</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
         <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BB23" t="n">
         <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>2.08</v>
       </c>
       <c r="G24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
         <v>3.75</v>
@@ -5070,13 +5070,13 @@
         <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
         <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5127,7 +5127,7 @@
         <v>390</v>
       </c>
       <c r="AN24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO24" t="n">
         <v>60</v>
@@ -5148,7 +5148,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
         <v>14</v>
@@ -5166,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB24" t="n">
         <v>14.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G25" t="n">
         <v>1.93</v>
@@ -5228,13 +5228,13 @@
         <v>3.75</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J25" t="n">
         <v>4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.21</v>
@@ -5249,7 +5249,7 @@
         <v>1.11</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q25" t="n">
         <v>1.36</v>
@@ -5261,19 +5261,19 @@
         <v>1.89</v>
       </c>
       <c r="T25" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
         <v>2.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5306,7 +5306,7 @@
         <v>15</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>130</v>
@@ -5318,28 +5318,28 @@
         <v>170</v>
       </c>
       <c r="AM25" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>6.4</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="AU25" t="n">
         <v>11</v>
@@ -5348,10 +5348,10 @@
         <v>6.8</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
         <v>9.6</v>
@@ -5363,7 +5363,7 @@
         <v>26</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
         <v>13.5</v>
@@ -5375,14 +5375,14 @@
         <v>19</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG25" t="n">
         <v>14</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>4.8</v>
       </c>
       <c r="K26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.22</v>
@@ -5491,13 +5491,13 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>400</v>
+        <v>46</v>
       </c>
       <c r="AG26" t="n">
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5506,7 +5506,7 @@
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5518,65 +5518,65 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP26" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>5.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS26" t="n">
         <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU26" t="n">
         <v>8.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE26" t="n">
         <v>14</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="I27" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
@@ -5631,7 +5631,7 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
         <v>1.18</v>
@@ -5649,7 +5649,7 @@
         <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U27" t="n">
         <v>2.6</v>
@@ -5658,7 +5658,7 @@
         <v>2.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X27" t="n">
         <v>27</v>
@@ -5715,7 +5715,7 @@
         <v>7.8</v>
       </c>
       <c r="AP27" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
@@ -5733,7 +5733,7 @@
         <v>9.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5751,16 +5751,16 @@
         <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BF27" t="n">
         <v>13.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G28" t="n">
         <v>2.1</v>
@@ -5810,13 +5810,13 @@
         <v>4.7</v>
       </c>
       <c r="I28" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L28" t="n">
         <v>1.6</v>
@@ -5825,7 +5825,7 @@
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O28" t="n">
         <v>1.57</v>
@@ -5834,7 +5834,7 @@
         <v>1.51</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R28" t="n">
         <v>1.17</v>
@@ -5849,7 +5849,7 @@
         <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
         <v>1.9</v>
@@ -5876,10 +5876,10 @@
         <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
@@ -5906,10 +5906,10 @@
         <v>32</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
@@ -5918,7 +5918,7 @@
         <v>7.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>5.5</v>
@@ -5930,7 +5930,7 @@
         <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX28" t="n">
         <v>9.199999999999999</v>
@@ -5939,32 +5939,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>2.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H29" t="n">
         <v>3.55</v>
@@ -6007,10 +6007,10 @@
         <v>3.75</v>
       </c>
       <c r="J29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.31</v>
@@ -6019,7 +6019,7 @@
         <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.21</v>
@@ -6028,31 +6028,31 @@
         <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R29" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S29" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U29" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V29" t="n">
         <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z29" t="n">
         <v>500</v>
@@ -6103,16 +6103,16 @@
         <v>500</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AT29" t="n">
         <v>11.5</v>
@@ -6136,16 +6136,16 @@
         <v>13.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB29" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BC29" t="n">
         <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE29" t="n">
         <v>38</v>
@@ -6154,11 +6154,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G30" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H30" t="n">
         <v>7.4</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6258,7 +6258,7 @@
         <v>46</v>
       </c>
       <c r="AC30" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6291,68 +6291,68 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT30" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>4</v>
-      </c>
       <c r="AU30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF30" t="n">
         <v>5.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -6386,19 +6386,19 @@
         <v>3.1</v>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H31" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I31" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>3.25</v>
       </c>
       <c r="K31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.56</v>
@@ -6407,43 +6407,43 @@
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R31" t="n">
         <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X31" t="n">
         <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA31" t="n">
         <v>44</v>
@@ -6458,10 +6458,10 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF31" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
@@ -6476,16 +6476,16 @@
         <v>60</v>
       </c>
       <c r="AK31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL31" t="n">
         <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO31" t="n">
         <v>40</v>
@@ -6494,7 +6494,7 @@
         <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR31" t="n">
         <v>14.5</v>
@@ -6506,7 +6506,7 @@
         <v>8.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>11.5</v>
@@ -6518,7 +6518,7 @@
         <v>17.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ31" t="n">
         <v>20</v>
@@ -6533,20 +6533,20 @@
         <v>36</v>
       </c>
       <c r="BD31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE31" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BF31" t="n">
-        <v>46</v>
+        <v>14.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -6580,10 +6580,10 @@
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H32" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I32" t="n">
         <v>2.76</v>
@@ -6601,28 +6601,28 @@
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V32" t="n">
         <v>1.56</v>
@@ -6631,10 +6631,10 @@
         <v>1.48</v>
       </c>
       <c r="X32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
         <v>17</v>
@@ -6643,7 +6643,7 @@
         <v>42</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC32" t="n">
         <v>7.2</v>
@@ -6652,7 +6652,7 @@
         <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF32" t="n">
         <v>19</v>
@@ -6661,10 +6661,10 @@
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ32" t="n">
         <v>55</v>
@@ -6673,22 +6673,22 @@
         <v>38</v>
       </c>
       <c r="AL32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM32" t="n">
         <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP32" t="n">
         <v>10</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR32" t="n">
         <v>15</v>
@@ -6697,16 +6697,16 @@
         <v>36</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX32" t="n">
         <v>17</v>
@@ -6715,7 +6715,7 @@
         <v>12</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA32" t="n">
         <v>36</v>
@@ -6727,20 +6727,20 @@
         <v>32</v>
       </c>
       <c r="BD32" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BF32" t="n">
         <v>32</v>
       </c>
       <c r="BG32" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H33" t="n">
         <v>3.75</v>
@@ -6798,13 +6798,13 @@
         <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P33" t="n">
         <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
         <v>1.26</v>
@@ -6816,13 +6816,13 @@
         <v>1.95</v>
       </c>
       <c r="U33" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V33" t="n">
         <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6837,7 +6837,7 @@
         <v>170</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC33" t="n">
         <v>7.6</v>
@@ -6876,7 +6876,7 @@
         <v>26</v>
       </c>
       <c r="AO33" t="n">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AP33" t="n">
         <v>9.6</v>
@@ -6888,7 +6888,7 @@
         <v>20</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AT33" t="n">
         <v>7.6</v>
@@ -6900,7 +6900,7 @@
         <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX33" t="n">
         <v>11</v>
@@ -6909,13 +6909,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ33" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BB33" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BC33" t="n">
         <v>23</v>
@@ -6924,7 +6924,7 @@
         <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF33" t="n">
         <v>20</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G34" t="n">
         <v>4.3</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I34" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J34" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K34" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L34" t="n">
         <v>1.49</v>
@@ -6998,7 +6998,7 @@
         <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R34" t="n">
         <v>1.27</v>
@@ -7013,7 +7013,7 @@
         <v>1.9</v>
       </c>
       <c r="V34" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="W34" t="n">
         <v>1.3</v>
@@ -7025,7 +7025,7 @@
         <v>7.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA34" t="n">
         <v>25</v>
@@ -7040,7 +7040,7 @@
         <v>10.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF34" t="n">
         <v>32</v>
@@ -7067,7 +7067,7 @@
         <v>580</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AO34" t="n">
         <v>19.5</v>
@@ -7106,29 +7106,29 @@
         <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB34" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD34" t="n">
         <v>13</v>
       </c>
-      <c r="BC34" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BE34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF34" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>12.5</v>
       </c>
       <c r="BG34" t="n">
         <v>16.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G35" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H35" t="n">
         <v>3.2</v>
@@ -7171,10 +7171,10 @@
         <v>3.35</v>
       </c>
       <c r="J35" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L35" t="n">
         <v>1.5</v>
@@ -7183,19 +7183,19 @@
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
         <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
         <v>4.3</v>
@@ -7204,13 +7204,13 @@
         <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V35" t="n">
         <v>1.42</v>
       </c>
       <c r="W35" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X35" t="n">
         <v>10</v>
@@ -7261,68 +7261,68 @@
         <v>500</v>
       </c>
       <c r="AN35" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO35" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP35" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ35" t="n">
         <v>10</v>
       </c>
       <c r="AR35" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AS35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT35" t="n">
         <v>9</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
         <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX35" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY35" t="n">
         <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC35" t="n">
         <v>14.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE35" t="n">
         <v>10</v>
       </c>
       <c r="BF35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG35" t="n">
         <v>9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -7356,13 +7356,13 @@
         <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J36" t="n">
         <v>4.2</v>
@@ -7395,31 +7395,31 @@
         <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U36" t="n">
         <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W36" t="n">
         <v>2.42</v>
       </c>
       <c r="X36" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y36" t="n">
         <v>40</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA36" t="n">
         <v>900</v>
       </c>
       <c r="AB36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC36" t="n">
         <v>9.199999999999999</v>
@@ -7428,7 +7428,7 @@
         <v>44</v>
       </c>
       <c r="AE36" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
         <v>10.5</v>
@@ -7446,7 +7446,7 @@
         <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL36" t="n">
         <v>95</v>
@@ -7455,7 +7455,7 @@
         <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
@@ -7470,7 +7470,7 @@
         <v>20</v>
       </c>
       <c r="AS36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT36" t="n">
         <v>7.6</v>
@@ -7491,10 +7491,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB36" t="n">
         <v>14</v>
@@ -7506,17 +7506,17 @@
         <v>18</v>
       </c>
       <c r="BE36" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF36" t="n">
         <v>8.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -7553,49 +7553,49 @@
         <v>4.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I37" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K37" t="n">
         <v>3.65</v>
       </c>
-      <c r="K37" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L37" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P37" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T37" t="n">
         <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W37" t="n">
         <v>1.29</v>
@@ -7607,40 +7607,40 @@
         <v>8.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB37" t="n">
         <v>14.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD37" t="n">
         <v>10.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH37" t="n">
         <v>19</v>
       </c>
       <c r="AI37" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ37" t="n">
         <v>95</v>
       </c>
       <c r="AK37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL37" t="n">
         <v>65</v>
@@ -7652,7 +7652,7 @@
         <v>65</v>
       </c>
       <c r="AO37" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP37" t="n">
         <v>12.5</v>
@@ -7688,10 +7688,10 @@
         <v>18</v>
       </c>
       <c r="BA37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB37" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BC37" t="n">
         <v>50</v>
@@ -7706,11 +7706,11 @@
         <v>55</v>
       </c>
       <c r="BG37" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G38" t="n">
         <v>2.5</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I38" t="n">
         <v>3.3</v>
@@ -7756,31 +7756,31 @@
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L38" t="n">
         <v>1.36</v>
       </c>
       <c r="M38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N38" t="n">
         <v>4.4</v>
       </c>
       <c r="O38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P38" t="n">
         <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R38" t="n">
         <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T38" t="n">
         <v>1.64</v>
@@ -7843,68 +7843,68 @@
         <v>580</v>
       </c>
       <c r="AN38" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO38" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP38" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU38" t="n">
         <v>5.1</v>
       </c>
       <c r="AV38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AX38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
         <v>6.8</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="BB38" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG38" t="n">
         <v>6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -7959,16 +7959,16 @@
         <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P39" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R39" t="n">
         <v>1.35</v>
@@ -7977,7 +7977,7 @@
         <v>3.7</v>
       </c>
       <c r="T39" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U39" t="n">
         <v>2</v>
@@ -7992,7 +7992,7 @@
         <v>14</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z39" t="n">
         <v>42</v>
@@ -8004,7 +8004,7 @@
         <v>8</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
         <v>21</v>
@@ -8037,7 +8037,7 @@
         <v>130</v>
       </c>
       <c r="AN39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO39" t="n">
         <v>110</v>
@@ -8046,7 +8046,7 @@
         <v>13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR39" t="n">
         <v>38</v>
@@ -8058,7 +8058,7 @@
         <v>7.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV39" t="n">
         <v>19.5</v>
@@ -8082,7 +8082,7 @@
         <v>16.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD39" t="n">
         <v>34</v>
@@ -8094,11 +8094,11 @@
         <v>10.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -8132,19 +8132,19 @@
         <v>2.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H40" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L40" t="n">
         <v>1.56</v>
@@ -8162,7 +8162,7 @@
         <v>1.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R40" t="n">
         <v>1.21</v>
@@ -8180,7 +8180,7 @@
         <v>1.32</v>
       </c>
       <c r="W40" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X40" t="n">
         <v>9.4</v>
@@ -8207,7 +8207,7 @@
         <v>370</v>
       </c>
       <c r="AF40" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AG40" t="n">
         <v>12</v>
@@ -8246,13 +8246,13 @@
         <v>22</v>
       </c>
       <c r="AS40" t="n">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="AT40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU40" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>6.2</v>
       </c>
       <c r="AV40" t="n">
         <v>14.5</v>
@@ -8270,29 +8270,29 @@
         <v>19</v>
       </c>
       <c r="BA40" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB40" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="BC40" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H41" t="n">
         <v>6.2</v>
@@ -8341,31 +8341,31 @@
         <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P41" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R41" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U41" t="n">
         <v>2.12</v>
@@ -8374,7 +8374,7 @@
         <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X41" t="n">
         <v>18.5</v>
@@ -8389,10 +8389,10 @@
         <v>170</v>
       </c>
       <c r="AB41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD41" t="n">
         <v>23</v>
@@ -8401,10 +8401,10 @@
         <v>80</v>
       </c>
       <c r="AF41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG41" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AH41" t="n">
         <v>20</v>
@@ -8413,7 +8413,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK41" t="n">
         <v>15.5</v>
@@ -8425,19 +8425,19 @@
         <v>95</v>
       </c>
       <c r="AN41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO41" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP41" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>21</v>
       </c>
       <c r="AR41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS41" t="n">
         <v>140</v>
@@ -8446,7 +8446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU41" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV41" t="n">
         <v>21</v>
@@ -8458,10 +8458,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA41" t="n">
         <v>70</v>
@@ -8479,14 +8479,14 @@
         <v>90</v>
       </c>
       <c r="BF41" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -8541,10 +8541,10 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P42" t="n">
         <v>2.02</v>
@@ -8553,16 +8553,16 @@
         <v>1.94</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
         <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U42" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V42" t="n">
         <v>1.27</v>
@@ -8631,10 +8631,10 @@
         <v>13.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT42" t="n">
         <v>8.4</v>
@@ -8643,10 +8643,10 @@
         <v>7.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX42" t="n">
         <v>10</v>
@@ -8655,32 +8655,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB42" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF42" t="n">
         <v>11</v>
       </c>
       <c r="BG42" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G43" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H43" t="n">
         <v>4.6</v>
@@ -8726,10 +8726,10 @@
         <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L43" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
@@ -8744,7 +8744,7 @@
         <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -8753,16 +8753,16 @@
         <v>3.6</v>
       </c>
       <c r="T43" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U43" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V43" t="n">
         <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X43" t="n">
         <v>32</v>
@@ -8789,7 +8789,7 @@
         <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG43" t="n">
         <v>10</v>
@@ -8801,7 +8801,7 @@
         <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK43" t="n">
         <v>1000</v>
@@ -8816,65 +8816,65 @@
         <v>85</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP43" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>9.199999999999999</v>
+        <v>2.74</v>
       </c>
       <c r="AT43" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU43" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AW43" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="AX43" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY43" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ43" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="BA43" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="BB43" t="n">
         <v>6.8</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="BF43" t="n">
         <v>10</v>
       </c>
       <c r="BG43" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
         <v>2.86</v>
       </c>
       <c r="I44" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J44" t="n">
         <v>3.3</v>
@@ -8941,19 +8941,19 @@
         <v>2.38</v>
       </c>
       <c r="R44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
         <v>4.7</v>
       </c>
       <c r="T44" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>1.96</v>
       </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W44" t="n">
         <v>1.54</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -9102,61 +9102,61 @@
         <v>1.79</v>
       </c>
       <c r="G45" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H45" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I45" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L45" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M45" t="n">
         <v>1.13</v>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O45" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P45" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="R45" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S45" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="U45" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V45" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W45" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X45" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y45" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z45" t="n">
         <v>1000</v>
@@ -9165,7 +9165,7 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AC45" t="n">
         <v>8.4</v>
@@ -9180,10 +9180,10 @@
         <v>9.6</v>
       </c>
       <c r="AG45" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
         <v>1000</v>
@@ -9201,13 +9201,13 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ45" t="n">
         <v>11</v>
@@ -9219,10 +9219,10 @@
         <v>10</v>
       </c>
       <c r="AT45" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU45" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV45" t="n">
         <v>20</v>
@@ -9234,10 +9234,10 @@
         <v>8</v>
       </c>
       <c r="AY45" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ45" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="BA45" t="n">
         <v>10</v>
@@ -9246,7 +9246,7 @@
         <v>18</v>
       </c>
       <c r="BC45" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BD45" t="n">
         <v>9.4</v>
@@ -9255,14 +9255,14 @@
         <v>10.5</v>
       </c>
       <c r="BF45" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G46" t="n">
         <v>2.58</v>
@@ -9302,13 +9302,13 @@
         <v>3.3</v>
       </c>
       <c r="I46" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>3.1</v>
       </c>
       <c r="K46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L46" t="n">
         <v>1.5</v>
@@ -9317,22 +9317,22 @@
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O46" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="P46" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T46" t="n">
         <v>1.9</v>
@@ -9395,7 +9395,7 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
@@ -9410,7 +9410,7 @@
         <v>20</v>
       </c>
       <c r="AS46" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -9434,7 +9434,7 @@
         <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB46" t="n">
         <v>13</v>
@@ -9449,14 +9449,14 @@
         <v>9</v>
       </c>
       <c r="BF46" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G47" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H47" t="n">
         <v>4.2</v>
@@ -9499,10 +9499,10 @@
         <v>4.4</v>
       </c>
       <c r="J47" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K47" t="n">
         <v>2.96</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.05</v>
       </c>
       <c r="L47" t="n">
         <v>1.7</v>
@@ -9514,13 +9514,13 @@
         <v>2.36</v>
       </c>
       <c r="O47" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P47" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
         <v>1.14</v>
@@ -9529,16 +9529,16 @@
         <v>7.2</v>
       </c>
       <c r="T47" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U47" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V47" t="n">
         <v>1.29</v>
       </c>
       <c r="W47" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X47" t="n">
         <v>7</v>
@@ -9556,10 +9556,10 @@
         <v>6.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE47" t="n">
         <v>500</v>
@@ -9568,19 +9568,19 @@
         <v>12.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH47" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AI47" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AJ47" t="n">
         <v>34</v>
       </c>
       <c r="AK47" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AL47" t="n">
         <v>200</v>
@@ -9616,7 +9616,7 @@
         <v>17.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
@@ -9625,7 +9625,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA47" t="n">
         <v>80</v>
@@ -9634,10 +9634,10 @@
         <v>19.5</v>
       </c>
       <c r="BC47" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BD47" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE47" t="n">
         <v>100</v>
@@ -9646,11 +9646,11 @@
         <v>23</v>
       </c>
       <c r="BG47" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G48" t="n">
         <v>2.64</v>
@@ -9699,7 +9699,7 @@
         <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
@@ -9723,13 +9723,13 @@
         <v>4.4</v>
       </c>
       <c r="T48" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U48" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V48" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W48" t="n">
         <v>1.61</v>
@@ -9771,7 +9771,7 @@
         <v>500</v>
       </c>
       <c r="AJ48" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK48" t="n">
         <v>500</v>
@@ -9798,7 +9798,7 @@
         <v>6.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AT48" t="n">
         <v>4.9</v>
@@ -9810,7 +9810,7 @@
         <v>5.9</v>
       </c>
       <c r="AW48" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AX48" t="n">
         <v>6.2</v>
@@ -9822,19 +9822,19 @@
         <v>6.6</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.52</v>
+        <v>8.4</v>
       </c>
       <c r="BB48" t="n">
         <v>7.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BF48" t="n">
         <v>5.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -9890,13 +9890,13 @@
         <v>4.4</v>
       </c>
       <c r="K49" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L49" t="n">
         <v>1.51</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N49" t="n">
         <v>3.05</v>
@@ -9905,7 +9905,7 @@
         <v>1.46</v>
       </c>
       <c r="P49" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q49" t="n">
         <v>2.4</v>
@@ -9917,10 +9917,10 @@
         <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U49" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V49" t="n">
         <v>1.09</v>
@@ -9935,22 +9935,22 @@
         <v>24</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="AB49" t="n">
         <v>5.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF49" t="n">
         <v>6.8</v>
@@ -9959,28 +9959,28 @@
         <v>11</v>
       </c>
       <c r="AH49" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AI49" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AJ49" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK49" t="n">
         <v>21</v>
       </c>
       <c r="AL49" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AM49" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AN49" t="n">
         <v>11</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="AP49" t="n">
         <v>9.800000000000001</v>
@@ -9989,22 +9989,22 @@
         <v>20</v>
       </c>
       <c r="AR49" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AS49" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU49" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV49" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AW49" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AX49" t="n">
         <v>6.2</v>
@@ -10013,10 +10013,10 @@
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BA49" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BB49" t="n">
         <v>10.5</v>
@@ -10025,20 +10025,20 @@
         <v>18</v>
       </c>
       <c r="BD49" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BE49" t="n">
         <v>100</v>
       </c>
       <c r="BF49" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG49" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -10072,10 +10072,10 @@
         <v>2.94</v>
       </c>
       <c r="G50" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I50" t="n">
         <v>2.74</v>
@@ -10111,10 +10111,10 @@
         <v>3.95</v>
       </c>
       <c r="T50" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U50" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V50" t="n">
         <v>1.57</v>
@@ -10123,7 +10123,7 @@
         <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y50" t="n">
         <v>10.5</v>
@@ -10171,13 +10171,13 @@
         <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO50" t="n">
         <v>30</v>
       </c>
       <c r="AP50" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ50" t="n">
         <v>9.6</v>
@@ -10186,7 +10186,7 @@
         <v>16</v>
       </c>
       <c r="AS50" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT50" t="n">
         <v>10</v>
@@ -10198,7 +10198,7 @@
         <v>11</v>
       </c>
       <c r="AW50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX50" t="n">
         <v>17.5</v>
@@ -10225,14 +10225,14 @@
         <v>30</v>
       </c>
       <c r="BF50" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BG50" t="n">
         <v>25</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G51" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H51" t="n">
         <v>3.15</v>
@@ -10275,7 +10275,7 @@
         <v>3.4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K51" t="n">
         <v>3.3</v>
@@ -10314,13 +10314,13 @@
         <v>1.41</v>
       </c>
       <c r="W51" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X51" t="n">
         <v>22</v>
       </c>
       <c r="Y51" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z51" t="n">
         <v>1000</v>
@@ -10347,7 +10347,7 @@
         <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI51" t="n">
         <v>1000</v>
@@ -10371,7 +10371,7 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ51" t="n">
         <v>9.4</v>
@@ -10386,7 +10386,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU51" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV51" t="n">
         <v>8.4</v>
@@ -10404,10 +10404,10 @@
         <v>7.6</v>
       </c>
       <c r="BA51" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC51" t="n">
         <v>9.199999999999999</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
         <v>3.35</v>
       </c>
       <c r="L52" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M52" t="n">
         <v>1.11</v>
@@ -10514,7 +10514,7 @@
         <v>17.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z52" t="n">
         <v>500</v>
@@ -10553,7 +10553,7 @@
         <v>110</v>
       </c>
       <c r="AL52" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AM52" t="n">
         <v>580</v>
@@ -10565,62 +10565,62 @@
         <v>500</v>
       </c>
       <c r="AP52" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ52" t="n">
         <v>6.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS52" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT52" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU52" t="n">
         <v>6.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="AX52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA52" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY52" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BB52" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC52" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BD52" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF52" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG52" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G53" t="n">
         <v>2.26</v>
@@ -10666,7 +10666,7 @@
         <v>3.35</v>
       </c>
       <c r="K53" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L53" t="n">
         <v>1.47</v>
@@ -10693,7 +10693,7 @@
         <v>4.2</v>
       </c>
       <c r="T53" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U53" t="n">
         <v>1.96</v>
@@ -10720,7 +10720,7 @@
         <v>16.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD53" t="n">
         <v>1000</v>
@@ -10765,10 +10765,10 @@
         <v>6.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT53" t="n">
         <v>4.9</v>
@@ -10780,7 +10780,7 @@
         <v>9</v>
       </c>
       <c r="AW53" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX53" t="n">
         <v>6.4</v>
@@ -10789,32 +10789,32 @@
         <v>7</v>
       </c>
       <c r="AZ53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA53" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB53" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC53" t="n">
         <v>6.6</v>
       </c>
       <c r="BD53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG53" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -10869,25 +10869,25 @@
         <v>1.06</v>
       </c>
       <c r="N54" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O54" t="n">
         <v>1.29</v>
       </c>
       <c r="P54" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R54" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S54" t="n">
         <v>3.25</v>
       </c>
       <c r="T54" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U54" t="n">
         <v>2.02</v>
@@ -10899,10 +10899,10 @@
         <v>2.52</v>
       </c>
       <c r="X54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Z54" t="n">
         <v>230</v>
@@ -10917,10 +10917,10 @@
         <v>9.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AE54" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF54" t="n">
         <v>10</v>
@@ -10929,19 +10929,19 @@
         <v>10</v>
       </c>
       <c r="AH54" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AI54" t="n">
         <v>700</v>
       </c>
       <c r="AJ54" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="AK54" t="n">
         <v>17.5</v>
       </c>
       <c r="AL54" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AM54" t="n">
         <v>580</v>
@@ -10953,19 +10953,19 @@
         <v>700</v>
       </c>
       <c r="AP54" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ54" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AR54" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="AS54" t="n">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="AT54" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU54" t="n">
         <v>8.6</v>
@@ -10974,19 +10974,19 @@
         <v>20</v>
       </c>
       <c r="AW54" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="AX54" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY54" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA54" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="BB54" t="n">
         <v>14</v>
@@ -10995,20 +10995,20 @@
         <v>15</v>
       </c>
       <c r="BD54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BE54" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="BF54" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG54" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G55" t="n">
         <v>2.92</v>
@@ -11102,13 +11102,13 @@
         <v>22</v>
       </c>
       <c r="AA55" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC55" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD55" t="n">
         <v>16.5</v>
@@ -11144,19 +11144,19 @@
         <v>65</v>
       </c>
       <c r="AO55" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP55" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="AQ55" t="n">
         <v>7.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT55" t="n">
         <v>7.2</v>
@@ -11165,44 +11165,44 @@
         <v>6.2</v>
       </c>
       <c r="AV55" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="AX55" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB55" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC55" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF55" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -11233,170 +11233,170 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="I56" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O56" t="n">
         <v>1.58</v>
       </c>
-      <c r="M56" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.53</v>
-      </c>
       <c r="P56" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R56" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S56" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="T56" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U56" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V56" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W56" t="n">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="X56" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB56" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC56" t="n">
         <v>8.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF56" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG56" t="n">
         <v>13</v>
       </c>
       <c r="AH56" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ56" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AK56" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL56" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP56" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR56" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AT56" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU56" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV56" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AW56" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX56" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY56" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ56" t="n">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="BA56" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BB56" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC56" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BF56" t="n">
         <v>16</v>
       </c>
       <c r="BG56" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-16.xlsx
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:31:26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Kastamonuspor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76 Igdir Belediyespor</t>
+          <t>Beyoglu Yeni Carsi</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>1.99</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>19</v>
-      </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AB2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>550</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>550</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT2" t="n">
         <v>12</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>80</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:31:41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kastamonuspor</t>
+          <t>Karaman Belediyespor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beyoglu Yeni Carsi</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>14.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92</v>
+        <v>270</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>15.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="P3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>12.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>210</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>990</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>2.22</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AY3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AT3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:31:55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sanliurfaspor</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Altinordu</t>
+          <t>76 Igdir Belediyespor</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.35</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="P4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>9.6</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AR4" t="n">
         <v>14</v>
       </c>
-      <c r="AD4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AS4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AZ4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AL4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
       <c r="BA4" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>27</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:32:10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Karaman Belediyespor</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Altinordu</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17.5</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>9.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.15</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>6.8</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.4</v>
+        <v>110</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>480</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AE5" t="n">
-        <v>18.5</v>
+        <v>170</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>70</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>80</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>150</v>
+        <v>5.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.26</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
         <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V6" t="n">
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="AW6" t="n">
         <v>5.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC6" t="n">
         <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.6</v>
+        <v>110</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.45</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AT7" t="n">
         <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BA7" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>27</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1921,52 +1921,52 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V8" t="n">
         <v>1.04</v>
@@ -1975,10 +1975,10 @@
         <v>4.8</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL8" t="n">
         <v>70</v>
@@ -2023,46 +2023,46 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
         <v>4.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AY8" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA8" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -2071,20 +2071,20 @@
         <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2133,34 +2133,34 @@
         <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
         <v>3.5</v>
@@ -2169,16 +2169,16 @@
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AB9" t="n">
         <v>34</v>
@@ -2199,7 +2199,7 @@
         <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>36</v>
@@ -2220,7 +2220,7 @@
         <v>200</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
@@ -2247,38 +2247,38 @@
         <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>18.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
         <v>28</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>13</v>
       </c>
       <c r="BE9" t="n">
         <v>40</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BG9" t="n">
         <v>4.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
@@ -2321,7 +2321,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2333,19 +2333,19 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
         <v>3.4</v>
@@ -2354,34 +2354,34 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AE10" t="n">
         <v>400</v>
@@ -2399,61 +2399,61 @@
         <v>320</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
         <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS10" t="n">
         <v>10</v>
       </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT10" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC10" t="n">
         <v>15</v>
@@ -2462,17 +2462,17 @@
         <v>18.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2503,37 +2503,37 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
         <v>2.5</v>
@@ -2542,52 +2542,52 @@
         <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="n">
         <v>700</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AS11" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>48</v>
+        <v>9.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G12" t="n">
         <v>2.02</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -2727,58 +2727,58 @@
         <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="X12" t="n">
         <v>500</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
         <v>16</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>16</v>
@@ -2787,37 +2787,37 @@
         <v>32</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12" t="n">
         <v>40</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AO12" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
@@ -2826,10 +2826,10 @@
         <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY12" t="n">
         <v>5.7</v>
@@ -2838,29 +2838,29 @@
         <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG12" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G13" t="n">
         <v>4.6</v>
@@ -2906,34 +2906,34 @@
         <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.33</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
         <v>2.08</v>
@@ -2942,34 +2942,34 @@
         <v>1.98</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
         <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AG13" t="n">
         <v>32</v>
@@ -2981,7 +2981,7 @@
         <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
         <v>34</v>
@@ -3002,10 +3002,10 @@
         <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
         <v>10.5</v>
@@ -3014,7 +3014,7 @@
         <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>6.4</v>
@@ -3023,28 +3023,28 @@
         <v>10.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
         <v>20</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>11.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -3097,13 +3097,13 @@
         <v>5.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3115,37 +3115,37 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.78</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.74</v>
-      </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3160,7 +3160,7 @@
         <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AF14" t="n">
         <v>12</v>
@@ -3184,7 +3184,7 @@
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
         <v>10.5</v>
@@ -3199,7 +3199,7 @@
         <v>18</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AS14" t="n">
         <v>9.6</v>
@@ -3208,7 +3208,7 @@
         <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
         <v>17.5</v>
@@ -3223,10 +3223,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3238,17 +3238,17 @@
         <v>14.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
         <v>50</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
         <v>1.9</v>
@@ -3294,37 +3294,37 @@
         <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
         <v>2.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T15" t="n">
         <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
         <v>1.23</v>
@@ -3333,7 +3333,7 @@
         <v>2.1</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y15" t="n">
         <v>17.5</v>
@@ -3345,16 +3345,16 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
         <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF15" t="n">
         <v>11</v>
@@ -3363,40 +3363,40 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ15" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
         <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
         <v>7.2</v>
@@ -3408,7 +3408,7 @@
         <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -3417,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
         <v>28</v>
@@ -3432,7 +3432,7 @@
         <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF15" t="n">
         <v>12</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3479,13 +3479,13 @@
         <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="K16" t="n">
         <v>9.4</v>
@@ -3497,34 +3497,34 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X16" t="n">
         <v>32</v>
@@ -3557,7 +3557,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3581,7 +3581,7 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.2</v>
@@ -3593,10 +3593,10 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
         <v>4.2</v>
@@ -3617,7 +3617,7 @@
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC16" t="n">
         <v>7.4</v>
@@ -3629,14 +3629,14 @@
         <v>3.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.42</v>
@@ -3691,34 +3691,34 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.99</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>14.5</v>
@@ -3733,31 +3733,31 @@
         <v>16.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
         <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF17" t="n">
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>400</v>
@@ -3772,25 +3772,25 @@
         <v>700</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
         <v>13.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
         <v>8.800000000000001</v>
@@ -3799,10 +3799,10 @@
         <v>15.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>18.5</v>
@@ -3811,26 +3811,26 @@
         <v>32</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE17" t="n">
         <v>9.4</v>
       </c>
-      <c r="BD17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE17" t="n">
+      <c r="BF17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG17" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G18" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.33</v>
@@ -3891,10 +3891,10 @@
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
         <v>1.55</v>
@@ -3906,13 +3906,13 @@
         <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V18" t="n">
         <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3924,16 +3924,16 @@
         <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>32</v>
@@ -3951,10 +3951,10 @@
         <v>36</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
         <v>32</v>
@@ -3969,7 +3969,7 @@
         <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
         <v>14.5</v>
@@ -3981,7 +3981,7 @@
         <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3993,7 +3993,7 @@
         <v>24</v>
       </c>
       <c r="AX18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
         <v>10.5</v>
@@ -4002,7 +4002,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
@@ -4011,20 +4011,20 @@
         <v>21</v>
       </c>
       <c r="BD18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BF18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4055,28 +4055,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
         <v>4.2</v>
@@ -4085,140 +4085,140 @@
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
         <v>9.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>21</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>19</v>
       </c>
       <c r="AK19" t="n">
         <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="AP19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
         <v>16.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC19" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>15</v>
-      </c>
       <c r="BD19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4252,22 +4252,22 @@
         <v>2.12</v>
       </c>
       <c r="G20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I20" t="n">
         <v>3.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4276,16 +4276,16 @@
         <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
         <v>3.1</v>
@@ -4294,25 +4294,25 @@
         <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
         <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
         <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
@@ -4324,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF20" t="n">
         <v>15</v>
@@ -4336,7 +4336,7 @@
         <v>17.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
         <v>28</v>
@@ -4345,10 +4345,10 @@
         <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN20" t="n">
         <v>14.5</v>
@@ -4393,7 +4393,7 @@
         <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC20" t="n">
         <v>18.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I21" t="n">
         <v>2.92</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>2.92</v>
@@ -4467,67 +4467,67 @@
         <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
         <v>1.67</v>
       </c>
       <c r="P21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
         <v>1.71</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X21" t="n">
         <v>7.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z21" t="n">
         <v>17.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>420</v>
+        <v>60</v>
       </c>
       <c r="AB21" t="n">
         <v>8</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI21" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="n">
         <v>600</v>
@@ -4554,31 +4554,31 @@
         <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AT21" t="n">
         <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>23</v>
@@ -4587,26 +4587,26 @@
         <v>48</v>
       </c>
       <c r="BB21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC21" t="n">
         <v>42</v>
       </c>
       <c r="BD21" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE21" t="n">
         <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BG21" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J22" t="n">
         <v>2.72</v>
       </c>
-      <c r="I22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.78</v>
-      </c>
       <c r="K22" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="L22" t="n">
         <v>1.82</v>
@@ -4664,25 +4664,25 @@
         <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="P22" t="n">
         <v>1.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
         <v>1.11</v>
       </c>
       <c r="S22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="T22" t="n">
         <v>2.68</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
         <v>1.55</v>
@@ -4697,10 +4697,10 @@
         <v>6.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB22" t="n">
         <v>8.199999999999999</v>
@@ -4712,61 +4712,61 @@
         <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="n">
         <v>24</v>
       </c>
       <c r="AG22" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AI22" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AJ22" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK22" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM22" t="n">
         <v>540</v>
       </c>
       <c r="AN22" t="n">
-        <v>490</v>
+        <v>600</v>
       </c>
       <c r="AO22" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>5.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
         <v>17</v>
@@ -4778,16 +4778,16 @@
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB22" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BC22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BD22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BE22" t="n">
         <v>100</v>
@@ -4796,11 +4796,11 @@
         <v>50</v>
       </c>
       <c r="BG22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
         <v>2.72</v>
@@ -4840,13 +4840,13 @@
         <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.52</v>
@@ -4858,13 +4858,13 @@
         <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
@@ -4873,10 +4873,10 @@
         <v>4.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>1.42</v>
@@ -4909,10 +4909,10 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>32</v>
@@ -4936,10 +4936,10 @@
         <v>500</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
         <v>9.199999999999999</v>
@@ -4948,7 +4948,7 @@
         <v>15</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT23" t="n">
         <v>7.8</v>
@@ -4969,32 +4969,32 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE23" t="n">
         <v>11</v>
       </c>
-      <c r="BA23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BF23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.08</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
@@ -5049,19 +5049,19 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
         <v>3.6</v>
@@ -5076,7 +5076,7 @@
         <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5088,7 +5088,7 @@
         <v>29</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="AB24" t="n">
         <v>9.4</v>
@@ -5100,7 +5100,7 @@
         <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
         <v>13.5</v>
@@ -5127,7 +5127,7 @@
         <v>390</v>
       </c>
       <c r="AN24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO24" t="n">
         <v>60</v>
@@ -5139,10 +5139,10 @@
         <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AT24" t="n">
         <v>8.199999999999999</v>
@@ -5154,7 +5154,7 @@
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AX24" t="n">
         <v>11</v>
@@ -5166,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
         <v>14.5</v>
@@ -5175,20 +5175,20 @@
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
         <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG24" t="n">
         <v>9.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G25" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H25" t="n">
         <v>3.75</v>
@@ -5231,7 +5231,7 @@
         <v>3.95</v>
       </c>
       <c r="J25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K25" t="n">
         <v>4.7</v>
@@ -5243,37 +5243,37 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P25" t="n">
         <v>3.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S25" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5285,10 +5285,10 @@
         <v>500</v>
       </c>
       <c r="AB25" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
         <v>34</v>
@@ -5303,7 +5303,7 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5318,71 +5318,71 @@
         <v>170</v>
       </c>
       <c r="AM25" t="n">
-        <v>580</v>
+        <v>38</v>
       </c>
       <c r="AN25" t="n">
         <v>6.4</v>
       </c>
       <c r="AO25" t="n">
-        <v>220</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT25" t="n">
         <v>18.5</v>
       </c>
       <c r="AU25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>11</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>12</v>
       </c>
       <c r="BA25" t="n">
         <v>26</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BE25" t="n">
         <v>19</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG25" t="n">
         <v>14</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5419,13 +5419,13 @@
         <v>1.65</v>
       </c>
       <c r="H26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I26" t="n">
         <v>5.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K26" t="n">
         <v>5.2</v>
@@ -5437,25 +5437,25 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R26" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S26" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U26" t="n">
         <v>2.78</v>
@@ -5467,7 +5467,7 @@
         <v>2.52</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Y26" t="n">
         <v>1000</v>
@@ -5494,10 +5494,10 @@
         <v>46</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5506,7 +5506,7 @@
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AO26" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
         <v>28</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU26" t="n">
         <v>8.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AZ26" t="n">
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE26" t="n">
         <v>14</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v>1.57</v>
       </c>
       <c r="U27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V27" t="n">
         <v>2.16</v>
@@ -5697,7 +5697,7 @@
         <v>27</v>
       </c>
       <c r="AJ27" t="n">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="AK27" t="n">
         <v>44</v>
@@ -5739,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AY27" t="n">
         <v>15.5</v>
@@ -5751,10 +5751,10 @@
         <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>30</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G28" t="n">
         <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K28" t="n">
         <v>3.45</v>
@@ -5825,7 +5825,7 @@
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.57</v>
@@ -5837,7 +5837,7 @@
         <v>2.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
         <v>5.7</v>
@@ -5846,19 +5846,19 @@
         <v>2.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V28" t="n">
         <v>1.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X28" t="n">
         <v>8.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
         <v>40</v>
@@ -5891,7 +5891,7 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK28" t="n">
         <v>30</v>
@@ -5903,10 +5903,10 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
         <v>7.2</v>
@@ -5915,10 +5915,10 @@
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT28" t="n">
         <v>5.5</v>
@@ -5930,7 +5930,7 @@
         <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX28" t="n">
         <v>9.199999999999999</v>
@@ -5939,32 +5939,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BE28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG28" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I29" t="n">
         <v>3.75</v>
@@ -6013,46 +6013,46 @@
         <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
         <v>1.58</v>
       </c>
       <c r="S29" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T29" t="n">
         <v>1.59</v>
       </c>
       <c r="U29" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V29" t="n">
         <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X29" t="n">
         <v>75</v>
       </c>
       <c r="Y29" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>500</v>
@@ -6061,7 +6061,7 @@
         <v>500</v>
       </c>
       <c r="AB29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
@@ -6088,7 +6088,7 @@
         <v>85</v>
       </c>
       <c r="AK29" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL29" t="n">
         <v>500</v>
@@ -6100,19 +6100,19 @@
         <v>10.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP29" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AR29" t="n">
         <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="AT29" t="n">
         <v>11.5</v>
@@ -6133,16 +6133,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA29" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>12</v>
       </c>
       <c r="BC29" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>19.5</v>
@@ -6154,11 +6154,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6198,19 +6198,19 @@
         <v>7.4</v>
       </c>
       <c r="I30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
         <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
         <v>3.4</v>
@@ -6219,7 +6219,7 @@
         <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q30" t="n">
         <v>2.12</v>
@@ -6228,13 +6228,13 @@
         <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T30" t="n">
         <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V30" t="n">
         <v>1.14</v>
@@ -6258,7 +6258,7 @@
         <v>46</v>
       </c>
       <c r="AC30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.83</v>
+        <v>5.7</v>
       </c>
       <c r="AT30" t="n">
         <v>4.2</v>
@@ -6315,10 +6315,10 @@
         <v>4.7</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.87</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
         <v>4.8</v>
@@ -6327,32 +6327,32 @@
         <v>5.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30" t="n">
         <v>5.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>3.1</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H31" t="n">
         <v>2.64</v>
@@ -6395,49 +6395,49 @@
         <v>2.7</v>
       </c>
       <c r="J31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.25</v>
       </c>
-      <c r="K31" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="V31" t="n">
         <v>1.58</v>
       </c>
       <c r="W31" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y31" t="n">
         <v>8.800000000000001</v>
@@ -6449,7 +6449,7 @@
         <v>44</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>7.2</v>
@@ -6458,16 +6458,16 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
         <v>60</v>
@@ -6476,22 +6476,22 @@
         <v>60</v>
       </c>
       <c r="AK31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL31" t="n">
         <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN31" t="n">
         <v>50</v>
       </c>
       <c r="AO31" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
         <v>8.199999999999999</v>
@@ -6503,7 +6503,7 @@
         <v>36</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6515,38 +6515,38 @@
         <v>30</v>
       </c>
       <c r="AX31" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY31" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
         <v>48</v>
       </c>
       <c r="BB31" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BC31" t="n">
         <v>36</v>
       </c>
       <c r="BD31" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="BF31" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="BG31" t="n">
         <v>32</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
         <v>2.7</v>
       </c>
       <c r="I32" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
@@ -6607,7 +6607,7 @@
         <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q32" t="n">
         <v>2.24</v>
@@ -6619,19 +6619,19 @@
         <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W32" t="n">
         <v>1.48</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF32" t="n">
         <v>19</v>
@@ -6703,7 +6703,7 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW32" t="n">
         <v>28</v>
@@ -6715,7 +6715,7 @@
         <v>12</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA32" t="n">
         <v>36</v>
@@ -6727,20 +6727,20 @@
         <v>32</v>
       </c>
       <c r="BD32" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="BG32" t="n">
         <v>27</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>2.28</v>
       </c>
       <c r="H33" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I33" t="n">
         <v>3.95</v>
@@ -6795,37 +6795,37 @@
         <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
         <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q33" t="n">
         <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
         <v>1.95</v>
       </c>
       <c r="U33" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V33" t="n">
         <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
@@ -6837,7 +6837,7 @@
         <v>170</v>
       </c>
       <c r="AB33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
         <v>7.6</v>
@@ -6924,7 +6924,7 @@
         <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF33" t="n">
         <v>20</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6974,13 +6974,13 @@
         <v>2.02</v>
       </c>
       <c r="I34" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L34" t="n">
         <v>1.49</v>
@@ -6995,10 +6995,10 @@
         <v>1.43</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R34" t="n">
         <v>1.27</v>
@@ -7010,10 +7010,10 @@
         <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V34" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W34" t="n">
         <v>1.3</v>
@@ -7028,13 +7028,13 @@
         <v>11.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB34" t="n">
         <v>13</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD34" t="n">
         <v>10.5</v>
@@ -7043,31 +7043,31 @@
         <v>24</v>
       </c>
       <c r="AF34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG34" t="n">
         <v>17.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI34" t="n">
         <v>46</v>
       </c>
       <c r="AJ34" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN34" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AO34" t="n">
         <v>19.5</v>
@@ -7076,13 +7076,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT34" t="n">
         <v>11.5</v>
@@ -7091,44 +7091,44 @@
         <v>7.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX34" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AY34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ34" t="n">
         <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BB34" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BD34" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BF34" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7159,40 +7159,40 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G35" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I35" t="n">
         <v>3.35</v>
       </c>
       <c r="J35" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>3.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P35" t="n">
         <v>1.72</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R35" t="n">
         <v>1.28</v>
@@ -7204,125 +7204,125 @@
         <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V35" t="n">
         <v>1.42</v>
       </c>
       <c r="W35" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB35" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC35" t="n">
         <v>6.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE35" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="AF35" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="AG35" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="AH35" t="n">
         <v>46</v>
       </c>
       <c r="AI35" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AJ35" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK35" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AL35" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AN35" t="n">
-        <v>600</v>
+        <v>32</v>
       </c>
       <c r="AO35" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP35" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ35" t="n">
         <v>10</v>
       </c>
       <c r="AR35" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AS35" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AT35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW35" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AX35" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BB35" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG35" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>9</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H36" t="n">
         <v>5.7</v>
@@ -7365,7 +7365,7 @@
         <v>6.2</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K36" t="n">
         <v>4.4</v>
@@ -7383,10 +7383,10 @@
         <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R36" t="n">
         <v>1.39</v>
@@ -7446,7 +7446,7 @@
         <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL36" t="n">
         <v>95</v>
@@ -7461,13 +7461,13 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS36" t="n">
         <v>13</v>
@@ -7482,7 +7482,7 @@
         <v>19</v>
       </c>
       <c r="AW36" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AX36" t="n">
         <v>8.800000000000001</v>
@@ -7494,7 +7494,7 @@
         <v>12.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BB36" t="n">
         <v>14</v>
@@ -7503,10 +7503,10 @@
         <v>15.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BE36" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BF36" t="n">
         <v>8.6</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G37" t="n">
         <v>4.4</v>
       </c>
       <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
         <v>2.02</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.04</v>
       </c>
       <c r="J37" t="n">
         <v>3.6</v>
@@ -7565,7 +7565,7 @@
         <v>3.65</v>
       </c>
       <c r="L37" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -7577,10 +7577,10 @@
         <v>1.37</v>
       </c>
       <c r="P37" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R37" t="n">
         <v>1.33</v>
@@ -7589,28 +7589,28 @@
         <v>3.9</v>
       </c>
       <c r="T37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
         <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="W37" t="n">
         <v>1.29</v>
       </c>
       <c r="X37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB37" t="n">
         <v>14.5</v>
@@ -7625,10 +7625,10 @@
         <v>22</v>
       </c>
       <c r="AF37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH37" t="n">
         <v>19</v>
@@ -7643,28 +7643,28 @@
         <v>60</v>
       </c>
       <c r="AL37" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM37" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN37" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT37" t="n">
         <v>13</v>
@@ -7679,10 +7679,10 @@
         <v>20</v>
       </c>
       <c r="AX37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY37" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ37" t="n">
         <v>18</v>
@@ -7697,20 +7697,20 @@
         <v>50</v>
       </c>
       <c r="BD37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE37" t="n">
         <v>90</v>
       </c>
       <c r="BF37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG37" t="n">
         <v>15</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.34</v>
       </c>
       <c r="G38" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H38" t="n">
         <v>3.05</v>
@@ -7753,7 +7753,7 @@
         <v>3.3</v>
       </c>
       <c r="J38" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
         <v>3.95</v>
@@ -7771,10 +7771,10 @@
         <v>1.26</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R38" t="n">
         <v>1.45</v>
@@ -7783,13 +7783,13 @@
         <v>2.98</v>
       </c>
       <c r="T38" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U38" t="n">
         <v>2.3</v>
       </c>
       <c r="V38" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W38" t="n">
         <v>1.67</v>
@@ -7849,62 +7849,62 @@
         <v>600</v>
       </c>
       <c r="AP38" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ38" t="n">
         <v>7.2</v>
       </c>
       <c r="AR38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS38" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS38" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AT38" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV38" t="n">
         <v>6.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX38" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY38" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AZ38" t="n">
         <v>6.8</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.3</v>
+        <v>17.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BD38" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF38" t="n">
         <v>7.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7938,10 +7938,10 @@
         <v>1.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H39" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I39" t="n">
         <v>5.7</v>
@@ -7950,10 +7950,10 @@
         <v>3.95</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
         <v>1.07</v>
@@ -7968,7 +7968,7 @@
         <v>1.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R39" t="n">
         <v>1.35</v>
@@ -7986,13 +7986,13 @@
         <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X39" t="n">
         <v>14</v>
       </c>
       <c r="Y39" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z39" t="n">
         <v>42</v>
@@ -8004,7 +8004,7 @@
         <v>8</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
         <v>21</v>
@@ -8025,7 +8025,7 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK39" t="n">
         <v>18.5</v>
@@ -8046,19 +8046,19 @@
         <v>13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR39" t="n">
         <v>38</v>
       </c>
       <c r="AS39" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV39" t="n">
         <v>19.5</v>
@@ -8079,26 +8079,26 @@
         <v>70</v>
       </c>
       <c r="BB39" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD39" t="n">
         <v>34</v>
       </c>
       <c r="BE39" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG39" t="n">
         <v>90</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
         <v>2.36</v>
       </c>
       <c r="H40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I40" t="n">
         <v>4.2</v>
@@ -8168,7 +8168,7 @@
         <v>1.21</v>
       </c>
       <c r="S40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T40" t="n">
         <v>2.06</v>
@@ -8177,7 +8177,7 @@
         <v>1.83</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W40" t="n">
         <v>1.73</v>
@@ -8189,7 +8189,7 @@
         <v>11.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AA40" t="n">
         <v>900</v>
@@ -8201,13 +8201,13 @@
         <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE40" t="n">
         <v>370</v>
       </c>
       <c r="AF40" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AG40" t="n">
         <v>12</v>
@@ -8219,10 +8219,10 @@
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AK40" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL40" t="n">
         <v>1000</v>
@@ -8237,10 +8237,10 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR40" t="n">
         <v>22</v>
@@ -8255,7 +8255,7 @@
         <v>6.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW40" t="n">
         <v>50</v>
@@ -8267,19 +8267,19 @@
         <v>10</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB40" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BC40" t="n">
         <v>15</v>
       </c>
       <c r="BD40" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BE40" t="n">
         <v>10.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.62</v>
       </c>
-      <c r="G41" t="n">
-        <v>1.63</v>
-      </c>
       <c r="H41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
         <v>4.4</v>
@@ -8341,7 +8341,7 @@
         <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
@@ -8353,10 +8353,10 @@
         <v>1.26</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R41" t="n">
         <v>1.47</v>
@@ -8365,34 +8365,34 @@
         <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U41" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V41" t="n">
         <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X41" t="n">
         <v>18.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z41" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA41" t="n">
         <v>170</v>
       </c>
       <c r="AB41" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD41" t="n">
         <v>23</v>
@@ -8401,7 +8401,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG41" t="n">
         <v>9.6</v>
@@ -8422,13 +8422,13 @@
         <v>32</v>
       </c>
       <c r="AM41" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN41" t="n">
         <v>8</v>
       </c>
       <c r="AO41" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP41" t="n">
         <v>17.5</v>
@@ -8437,16 +8437,16 @@
         <v>21</v>
       </c>
       <c r="AR41" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS41" t="n">
         <v>140</v>
       </c>
       <c r="AT41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV41" t="n">
         <v>21</v>
@@ -8461,7 +8461,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA41" t="n">
         <v>70</v>
@@ -8482,11 +8482,11 @@
         <v>7.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G42" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H42" t="n">
         <v>4.4</v>
@@ -8529,16 +8529,16 @@
         <v>4.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K42" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -8547,19 +8547,19 @@
         <v>1.32</v>
       </c>
       <c r="P42" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U42" t="n">
         <v>2.14</v>
@@ -8568,13 +8568,13 @@
         <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X42" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y42" t="n">
         <v>29</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>16.5</v>
       </c>
       <c r="Z42" t="n">
         <v>90</v>
@@ -8583,37 +8583,37 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AK42" t="n">
-        <v>46</v>
+        <v>19.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
         <v>580</v>
@@ -8622,25 +8622,25 @@
         <v>13</v>
       </c>
       <c r="AO42" t="n">
-        <v>260</v>
+        <v>600</v>
       </c>
       <c r="AP42" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AQ42" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR42" t="n">
         <v>15</v>
       </c>
       <c r="AS42" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT42" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV42" t="n">
         <v>16.5</v>
@@ -8652,25 +8652,25 @@
         <v>10</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA42" t="n">
         <v>44</v>
       </c>
       <c r="BB42" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD42" t="n">
         <v>27</v>
       </c>
       <c r="BE42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF42" t="n">
         <v>11</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G43" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L43" t="n">
         <v>1.42</v>
@@ -8741,7 +8741,7 @@
         <v>1.32</v>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q43" t="n">
         <v>2</v>
@@ -8750,19 +8750,19 @@
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T43" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U43" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V43" t="n">
         <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X43" t="n">
         <v>32</v>
@@ -8786,7 +8786,7 @@
         <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF43" t="n">
         <v>40</v>
@@ -8822,13 +8822,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="AT43" t="n">
         <v>7.8</v>
@@ -8837,10 +8837,10 @@
         <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="AX43" t="n">
         <v>6.4</v>
@@ -8849,32 +8849,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ43" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="BB43" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="BD43" t="n">
         <v>10.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BF43" t="n">
         <v>10</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G44" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H44" t="n">
         <v>2.86</v>
@@ -8917,13 +8917,13 @@
         <v>2.96</v>
       </c>
       <c r="J44" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
@@ -8932,10 +8932,10 @@
         <v>3.1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P44" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q44" t="n">
         <v>2.38</v>
@@ -8947,31 +8947,31 @@
         <v>4.7</v>
       </c>
       <c r="T44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U44" t="n">
         <v>2</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.96</v>
       </c>
       <c r="V44" t="n">
         <v>1.51</v>
       </c>
       <c r="W44" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y44" t="n">
         <v>10.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="n">
         <v>340</v>
       </c>
       <c r="AB44" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC44" t="n">
         <v>7.6</v>
@@ -8983,7 +8983,7 @@
         <v>110</v>
       </c>
       <c r="AF44" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AG44" t="n">
         <v>13.5</v>
@@ -8995,25 +8995,25 @@
         <v>290</v>
       </c>
       <c r="AJ44" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AK44" t="n">
         <v>110</v>
       </c>
       <c r="AL44" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AM44" t="n">
         <v>580</v>
       </c>
       <c r="AN44" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AO44" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ44" t="n">
         <v>8.6</v>
@@ -9022,7 +9022,7 @@
         <v>15.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT44" t="n">
         <v>8.199999999999999</v>
@@ -9034,7 +9034,7 @@
         <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AX44" t="n">
         <v>15.5</v>
@@ -9049,26 +9049,26 @@
         <v>44</v>
       </c>
       <c r="BB44" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC44" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BD44" t="n">
         <v>44</v>
       </c>
       <c r="BE44" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF44" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G45" t="n">
         <v>1.89</v>
@@ -9108,13 +9108,13 @@
         <v>5.5</v>
       </c>
       <c r="I45" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J45" t="n">
         <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L45" t="n">
         <v>1.61</v>
@@ -9123,34 +9123,34 @@
         <v>1.13</v>
       </c>
       <c r="N45" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="O45" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P45" t="n">
         <v>1.51</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R45" t="n">
         <v>1.17</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U45" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V45" t="n">
         <v>1.19</v>
       </c>
       <c r="W45" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X45" t="n">
         <v>8.800000000000001</v>
@@ -9246,10 +9246,10 @@
         <v>18</v>
       </c>
       <c r="BC45" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE45" t="n">
         <v>10.5</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G46" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H46" t="n">
         <v>3.3</v>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J46" t="n">
         <v>3.1</v>
@@ -9317,16 +9317,16 @@
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R46" t="n">
         <v>1.24</v>
@@ -9398,7 +9398,7 @@
         <v>60</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP46" t="n">
         <v>9.199999999999999</v>
@@ -9410,7 +9410,7 @@
         <v>20</v>
       </c>
       <c r="AS46" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -9422,7 +9422,7 @@
         <v>12.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX46" t="n">
         <v>12.5</v>
@@ -9434,7 +9434,7 @@
         <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB46" t="n">
         <v>13</v>
@@ -9449,14 +9449,14 @@
         <v>9</v>
       </c>
       <c r="BF46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG46" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -9490,22 +9490,22 @@
         <v>2.3</v>
       </c>
       <c r="G47" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H47" t="n">
         <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="K47" t="n">
         <v>2.96</v>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M47" t="n">
         <v>1.17</v>
@@ -9520,31 +9520,31 @@
         <v>1.42</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
         <v>1.14</v>
       </c>
       <c r="S47" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U47" t="n">
         <v>1.63</v>
       </c>
       <c r="V47" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W47" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X47" t="n">
         <v>7</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
         <v>44</v>
@@ -9559,7 +9559,7 @@
         <v>7.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE47" t="n">
         <v>500</v>
@@ -9568,10 +9568,10 @@
         <v>12.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AI47" t="n">
         <v>420</v>
@@ -9583,16 +9583,16 @@
         <v>65</v>
       </c>
       <c r="AL47" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AM47" t="n">
         <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AO47" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP47" t="n">
         <v>6.2</v>
@@ -9604,7 +9604,7 @@
         <v>24</v>
       </c>
       <c r="AS47" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT47" t="n">
         <v>5.7</v>
@@ -9613,7 +9613,7 @@
         <v>6.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW47" t="n">
         <v>50</v>
@@ -9628,16 +9628,16 @@
         <v>25</v>
       </c>
       <c r="BA47" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="BB47" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BD47" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE47" t="n">
         <v>100</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G48" t="n">
         <v>2.64</v>
@@ -9690,13 +9690,13 @@
         <v>3.2</v>
       </c>
       <c r="I48" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.51</v>
@@ -9705,7 +9705,7 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>1.43</v>
@@ -9720,13 +9720,13 @@
         <v>1.24</v>
       </c>
       <c r="S48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T48" t="n">
         <v>1.91</v>
       </c>
       <c r="U48" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V48" t="n">
         <v>1.4</v>
@@ -9795,22 +9795,22 @@
         <v>6.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AT48" t="n">
         <v>4.9</v>
       </c>
       <c r="AU48" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AV48" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AX48" t="n">
         <v>6.2</v>
@@ -9819,10 +9819,10 @@
         <v>7.6</v>
       </c>
       <c r="AZ48" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BA48" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="BB48" t="n">
         <v>7.6</v>
@@ -9831,10 +9831,10 @@
         <v>5.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BF48" t="n">
         <v>5.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
         <v>4.7</v>
       </c>
       <c r="L49" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -9902,13 +9902,13 @@
         <v>3.05</v>
       </c>
       <c r="O49" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P49" t="n">
         <v>1.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R49" t="n">
         <v>1.24</v>
@@ -9917,13 +9917,13 @@
         <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U49" t="n">
         <v>1.56</v>
       </c>
       <c r="V49" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W49" t="n">
         <v>3.1</v>
@@ -9947,10 +9947,10 @@
         <v>10.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE49" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AF49" t="n">
         <v>6.8</v>
@@ -9965,10 +9965,10 @@
         <v>290</v>
       </c>
       <c r="AJ49" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="n">
         <v>70</v>
@@ -9989,22 +9989,22 @@
         <v>20</v>
       </c>
       <c r="AR49" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AS49" t="n">
         <v>100</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU49" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV49" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AW49" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AX49" t="n">
         <v>6.2</v>
@@ -10013,7 +10013,7 @@
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BA49" t="n">
         <v>110</v>
@@ -10025,20 +10025,20 @@
         <v>18</v>
       </c>
       <c r="BD49" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE49" t="n">
         <v>100</v>
       </c>
       <c r="BF49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG49" t="n">
         <v>95</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
         <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I50" t="n">
         <v>2.74</v>
@@ -10096,25 +10096,25 @@
         <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P50" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R50" t="n">
         <v>1.31</v>
       </c>
       <c r="S50" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U50" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V50" t="n">
         <v>1.57</v>
@@ -10123,13 +10123,13 @@
         <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y50" t="n">
         <v>10.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA50" t="n">
         <v>40</v>
@@ -10138,10 +10138,10 @@
         <v>11</v>
       </c>
       <c r="AC50" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE50" t="n">
         <v>32</v>
@@ -10150,7 +10150,7 @@
         <v>19</v>
       </c>
       <c r="AG50" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH50" t="n">
         <v>18.5</v>
@@ -10171,7 +10171,7 @@
         <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO50" t="n">
         <v>30</v>
@@ -10183,7 +10183,7 @@
         <v>9.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS50" t="n">
         <v>34</v>
@@ -10198,7 +10198,7 @@
         <v>11</v>
       </c>
       <c r="AW50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX50" t="n">
         <v>17.5</v>
@@ -10207,32 +10207,32 @@
         <v>11</v>
       </c>
       <c r="AZ50" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA50" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB50" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BC50" t="n">
         <v>30</v>
       </c>
       <c r="BD50" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE50" t="n">
         <v>30</v>
       </c>
       <c r="BF50" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BG50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -10272,13 +10272,13 @@
         <v>3.15</v>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J51" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K51" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L51" t="n">
         <v>1.48</v>
@@ -10287,7 +10287,7 @@
         <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O51" t="n">
         <v>1.4</v>
@@ -10296,7 +10296,7 @@
         <v>1.73</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R51" t="n">
         <v>1.28</v>
@@ -10320,7 +10320,7 @@
         <v>22</v>
       </c>
       <c r="Y51" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="Z51" t="n">
         <v>1000</v>
@@ -10332,13 +10332,13 @@
         <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD51" t="n">
         <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF51" t="n">
         <v>80</v>
@@ -10356,7 +10356,7 @@
         <v>170</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL51" t="n">
         <v>1000</v>
@@ -10365,7 +10365,7 @@
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO51" t="n">
         <v>1000</v>
@@ -10377,10 +10377,10 @@
         <v>9.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AT51" t="n">
         <v>8.199999999999999</v>
@@ -10389,44 +10389,44 @@
         <v>6.4</v>
       </c>
       <c r="AV51" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AX51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BB51" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BF51" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG51" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -10460,13 +10460,13 @@
         <v>2.26</v>
       </c>
       <c r="G52" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H52" t="n">
         <v>3.6</v>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>3.05</v>
@@ -10484,7 +10484,7 @@
         <v>2.88</v>
       </c>
       <c r="O52" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P52" t="n">
         <v>1.62</v>
@@ -10496,7 +10496,7 @@
         <v>1.23</v>
       </c>
       <c r="S52" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T52" t="n">
         <v>2</v>
@@ -10565,49 +10565,49 @@
         <v>500</v>
       </c>
       <c r="AP52" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ52" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR52" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS52" t="n">
         <v>5.8</v>
       </c>
       <c r="AT52" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU52" t="n">
         <v>6.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AX52" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AY52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ52" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA52" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB52" t="n">
         <v>10.5</v>
       </c>
       <c r="BC52" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE52" t="n">
         <v>6</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>2.16</v>
       </c>
       <c r="G53" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H53" t="n">
         <v>3.65</v>
@@ -10702,7 +10702,7 @@
         <v>1.33</v>
       </c>
       <c r="W53" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X53" t="n">
         <v>20</v>
@@ -10768,7 +10768,7 @@
         <v>6.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT53" t="n">
         <v>4.9</v>
@@ -10804,7 +10804,7 @@
         <v>7.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BF53" t="n">
         <v>6.4</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -10890,10 +10890,10 @@
         <v>1.9</v>
       </c>
       <c r="U54" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W54" t="n">
         <v>2.52</v>
@@ -10905,7 +10905,7 @@
         <v>26</v>
       </c>
       <c r="Z54" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AA54" t="n">
         <v>700</v>
@@ -10920,7 +10920,7 @@
         <v>32</v>
       </c>
       <c r="AE54" t="n">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="AF54" t="n">
         <v>10</v>
@@ -10941,7 +10941,7 @@
         <v>17.5</v>
       </c>
       <c r="AL54" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AM54" t="n">
         <v>580</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="AQ54" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR54" t="n">
         <v>42</v>
@@ -10968,13 +10968,13 @@
         <v>8</v>
       </c>
       <c r="AU54" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV54" t="n">
         <v>20</v>
       </c>
       <c r="AW54" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX54" t="n">
         <v>8.800000000000001</v>
@@ -10995,7 +10995,7 @@
         <v>15</v>
       </c>
       <c r="BD54" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BE54" t="n">
         <v>42</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -11039,13 +11039,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G55" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H55" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
         <v>3.1</v>
@@ -11054,10 +11054,10 @@
         <v>3.05</v>
       </c>
       <c r="K55" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L55" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M55" t="n">
         <v>1.14</v>
@@ -11066,7 +11066,7 @@
         <v>2.56</v>
       </c>
       <c r="O55" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P55" t="n">
         <v>1.5</v>
@@ -11078,10 +11078,10 @@
         <v>1.17</v>
       </c>
       <c r="S55" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T55" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
         <v>1.75</v>
@@ -11093,16 +11093,16 @@
         <v>1.52</v>
       </c>
       <c r="X55" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AA55" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AB55" t="n">
         <v>8</v>
@@ -11111,28 +11111,28 @@
         <v>7.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE55" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AF55" t="n">
         <v>20</v>
       </c>
       <c r="AG55" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AI55" t="n">
         <v>80</v>
       </c>
       <c r="AJ55" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AK55" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AL55" t="n">
         <v>75</v>
@@ -11141,7 +11141,7 @@
         <v>230</v>
       </c>
       <c r="AN55" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AO55" t="n">
         <v>65</v>
@@ -11156,7 +11156,7 @@
         <v>13.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="AT55" t="n">
         <v>7.2</v>
@@ -11168,41 +11168,41 @@
         <v>12.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX55" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AY55" t="n">
         <v>12</v>
       </c>
       <c r="AZ55" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BA55" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BB55" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BC55" t="n">
         <v>38</v>
       </c>
       <c r="BD55" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BE55" t="n">
-        <v>6.8</v>
+        <v>48</v>
       </c>
       <c r="BF55" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BG55" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G56" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H56" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L56" t="n">
         <v>1.61</v>
@@ -11257,7 +11257,7 @@
         <v>1.13</v>
       </c>
       <c r="N56" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O56" t="n">
         <v>1.58</v>
@@ -11275,16 +11275,16 @@
         <v>5.8</v>
       </c>
       <c r="T56" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U56" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V56" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W56" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="X56" t="n">
         <v>9.800000000000001</v>
@@ -11296,10 +11296,10 @@
         <v>36</v>
       </c>
       <c r="AA56" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB56" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC56" t="n">
         <v>8.6</v>
@@ -11323,10 +11323,10 @@
         <v>120</v>
       </c>
       <c r="AJ56" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL56" t="n">
         <v>1000</v>
@@ -11338,7 +11338,7 @@
         <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP56" t="n">
         <v>7.2</v>
@@ -11347,13 +11347,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR56" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AT56" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU56" t="n">
         <v>6.4</v>
@@ -11362,7 +11362,7 @@
         <v>16</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX56" t="n">
         <v>9.4</v>
@@ -11374,29 +11374,29 @@
         <v>22</v>
       </c>
       <c r="BA56" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB56" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC56" t="n">
         <v>26</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF56" t="n">
         <v>16</v>
       </c>
       <c r="BG56" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
